--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>207207</v>
       </c>
       <c r="C2718" t="n">
-        <v>3.51600003242493</v>
+        <v>3.52999997138977</v>
       </c>
       <c r="D2718" t="n">
         <v>3.42799997329712</v>
@@ -62883,6 +62883,29 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>205001</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>3.56200003623962</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>3.4760000705719</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>3.49399995803833</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>3.49799990653992</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>136279</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>3.48600006103516</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>168979</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>3.49399995803833</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>3.42799997329712</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>3.42199993133545</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -62943,7 +62943,7 @@
         <v>3.49399995803833</v>
       </c>
       <c r="D2721" t="n">
-        <v>3.42799997329712</v>
+        <v>3.42199993133545</v>
       </c>
       <c r="E2721" t="n">
         <v>3.45000004768372</v>
@@ -62952,6 +62952,29 @@
         <v>3.42199993133545</v>
       </c>
       <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>755841</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>3.31200003623962</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>3.31200003623962</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>214854</v>
+        <v>250904</v>
       </c>
       <c r="C2715" t="n">
-        <v>3.52999997138977</v>
+        <v>3.57399988174438</v>
       </c>
       <c r="D2715" t="n">
-        <v>3.47000002861023</v>
+        <v>3.50600004196167</v>
       </c>
       <c r="E2715" t="n">
-        <v>3.52999997138977</v>
+        <v>3.54999995231628</v>
       </c>
       <c r="F2715" t="n">
-        <v>3.48200011253357</v>
+        <v>3.5239999294281</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>230436</v>
+        <v>214854</v>
       </c>
       <c r="C2716" t="n">
-        <v>3.48000001907349</v>
+        <v>3.52999997138977</v>
       </c>
       <c r="D2716" t="n">
-        <v>3.41400003433228</v>
+        <v>3.47000002861023</v>
       </c>
       <c r="E2716" t="n">
-        <v>3.46000003814697</v>
+        <v>3.52999997138977</v>
       </c>
       <c r="F2716" t="n">
-        <v>3.43400001525879</v>
+        <v>3.48200011253357</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>111611</v>
+        <v>230436</v>
       </c>
       <c r="C2717" t="n">
-        <v>3.45799994468689</v>
+        <v>3.48000001907349</v>
       </c>
       <c r="D2717" t="n">
-        <v>3.42000007629395</v>
+        <v>3.41400003433228</v>
       </c>
       <c r="E2717" t="n">
-        <v>3.4300000667572</v>
+        <v>3.46000003814697</v>
       </c>
       <c r="F2717" t="n">
-        <v>3.43600010871887</v>
+        <v>3.43400001525879</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>207207</v>
+        <v>111611</v>
       </c>
       <c r="C2718" t="n">
-        <v>3.52999997138977</v>
+        <v>3.45799994468689</v>
       </c>
       <c r="D2718" t="n">
-        <v>3.42799997329712</v>
+        <v>3.42000007629395</v>
       </c>
       <c r="E2718" t="n">
-        <v>3.42799997329712</v>
+        <v>3.4300000667572</v>
       </c>
       <c r="F2718" t="n">
-        <v>3.52999997138977</v>
+        <v>3.43600010871887</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>205001</v>
+        <v>207207</v>
       </c>
       <c r="C2719" t="n">
-        <v>3.56200003623962</v>
+        <v>3.52999997138977</v>
       </c>
       <c r="D2719" t="n">
-        <v>3.4760000705719</v>
+        <v>3.42799997329712</v>
       </c>
       <c r="E2719" t="n">
-        <v>3.49399995803833</v>
+        <v>3.42799997329712</v>
       </c>
       <c r="F2719" t="n">
-        <v>3.49799990653992</v>
+        <v>3.52999997138977</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>136279</v>
+        <v>205001</v>
       </c>
       <c r="C2720" t="n">
-        <v>3.5</v>
+        <v>3.56200003623962</v>
       </c>
       <c r="D2720" t="n">
-        <v>3.44000005722046</v>
+        <v>3.4760000705719</v>
       </c>
       <c r="E2720" t="n">
-        <v>3.44000005722046</v>
+        <v>3.49399995803833</v>
       </c>
       <c r="F2720" t="n">
-        <v>3.48600006103516</v>
+        <v>3.49799990653992</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>168979</v>
+        <v>136279</v>
       </c>
       <c r="C2721" t="n">
-        <v>3.49399995803833</v>
+        <v>3.5</v>
       </c>
       <c r="D2721" t="n">
-        <v>3.42199993133545</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="E2721" t="n">
-        <v>3.45000004768372</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="F2721" t="n">
-        <v>3.42199993133545</v>
+        <v>3.48600006103516</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>755841</v>
+        <v>168979</v>
       </c>
       <c r="C2722" t="n">
-        <v>3.55999994277954</v>
+        <v>3.49399995803833</v>
       </c>
       <c r="D2722" t="n">
+        <v>3.42199993133545</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>3.42199993133545</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>622228</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="E2723" t="n">
         <v>3.31200003623962</v>
       </c>
-      <c r="E2722" t="n">
-        <v>3.4300000667572</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>3.31200003623962</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>3.28200006484985</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.86999988555908</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.84800004959106</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>533927</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.99600005149841</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.85199999809265</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.85199999809265</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>2.85199999809265</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.95000004768372</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>420515</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.83599996566772</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.97000002861023</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>2.97000002861023</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>2.84599995613098</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>551692</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.82399988174438</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>2.82399988174438</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>2.82599997520447</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>600514</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>455682</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.84999990463257</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>2.84999990463257</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -456,7 +456,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G3" t="n">
-        <v>11.4748277664185</v>
+        <v>11.4748268127441</v>
       </c>
       <c r="H3" t="n">
         <v>1108247</v>
@@ -514,7 +514,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G5" t="n">
-        <v>10.9045333862305</v>
+        <v>10.9045343399048</v>
       </c>
       <c r="H5" t="n">
         <v>1852775</v>
@@ -659,7 +659,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G10" t="n">
-        <v>10.1900968551636</v>
+        <v>10.1900978088379</v>
       </c>
       <c r="H10" t="n">
         <v>1503952</v>
@@ -688,7 +688,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G11" t="n">
-        <v>10.0459575653076</v>
+        <v>10.0459585189819</v>
       </c>
       <c r="H11" t="n">
         <v>1539157</v>
@@ -717,7 +717,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>9.70127201080322</v>
+        <v>9.70127391815186</v>
       </c>
       <c r="H12" t="n">
         <v>1418563</v>
@@ -746,7 +746,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.68247222900391</v>
+        <v>9.68247318267822</v>
       </c>
       <c r="H13" t="n">
         <v>1176302</v>
@@ -833,7 +833,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G16" t="n">
-        <v>10.1023607254028</v>
+        <v>10.1023597717285</v>
       </c>
       <c r="H16" t="n">
         <v>1943472</v>
@@ -978,7 +978,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G21" t="n">
-        <v>9.66367149353027</v>
+        <v>9.66367244720459</v>
       </c>
       <c r="H21" t="n">
         <v>1558827</v>
@@ -1036,7 +1036,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G23" t="n">
-        <v>9.68873977661133</v>
+        <v>9.68874073028564</v>
       </c>
       <c r="H23" t="n">
         <v>1230112</v>
@@ -1065,7 +1065,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G24" t="n">
-        <v>9.50699710845947</v>
+        <v>9.50699806213379</v>
       </c>
       <c r="H24" t="n">
         <v>2187286</v>
@@ -1094,7 +1094,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G25" t="n">
-        <v>10.2277002334595</v>
+        <v>10.2276992797852</v>
       </c>
       <c r="H25" t="n">
         <v>3140539</v>
@@ -1123,7 +1123,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G26" t="n">
-        <v>10.0835599899292</v>
+        <v>10.0835590362549</v>
       </c>
       <c r="H26" t="n">
         <v>2727909</v>
@@ -1152,7 +1152,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G27" t="n">
-        <v>9.19991588592529</v>
+        <v>9.19991779327393</v>
       </c>
       <c r="H27" t="n">
         <v>2096946</v>
@@ -1181,7 +1181,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>9.32525539398193</v>
+        <v>9.32525634765625</v>
       </c>
       <c r="H28" t="n">
         <v>3143818</v>
@@ -1210,7 +1210,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G29" t="n">
-        <v>9.68873977661133</v>
+        <v>9.68874073028564</v>
       </c>
       <c r="H29" t="n">
         <v>2285199</v>
@@ -1239,7 +1239,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G30" t="n">
-        <v>8.98057270050049</v>
+        <v>8.98057174682617</v>
       </c>
       <c r="H30" t="n">
         <v>2027495</v>
@@ -1268,7 +1268,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G31" t="n">
-        <v>9.19364833831787</v>
+        <v>9.19364929199219</v>
       </c>
       <c r="H31" t="n">
         <v>1677204</v>
@@ -1355,7 +1355,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G34" t="n">
-        <v>9.98955535888672</v>
+        <v>9.9895544052124</v>
       </c>
       <c r="H34" t="n">
         <v>1286403</v>
@@ -1471,7 +1471,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G38" t="n">
-        <v>9.98955535888672</v>
+        <v>9.9895544052124</v>
       </c>
       <c r="H38" t="n">
         <v>1126410</v>
@@ -1500,7 +1500,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G39" t="n">
-        <v>9.37539100646973</v>
+        <v>9.37539196014404</v>
       </c>
       <c r="H39" t="n">
         <v>2579271</v>
@@ -1558,7 +1558,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G41" t="n">
-        <v>10.089825630188</v>
+        <v>10.0898275375366</v>
       </c>
       <c r="H41" t="n">
         <v>1226980</v>
@@ -1616,7 +1616,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G43" t="n">
-        <v>10.7603931427002</v>
+        <v>10.7603921890259</v>
       </c>
       <c r="H43" t="n">
         <v>1742306</v>
@@ -1790,7 +1790,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G49" t="n">
-        <v>11.3494892120361</v>
+        <v>11.3494882583618</v>
       </c>
       <c r="H49" t="n">
         <v>3548144</v>
@@ -1819,7 +1819,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G50" t="n">
-        <v>11.0674734115601</v>
+        <v>11.0674743652344</v>
       </c>
       <c r="H50" t="n">
         <v>2746078</v>
@@ -1877,7 +1877,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G52" t="n">
-        <v>11.7380390167236</v>
+        <v>11.7380409240723</v>
       </c>
       <c r="H52" t="n">
         <v>1277405</v>
@@ -1906,7 +1906,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>11.7192401885986</v>
+        <v>11.7192392349243</v>
       </c>
       <c r="H53" t="n">
         <v>1653019</v>
@@ -1935,7 +1935,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G54" t="n">
-        <v>11.6127004623413</v>
+        <v>11.6127014160156</v>
       </c>
       <c r="H54" t="n">
         <v>1634789</v>
@@ -1964,7 +1964,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G55" t="n">
-        <v>11.7255058288574</v>
+        <v>11.7255048751831</v>
       </c>
       <c r="H55" t="n">
         <v>1533301</v>
@@ -1993,7 +1993,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G56" t="n">
-        <v>11.8132448196411</v>
+        <v>11.8132438659668</v>
       </c>
       <c r="H56" t="n">
         <v>1570187</v>
@@ -2022,7 +2022,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>11.7192401885986</v>
+        <v>11.7192392349243</v>
       </c>
       <c r="H57" t="n">
         <v>2294980</v>
@@ -2109,7 +2109,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G60" t="n">
-        <v>11.0048046112061</v>
+        <v>11.0048036575317</v>
       </c>
       <c r="H60" t="n">
         <v>1931701</v>
@@ -2196,7 +2196,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G63" t="n">
-        <v>11.3620204925537</v>
+        <v>11.362021446228</v>
       </c>
       <c r="H63" t="n">
         <v>1901194</v>
@@ -2283,7 +2283,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8167963027954</v>
+        <v>10.8167953491211</v>
       </c>
       <c r="H66" t="n">
         <v>2312805</v>
@@ -2312,7 +2312,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G67" t="n">
-        <v>10.8167963027954</v>
+        <v>10.8167953491211</v>
       </c>
       <c r="H67" t="n">
         <v>1717734</v>
@@ -2399,7 +2399,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G70" t="n">
-        <v>11.2492160797119</v>
+        <v>11.2492170333862</v>
       </c>
       <c r="H70" t="n">
         <v>3927667</v>
@@ -2428,7 +2428,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G71" t="n">
-        <v>11.5437650680542</v>
+        <v>11.5437641143799</v>
       </c>
       <c r="H71" t="n">
         <v>2898593</v>
@@ -2486,7 +2486,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>12.1579275131226</v>
+        <v>12.1579265594482</v>
       </c>
       <c r="H73" t="n">
         <v>2276229</v>
@@ -2515,7 +2515,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>12.1704597473145</v>
+        <v>12.1704616546631</v>
       </c>
       <c r="H74" t="n">
         <v>1750019</v>
@@ -2544,7 +2544,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G75" t="n">
-        <v>12.3271350860596</v>
+        <v>12.3271360397339</v>
       </c>
       <c r="H75" t="n">
         <v>1517301</v>
@@ -2573,7 +2573,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G76" t="n">
-        <v>12.3522033691406</v>
+        <v>12.3522043228149</v>
       </c>
       <c r="H76" t="n">
         <v>2192358</v>
@@ -2631,7 +2631,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G78" t="n">
-        <v>12.4148721694946</v>
+        <v>12.4148750305176</v>
       </c>
       <c r="H78" t="n">
         <v>1799957</v>
@@ -2689,7 +2689,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G80" t="n">
-        <v>12.3835382461548</v>
+        <v>12.3835401535034</v>
       </c>
       <c r="H80" t="n">
         <v>1121472</v>
@@ -2863,7 +2863,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>11.9385843276978</v>
+        <v>11.9385833740234</v>
       </c>
       <c r="H86" t="n">
         <v>1411606</v>
@@ -2892,7 +2892,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G87" t="n">
-        <v>11.8195114135742</v>
+        <v>11.8195104598999</v>
       </c>
       <c r="H87" t="n">
         <v>1126967</v>
@@ -2921,7 +2921,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G88" t="n">
-        <v>12.1203260421753</v>
+        <v>12.1203269958496</v>
       </c>
       <c r="H88" t="n">
         <v>1779199</v>
@@ -2950,7 +2950,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G89" t="n">
-        <v>12.1015224456787</v>
+        <v>12.1015243530273</v>
       </c>
       <c r="H89" t="n">
         <v>1016505</v>
@@ -3008,7 +3008,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G91" t="n">
-        <v>12.2769994735718</v>
+        <v>12.2770004272461</v>
       </c>
       <c r="H91" t="n">
         <v>942593</v>
@@ -3066,7 +3066,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>11.6440362930298</v>
+        <v>11.6440343856812</v>
       </c>
       <c r="H93" t="n">
         <v>1147356</v>
@@ -3095,7 +3095,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>11.6879062652588</v>
+        <v>11.6879043579102</v>
       </c>
       <c r="H94" t="n">
         <v>884124</v>
@@ -3124,7 +3124,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G95" t="n">
-        <v>11.6189680099487</v>
+        <v>11.618968963623</v>
       </c>
       <c r="H95" t="n">
         <v>783093</v>
@@ -3153,7 +3153,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>11.9699192047119</v>
+        <v>11.9699172973633</v>
       </c>
       <c r="H96" t="n">
         <v>1614264</v>
@@ -3211,7 +3211,7 @@
         <v>19.3899993896484</v>
       </c>
       <c r="G98" t="n">
-        <v>12.1516580581665</v>
+        <v>12.1516590118408</v>
       </c>
       <c r="H98" t="n">
         <v>873387</v>
@@ -3240,7 +3240,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>12.43994140625</v>
+        <v>12.4399423599243</v>
       </c>
       <c r="H99" t="n">
         <v>1053915</v>
@@ -3298,7 +3298,7 @@
         <v>20</v>
       </c>
       <c r="G101" t="n">
-        <v>12.5974092483521</v>
+        <v>12.5974102020264</v>
       </c>
       <c r="H101" t="n">
         <v>1002511</v>
@@ -3356,7 +3356,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G103" t="n">
-        <v>12.8178625106812</v>
+        <v>12.8178634643555</v>
       </c>
       <c r="H103" t="n">
         <v>814469</v>
@@ -3443,7 +3443,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G106" t="n">
-        <v>12.6289024353027</v>
+        <v>12.6289014816284</v>
       </c>
       <c r="H106" t="n">
         <v>597708</v>
@@ -3501,7 +3501,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G108" t="n">
-        <v>12.5659160614014</v>
+        <v>12.5659151077271</v>
       </c>
       <c r="H108" t="n">
         <v>436393</v>
@@ -3559,7 +3559,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G110" t="n">
-        <v>12.2257862091064</v>
+        <v>12.2257852554321</v>
       </c>
       <c r="H110" t="n">
         <v>609987</v>
@@ -3588,7 +3588,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>12.5155267715454</v>
+        <v>12.5155258178711</v>
       </c>
       <c r="H111" t="n">
         <v>596759</v>
@@ -3617,7 +3617,7 @@
         <v>19.8299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>12.490330696106</v>
+        <v>12.4903316497803</v>
       </c>
       <c r="H112" t="n">
         <v>554877</v>
@@ -3646,7 +3646,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G113" t="n">
-        <v>12.4147453308105</v>
+        <v>12.4147462844849</v>
       </c>
       <c r="H113" t="n">
         <v>819611</v>
@@ -3762,7 +3762,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G117" t="n">
-        <v>11.0668230056763</v>
+        <v>11.066822052002</v>
       </c>
       <c r="H117" t="n">
         <v>1136973</v>
@@ -3849,7 +3849,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>11.9045515060425</v>
+        <v>11.9045505523682</v>
       </c>
       <c r="H120" t="n">
         <v>1061050</v>
@@ -3907,7 +3907,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>11.7155895233154</v>
+        <v>11.7155904769897</v>
       </c>
       <c r="H122" t="n">
         <v>789206</v>
@@ -3936,7 +3936,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G123" t="n">
-        <v>12.3643569946289</v>
+        <v>12.3643560409546</v>
       </c>
       <c r="H123" t="n">
         <v>1016975</v>
@@ -4052,7 +4052,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G127" t="n">
-        <v>10.1976022720337</v>
+        <v>10.197603225708</v>
       </c>
       <c r="H127" t="n">
         <v>1428359</v>
@@ -4110,7 +4110,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G129" t="n">
-        <v>10.0842256546021</v>
+        <v>10.0842266082764</v>
       </c>
       <c r="H129" t="n">
         <v>1099550</v>
@@ -4139,7 +4139,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>9.62441921234131</v>
+        <v>9.62442016601562</v>
       </c>
       <c r="H130" t="n">
         <v>727152</v>
@@ -4197,7 +4197,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G132" t="n">
-        <v>9.45435428619385</v>
+        <v>9.45435523986816</v>
       </c>
       <c r="H132" t="n">
         <v>1094196</v>
@@ -4313,7 +4313,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G136" t="n">
-        <v>10.7959785461426</v>
+        <v>10.7959794998169</v>
       </c>
       <c r="H136" t="n">
         <v>933358</v>
@@ -4458,7 +4458,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>10.1724081039429</v>
+        <v>10.1724071502686</v>
       </c>
       <c r="H141" t="n">
         <v>672156</v>
@@ -4545,7 +4545,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G144" t="n">
-        <v>10.1283178329468</v>
+        <v>10.1283168792725</v>
       </c>
       <c r="H144" t="n">
         <v>424987</v>
@@ -4574,7 +4574,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.1724081039429</v>
+        <v>10.1724071502686</v>
       </c>
       <c r="H145" t="n">
         <v>511193</v>
@@ -4603,7 +4603,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G146" t="n">
-        <v>9.46695327758789</v>
+        <v>9.46695232391357</v>
       </c>
       <c r="H146" t="n">
         <v>7471690</v>
@@ -4661,7 +4661,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G148" t="n">
-        <v>9.30318641662598</v>
+        <v>9.30318737030029</v>
       </c>
       <c r="H148" t="n">
         <v>1171880</v>
@@ -4777,7 +4777,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>8.28279590606689</v>
+        <v>8.28279685974121</v>
       </c>
       <c r="H152" t="n">
         <v>1111787</v>
@@ -4864,7 +4864,7 @@
         <v>14</v>
       </c>
       <c r="G155" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H155" t="n">
         <v>1912889</v>
@@ -5125,7 +5125,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G164" t="n">
-        <v>8.68591403961182</v>
+        <v>8.6859130859375</v>
       </c>
       <c r="H164" t="n">
         <v>1585086</v>
@@ -5154,7 +5154,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G165" t="n">
-        <v>9.0638370513916</v>
+        <v>9.06383609771729</v>
       </c>
       <c r="H165" t="n">
         <v>2535304</v>
@@ -5183,7 +5183,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G166" t="n">
-        <v>9.21500396728516</v>
+        <v>9.21500492095947</v>
       </c>
       <c r="H166" t="n">
         <v>2163717</v>
@@ -5212,7 +5212,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G167" t="n">
-        <v>8.99454879760742</v>
+        <v>8.99454975128174</v>
       </c>
       <c r="H167" t="n">
         <v>1182183</v>
@@ -5241,7 +5241,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G168" t="n">
-        <v>8.95045948028564</v>
+        <v>8.95045852661133</v>
       </c>
       <c r="H168" t="n">
         <v>1311813</v>
@@ -5444,7 +5444,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G175" t="n">
-        <v>9.20870590209961</v>
+        <v>9.20870494842529</v>
       </c>
       <c r="H175" t="n">
         <v>1096481</v>
@@ -5531,7 +5531,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>9.10162734985352</v>
+        <v>9.10162830352783</v>
       </c>
       <c r="H178" t="n">
         <v>950590</v>
@@ -5560,7 +5560,7 @@
         <v>14</v>
       </c>
       <c r="G179" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H179" t="n">
         <v>1221120</v>
@@ -5589,7 +5589,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G180" t="n">
-        <v>8.54104328155518</v>
+        <v>8.54104423522949</v>
       </c>
       <c r="H180" t="n">
         <v>1625492</v>
@@ -5647,7 +5647,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G182" t="n">
-        <v>8.62922477722168</v>
+        <v>8.62922382354736</v>
       </c>
       <c r="H182" t="n">
         <v>964252</v>
@@ -5763,7 +5763,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G186" t="n">
-        <v>8.54734230041504</v>
+        <v>8.54734134674072</v>
       </c>
       <c r="H186" t="n">
         <v>651282</v>
@@ -5821,7 +5821,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G188" t="n">
-        <v>8.76149749755859</v>
+        <v>8.76149845123291</v>
       </c>
       <c r="H188" t="n">
         <v>922708</v>
@@ -5879,7 +5879,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G190" t="n">
-        <v>8.68591403961182</v>
+        <v>8.6859130859375</v>
       </c>
       <c r="H190" t="n">
         <v>801255</v>
@@ -5966,7 +5966,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G193" t="n">
-        <v>8.79929065704346</v>
+        <v>8.79928970336914</v>
       </c>
       <c r="H193" t="n">
         <v>1335974</v>
@@ -6024,7 +6024,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G195" t="n">
-        <v>8.81188678741455</v>
+        <v>8.81188774108887</v>
       </c>
       <c r="H195" t="n">
         <v>844305</v>
@@ -6140,7 +6140,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G199" t="n">
-        <v>8.54734230041504</v>
+        <v>8.54734134674072</v>
       </c>
       <c r="H199" t="n">
         <v>1379248</v>
@@ -6198,7 +6198,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G201" t="n">
-        <v>8.19461536407471</v>
+        <v>8.19461441040039</v>
       </c>
       <c r="H201" t="n">
         <v>2306194</v>
@@ -6227,7 +6227,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G202" t="n">
-        <v>8.2072114944458</v>
+        <v>8.20721054077148</v>
       </c>
       <c r="H202" t="n">
         <v>2787358</v>
@@ -6256,7 +6256,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G203" t="n">
-        <v>8.28279590606689</v>
+        <v>8.28279685974121</v>
       </c>
       <c r="H203" t="n">
         <v>1163891</v>
@@ -6343,7 +6343,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G206" t="n">
-        <v>8.54104328155518</v>
+        <v>8.54104423522949</v>
       </c>
       <c r="H206" t="n">
         <v>730084</v>
@@ -6372,7 +6372,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G207" t="n">
-        <v>8.25130367279053</v>
+        <v>8.25130271911621</v>
       </c>
       <c r="H207" t="n">
         <v>3783163</v>
@@ -6459,7 +6459,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>8.26390075683594</v>
+        <v>8.26389980316162</v>
       </c>
       <c r="H210" t="n">
         <v>1092158</v>
@@ -6488,7 +6488,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>8.25130367279053</v>
+        <v>8.25130271911621</v>
       </c>
       <c r="H211" t="n">
         <v>1109219</v>
@@ -6633,7 +6633,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>7.84188652038574</v>
+        <v>7.84188604354858</v>
       </c>
       <c r="H216" t="n">
         <v>2063953</v>
@@ -6662,7 +6662,7 @@
         <v>12.25</v>
       </c>
       <c r="G217" t="n">
-        <v>7.71591234207153</v>
+        <v>7.71591281890869</v>
       </c>
       <c r="H217" t="n">
         <v>2414557</v>
@@ -6691,7 +6691,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>7.62143325805664</v>
+        <v>7.62143278121948</v>
       </c>
       <c r="H218" t="n">
         <v>1128128</v>
@@ -6720,7 +6720,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G219" t="n">
-        <v>7.6403284072876</v>
+        <v>7.64032888412476</v>
       </c>
       <c r="H219" t="n">
         <v>923117</v>
@@ -6749,7 +6749,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>7.62143325805664</v>
+        <v>7.62143278121948</v>
       </c>
       <c r="H220" t="n">
         <v>795000</v>
@@ -6807,7 +6807,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G222" t="n">
-        <v>7.3631854057312</v>
+        <v>7.36318492889404</v>
       </c>
       <c r="H222" t="n">
         <v>1639210</v>
@@ -6865,7 +6865,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>7.3631854057312</v>
+        <v>7.36318492889404</v>
       </c>
       <c r="H224" t="n">
         <v>1415172</v>
@@ -6894,7 +6894,7 @@
         <v>11.75</v>
       </c>
       <c r="G225" t="n">
-        <v>7.40097713470459</v>
+        <v>7.40097761154175</v>
       </c>
       <c r="H225" t="n">
         <v>841735</v>
@@ -6952,7 +6952,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G227" t="n">
-        <v>7.38208198547363</v>
+        <v>7.38208150863647</v>
       </c>
       <c r="H227" t="n">
         <v>995531</v>
@@ -7039,7 +7039,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G230" t="n">
-        <v>7.21201705932617</v>
+        <v>7.21201658248901</v>
       </c>
       <c r="H230" t="n">
         <v>1104119</v>
@@ -7068,7 +7068,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G231" t="n">
-        <v>7.28760051727295</v>
+        <v>7.28760004043579</v>
       </c>
       <c r="H231" t="n">
         <v>896267</v>
@@ -7155,7 +7155,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G234" t="n">
-        <v>7.04195213317871</v>
+        <v>7.04195117950439</v>
       </c>
       <c r="H234" t="n">
         <v>1442837</v>
@@ -7213,7 +7213,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G236" t="n">
-        <v>7.19941854476929</v>
+        <v>7.1994194984436</v>
       </c>
       <c r="H236" t="n">
         <v>1209794</v>
@@ -7242,7 +7242,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G237" t="n">
-        <v>7.23091220855713</v>
+        <v>7.23091173171997</v>
       </c>
       <c r="H237" t="n">
         <v>1245120</v>
@@ -7300,7 +7300,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G239" t="n">
-        <v>7.64662647247314</v>
+        <v>7.64662790298462</v>
       </c>
       <c r="H239" t="n">
         <v>2258364</v>
@@ -7474,7 +7474,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G245" t="n">
-        <v>11.2872791290283</v>
+        <v>11.287278175354</v>
       </c>
       <c r="H245" t="n">
         <v>28007514</v>
@@ -7503,7 +7503,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>11.40065574646</v>
+        <v>11.4006567001343</v>
       </c>
       <c r="H246" t="n">
         <v>16601084</v>
@@ -7532,7 +7532,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2242918014526</v>
+        <v>11.2242908477783</v>
       </c>
       <c r="H247" t="n">
         <v>9584317</v>
@@ -7561,7 +7561,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G248" t="n">
-        <v>11.1676034927368</v>
+        <v>11.1676025390625</v>
       </c>
       <c r="H248" t="n">
         <v>4459716</v>
@@ -7590,7 +7590,7 @@
         <v>18</v>
       </c>
       <c r="G249" t="n">
-        <v>11.3376693725586</v>
+        <v>11.3376684188843</v>
       </c>
       <c r="H249" t="n">
         <v>3602962</v>
@@ -7677,7 +7677,7 @@
         <v>20</v>
       </c>
       <c r="G252" t="n">
-        <v>12.5974092483521</v>
+        <v>12.5974102020264</v>
       </c>
       <c r="H252" t="n">
         <v>10849610</v>
@@ -7706,7 +7706,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G253" t="n">
-        <v>12.6289024353027</v>
+        <v>12.6289014816284</v>
       </c>
       <c r="H253" t="n">
         <v>5607153</v>
@@ -7764,7 +7764,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G255" t="n">
-        <v>12.8871479034424</v>
+        <v>12.8871469497681</v>
       </c>
       <c r="H255" t="n">
         <v>3550302</v>
@@ -7793,7 +7793,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>12.8178625106812</v>
+        <v>12.8178634643555</v>
       </c>
       <c r="H256" t="n">
         <v>1834829</v>
@@ -7822,7 +7822,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G257" t="n">
-        <v>12.9438371658325</v>
+        <v>12.9438362121582</v>
       </c>
       <c r="H257" t="n">
         <v>1863651</v>
@@ -7851,7 +7851,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G258" t="n">
-        <v>13.0761098861694</v>
+        <v>13.0761108398438</v>
       </c>
       <c r="H258" t="n">
         <v>1847315</v>
@@ -7996,7 +7996,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G263" t="n">
-        <v>12.9438371658325</v>
+        <v>12.9438362121582</v>
       </c>
       <c r="H263" t="n">
         <v>1630424</v>
@@ -8025,7 +8025,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G264" t="n">
-        <v>12.9753322601318</v>
+        <v>12.9753313064575</v>
       </c>
       <c r="H264" t="n">
         <v>1714652</v>
@@ -8112,7 +8112,7 @@
         <v>21</v>
       </c>
       <c r="G267" t="n">
-        <v>13.2272787094116</v>
+        <v>13.2272796630859</v>
       </c>
       <c r="H267" t="n">
         <v>1346982</v>
@@ -8141,7 +8141,7 @@
         <v>21</v>
       </c>
       <c r="G268" t="n">
-        <v>13.2272787094116</v>
+        <v>13.2272796630859</v>
       </c>
       <c r="H268" t="n">
         <v>1051154</v>
@@ -8228,7 +8228,7 @@
         <v>21.3799991607666</v>
       </c>
       <c r="G271" t="n">
-        <v>13.4666309356689</v>
+        <v>13.4666299819946</v>
       </c>
       <c r="H271" t="n">
         <v>3103321</v>
@@ -8257,7 +8257,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G272" t="n">
-        <v>13.4414348602295</v>
+        <v>13.4414358139038</v>
       </c>
       <c r="H272" t="n">
         <v>2196155</v>
@@ -8373,7 +8373,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G276" t="n">
-        <v>13.000524520874</v>
+        <v>13.0005254745483</v>
       </c>
       <c r="H276" t="n">
         <v>1578920</v>
@@ -8402,7 +8402,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G277" t="n">
-        <v>12.8997459411621</v>
+        <v>12.8997468948364</v>
       </c>
       <c r="H277" t="n">
         <v>475230</v>
@@ -8489,7 +8489,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>12.376953125</v>
+        <v>12.3769540786743</v>
       </c>
       <c r="H280" t="n">
         <v>860032</v>
@@ -8518,7 +8518,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>12.4714336395264</v>
+        <v>12.4714345932007</v>
       </c>
       <c r="H281" t="n">
         <v>661827</v>
@@ -8547,7 +8547,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G282" t="n">
-        <v>12.4273443222046</v>
+        <v>12.4273433685303</v>
       </c>
       <c r="H282" t="n">
         <v>693547</v>
@@ -8605,7 +8605,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>11.9990320205688</v>
+        <v>11.9990329742432</v>
       </c>
       <c r="H284" t="n">
         <v>1146615</v>
@@ -8692,7 +8692,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G287" t="n">
-        <v>12.1439027786255</v>
+        <v>12.1439018249512</v>
       </c>
       <c r="H287" t="n">
         <v>562772</v>
@@ -8750,7 +8750,7 @@
         <v>19.5</v>
       </c>
       <c r="G289" t="n">
-        <v>12.2824745178223</v>
+        <v>12.2824735641479</v>
       </c>
       <c r="H289" t="n">
         <v>786441</v>
@@ -8779,7 +8779,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G290" t="n">
-        <v>12.1439027786255</v>
+        <v>12.1439018249512</v>
       </c>
       <c r="H290" t="n">
         <v>685389</v>
@@ -8808,7 +8808,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G291" t="n">
-        <v>12.1502017974854</v>
+        <v>12.150200843811</v>
       </c>
       <c r="H291" t="n">
         <v>887724</v>
@@ -8837,7 +8837,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G292" t="n">
-        <v>12.4336423873901</v>
+        <v>12.4336433410645</v>
       </c>
       <c r="H292" t="n">
         <v>1478762</v>
@@ -8866,7 +8866,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>12.408447265625</v>
+        <v>12.4084463119507</v>
       </c>
       <c r="H293" t="n">
         <v>575906</v>
@@ -8895,7 +8895,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G294" t="n">
-        <v>12.5533180236816</v>
+        <v>12.553318977356</v>
       </c>
       <c r="H294" t="n">
         <v>948237</v>
@@ -8924,7 +8924,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G295" t="n">
-        <v>12.4021501541138</v>
+        <v>12.4021492004395</v>
       </c>
       <c r="H295" t="n">
         <v>898180</v>
@@ -8982,7 +8982,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G297" t="n">
-        <v>12.0998106002808</v>
+        <v>12.0998115539551</v>
       </c>
       <c r="H297" t="n">
         <v>832241</v>
@@ -9040,7 +9040,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G299" t="n">
-        <v>12.2383832931519</v>
+        <v>12.2383842468262</v>
       </c>
       <c r="H299" t="n">
         <v>586693</v>
@@ -9127,7 +9127,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G302" t="n">
-        <v>12.1564989089966</v>
+        <v>12.1564998626709</v>
       </c>
       <c r="H302" t="n">
         <v>657498</v>
@@ -9185,7 +9185,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G304" t="n">
-        <v>12.1502017974854</v>
+        <v>12.150200843811</v>
       </c>
       <c r="H304" t="n">
         <v>502346</v>
@@ -9243,7 +9243,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G306" t="n">
-        <v>12.5848093032837</v>
+        <v>12.584810256958</v>
       </c>
       <c r="H306" t="n">
         <v>928681</v>
@@ -9272,7 +9272,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G307" t="n">
-        <v>12.6792907714844</v>
+        <v>12.6792917251587</v>
       </c>
       <c r="H307" t="n">
         <v>967060</v>
@@ -9359,7 +9359,7 @@
         <v>19.6900005340576</v>
       </c>
       <c r="G310" t="n">
-        <v>12.4021501541138</v>
+        <v>12.4021492004395</v>
       </c>
       <c r="H310" t="n">
         <v>869365</v>
@@ -9417,7 +9417,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>12.408447265625</v>
+        <v>12.4084463119507</v>
       </c>
       <c r="H312" t="n">
         <v>4763949</v>
@@ -9446,7 +9446,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G313" t="n">
-        <v>12.3958511352539</v>
+        <v>12.3958501815796</v>
       </c>
       <c r="H313" t="n">
         <v>869117</v>
@@ -9504,7 +9504,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>12.1061105728149</v>
+        <v>12.1061096191406</v>
       </c>
       <c r="H315" t="n">
         <v>957590</v>
@@ -9562,7 +9562,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G317" t="n">
-        <v>12.1690969467163</v>
+        <v>12.169095993042</v>
       </c>
       <c r="H317" t="n">
         <v>642476</v>
@@ -9678,7 +9678,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G321" t="n">
-        <v>12.1502017974854</v>
+        <v>12.150200843811</v>
       </c>
       <c r="H321" t="n">
         <v>507199</v>
@@ -9765,7 +9765,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>12.0620183944702</v>
+        <v>12.0620193481445</v>
       </c>
       <c r="H324" t="n">
         <v>492501</v>
@@ -9881,7 +9881,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G328" t="n">
-        <v>11.6022129058838</v>
+        <v>11.6022138595581</v>
       </c>
       <c r="H328" t="n">
         <v>1065647</v>
@@ -9997,7 +9997,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G332" t="n">
-        <v>10.9849414825439</v>
+        <v>10.9849405288696</v>
       </c>
       <c r="H332" t="n">
         <v>1164849</v>
@@ -10113,7 +10113,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>12.0305252075195</v>
+        <v>12.0305261611938</v>
       </c>
       <c r="H336" t="n">
         <v>1527622</v>
@@ -10142,7 +10142,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G337" t="n">
-        <v>12.1187076568604</v>
+        <v>12.1187086105347</v>
       </c>
       <c r="H337" t="n">
         <v>986622</v>
@@ -10171,7 +10171,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G338" t="n">
-        <v>12.1816940307617</v>
+        <v>12.181694984436</v>
       </c>
       <c r="H338" t="n">
         <v>788063</v>
@@ -10229,7 +10229,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G340" t="n">
-        <v>11.8226690292358</v>
+        <v>11.8226680755615</v>
       </c>
       <c r="H340" t="n">
         <v>1018925</v>
@@ -10316,7 +10316,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G343" t="n">
-        <v>11.577018737793</v>
+        <v>11.5770196914673</v>
       </c>
       <c r="H343" t="n">
         <v>577148</v>
@@ -10403,7 +10403,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G346" t="n">
-        <v>11.7281885147095</v>
+        <v>11.7281875610352</v>
       </c>
       <c r="H346" t="n">
         <v>789047</v>
@@ -10432,7 +10432,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>11.8730592727661</v>
+        <v>11.8730583190918</v>
       </c>
       <c r="H347" t="n">
         <v>736647</v>
@@ -10490,7 +10490,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G349" t="n">
-        <v>11.5329284667969</v>
+        <v>11.5329275131226</v>
       </c>
       <c r="H349" t="n">
         <v>705797</v>
@@ -10606,7 +10606,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>11.4762392044067</v>
+        <v>11.4762382507324</v>
       </c>
       <c r="H353" t="n">
         <v>907620</v>
@@ -10693,7 +10693,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G356" t="n">
-        <v>11.3754587173462</v>
+        <v>11.3754596710205</v>
       </c>
       <c r="H356" t="n">
         <v>506210</v>
@@ -10722,7 +10722,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>11.3502655029297</v>
+        <v>11.3502645492554</v>
       </c>
       <c r="H357" t="n">
         <v>471915</v>
@@ -10751,7 +10751,7 @@
         <v>18</v>
       </c>
       <c r="G358" t="n">
-        <v>11.3376693725586</v>
+        <v>11.3376684188843</v>
       </c>
       <c r="H358" t="n">
         <v>499941</v>
@@ -10780,7 +10780,7 @@
         <v>18.75</v>
       </c>
       <c r="G359" t="n">
-        <v>11.8100719451904</v>
+        <v>11.8100709915161</v>
       </c>
       <c r="H359" t="n">
         <v>1360819</v>
@@ -10809,7 +10809,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G360" t="n">
-        <v>11.9234466552734</v>
+        <v>11.9234476089478</v>
       </c>
       <c r="H360" t="n">
         <v>869973</v>
@@ -10867,7 +10867,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G362" t="n">
-        <v>11.0668230056763</v>
+        <v>11.066822052002</v>
       </c>
       <c r="H362" t="n">
         <v>2149371</v>
@@ -10896,7 +10896,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>11.1109142303467</v>
+        <v>11.110915184021</v>
       </c>
       <c r="H363" t="n">
         <v>587033</v>
@@ -10954,7 +10954,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>10.8967580795288</v>
+        <v>10.8967590332031</v>
       </c>
       <c r="H365" t="n">
         <v>654487</v>
@@ -10983,7 +10983,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>10.9282522201538</v>
+        <v>10.9282512664795</v>
       </c>
       <c r="H366" t="n">
         <v>767011</v>
@@ -11041,7 +11041,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>10.9282522201538</v>
+        <v>10.9282512664795</v>
       </c>
       <c r="H368" t="n">
         <v>481370</v>
@@ -11099,7 +11099,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>10.9030570983887</v>
+        <v>10.903058052063</v>
       </c>
       <c r="H370" t="n">
         <v>687443</v>
@@ -11157,7 +11157,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G372" t="n">
-        <v>10.8967580795288</v>
+        <v>10.8967590332031</v>
       </c>
       <c r="H372" t="n">
         <v>345862</v>
@@ -11215,7 +11215,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G374" t="n">
-        <v>10.8148756027222</v>
+        <v>10.8148746490479</v>
       </c>
       <c r="H374" t="n">
         <v>492979</v>
@@ -11244,7 +11244,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G375" t="n">
-        <v>10.840069770813</v>
+        <v>10.8400707244873</v>
       </c>
       <c r="H375" t="n">
         <v>484837</v>
@@ -11302,7 +11302,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G377" t="n">
-        <v>10.9723424911499</v>
+        <v>10.9723434448242</v>
       </c>
       <c r="H377" t="n">
         <v>433171</v>
@@ -11331,7 +11331,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>10.9282522201538</v>
+        <v>10.9282512664795</v>
       </c>
       <c r="H378" t="n">
         <v>677469</v>
@@ -11418,7 +11418,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G381" t="n">
-        <v>10.7959785461426</v>
+        <v>10.7959794998169</v>
       </c>
       <c r="H381" t="n">
         <v>439358</v>
@@ -11476,7 +11476,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.0101346969604</v>
+        <v>11.0101337432861</v>
       </c>
       <c r="H383" t="n">
         <v>571437</v>
@@ -11505,7 +11505,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G384" t="n">
-        <v>10.840069770813</v>
+        <v>10.8400707244873</v>
       </c>
       <c r="H384" t="n">
         <v>546106</v>
@@ -11563,7 +11563,7 @@
         <v>17</v>
       </c>
       <c r="G386" t="n">
-        <v>10.7077980041504</v>
+        <v>10.7077970504761</v>
       </c>
       <c r="H386" t="n">
         <v>577702</v>
@@ -11592,7 +11592,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>10.5629272460938</v>
+        <v>10.5629281997681</v>
       </c>
       <c r="H387" t="n">
         <v>294918</v>
@@ -11650,7 +11650,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>10.1409139633179</v>
+        <v>10.1409149169922</v>
       </c>
       <c r="H389" t="n">
         <v>1318386</v>
@@ -11679,7 +11679,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G390" t="n">
-        <v>10.0716285705566</v>
+        <v>10.0716276168823</v>
       </c>
       <c r="H390" t="n">
         <v>658861</v>
@@ -11708,7 +11708,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G391" t="n">
-        <v>10.1598100662231</v>
+        <v>10.1598091125488</v>
       </c>
       <c r="H391" t="n">
         <v>804382</v>
@@ -11824,7 +11824,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>10.4873428344727</v>
+        <v>10.4873418807983</v>
       </c>
       <c r="H395" t="n">
         <v>517663</v>
@@ -11853,7 +11853,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>10.4873428344727</v>
+        <v>10.4873418807983</v>
       </c>
       <c r="H396" t="n">
         <v>414782</v>
@@ -11911,7 +11911,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G398" t="n">
-        <v>10.4747457504272</v>
+        <v>10.4747447967529</v>
       </c>
       <c r="H398" t="n">
         <v>401399</v>
@@ -12143,7 +12143,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>10.342472076416</v>
+        <v>10.3424730300903</v>
       </c>
       <c r="H406" t="n">
         <v>677671</v>
@@ -12172,7 +12172,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>10.455849647522</v>
+        <v>10.4558506011963</v>
       </c>
       <c r="H407" t="n">
         <v>564518</v>
@@ -12346,7 +12346,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G413" t="n">
-        <v>10.7959785461426</v>
+        <v>10.7959794998169</v>
       </c>
       <c r="H413" t="n">
         <v>343194</v>
@@ -12375,7 +12375,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>10.5566291809082</v>
+        <v>10.5566282272339</v>
       </c>
       <c r="H414" t="n">
         <v>511632</v>
@@ -12433,7 +12433,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G416" t="n">
-        <v>10.7266941070557</v>
+        <v>10.72669506073</v>
       </c>
       <c r="H416" t="n">
         <v>478602</v>
@@ -12549,7 +12549,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>10.6826009750366</v>
+        <v>10.6826028823853</v>
       </c>
       <c r="H420" t="n">
         <v>545700</v>
@@ -12694,7 +12694,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G425" t="n">
-        <v>9.90786170959473</v>
+        <v>9.90786075592041</v>
       </c>
       <c r="H425" t="n">
         <v>1248740</v>
@@ -12810,7 +12810,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G429" t="n">
-        <v>9.56143283843994</v>
+        <v>9.56143474578857</v>
       </c>
       <c r="H429" t="n">
         <v>597460</v>
@@ -12839,7 +12839,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>9.61182403564453</v>
+        <v>9.61182308197021</v>
       </c>
       <c r="H430" t="n">
         <v>653766</v>
@@ -12868,7 +12868,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G431" t="n">
-        <v>9.72519969940186</v>
+        <v>9.72519874572754</v>
       </c>
       <c r="H431" t="n">
         <v>1613239</v>
@@ -12926,7 +12926,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G433" t="n">
-        <v>9.65591335296631</v>
+        <v>9.65591430664062</v>
       </c>
       <c r="H433" t="n">
         <v>676114</v>
@@ -13129,7 +13129,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G440" t="n">
-        <v>9.11422538757324</v>
+        <v>9.11422443389893</v>
       </c>
       <c r="H440" t="n">
         <v>1161398</v>
@@ -13216,7 +13216,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G443" t="n">
-        <v>9.17091369628906</v>
+        <v>9.17091274261475</v>
       </c>
       <c r="H443" t="n">
         <v>681613</v>
@@ -13419,7 +13419,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G450" t="n">
-        <v>9.17091369628906</v>
+        <v>9.17091274261475</v>
       </c>
       <c r="H450" t="n">
         <v>456475</v>
@@ -13622,7 +13622,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G457" t="n">
-        <v>9.85117340087891</v>
+        <v>9.85117435455322</v>
       </c>
       <c r="H457" t="n">
         <v>1175865</v>
@@ -13651,7 +13651,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G458" t="n">
-        <v>10.0401344299316</v>
+        <v>10.040135383606</v>
       </c>
       <c r="H458" t="n">
         <v>1416943</v>
@@ -13738,7 +13738,7 @@
         <v>15.5</v>
       </c>
       <c r="G461" t="n">
-        <v>9.7629919052124</v>
+        <v>9.76299285888672</v>
       </c>
       <c r="H461" t="n">
         <v>717280</v>
@@ -13883,7 +13883,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G466" t="n">
-        <v>9.61812114715576</v>
+        <v>9.61812210083008</v>
       </c>
       <c r="H466" t="n">
         <v>1703293</v>
@@ -13999,7 +13999,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G470" t="n">
-        <v>9.93305683135986</v>
+        <v>9.93305778503418</v>
       </c>
       <c r="H470" t="n">
         <v>1990808</v>
@@ -14144,7 +14144,7 @@
         <v>15.25</v>
       </c>
       <c r="G475" t="n">
-        <v>9.60552501678467</v>
+        <v>9.60552406311035</v>
       </c>
       <c r="H475" t="n">
         <v>1091996</v>
@@ -14347,7 +14347,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G482" t="n">
-        <v>9.25279712677002</v>
+        <v>9.2527961730957</v>
       </c>
       <c r="H482" t="n">
         <v>583745</v>
@@ -14376,7 +14376,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>9.26539516448975</v>
+        <v>9.26539325714111</v>
       </c>
       <c r="H483" t="n">
         <v>804106</v>
@@ -14405,7 +14405,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G484" t="n">
-        <v>9.65591335296631</v>
+        <v>9.65591430664062</v>
       </c>
       <c r="H484" t="n">
         <v>2270255</v>
@@ -14434,7 +14434,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G485" t="n">
-        <v>9.61182403564453</v>
+        <v>9.61182308197021</v>
       </c>
       <c r="H485" t="n">
         <v>1125880</v>
@@ -14463,7 +14463,7 @@
         <v>15.25</v>
       </c>
       <c r="G486" t="n">
-        <v>9.60552501678467</v>
+        <v>9.60552406311035</v>
       </c>
       <c r="H486" t="n">
         <v>593843</v>
@@ -14521,7 +14521,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G488" t="n">
-        <v>10.0842256546021</v>
+        <v>10.0842266082764</v>
       </c>
       <c r="H488" t="n">
         <v>4395102</v>
@@ -14695,7 +14695,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G494" t="n">
-        <v>9.97084808349609</v>
+        <v>9.97084903717041</v>
       </c>
       <c r="H494" t="n">
         <v>646869</v>
@@ -14753,7 +14753,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>10.1724081039429</v>
+        <v>10.1724071502686</v>
       </c>
       <c r="H496" t="n">
         <v>1387530</v>
@@ -14869,7 +14869,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G500" t="n">
-        <v>10.5566291809082</v>
+        <v>10.5566282272339</v>
       </c>
       <c r="H500" t="n">
         <v>1405049</v>
@@ -14956,7 +14956,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G503" t="n">
-        <v>10.342472076416</v>
+        <v>10.3424730300903</v>
       </c>
       <c r="H503" t="n">
         <v>1295184</v>
@@ -14985,7 +14985,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G504" t="n">
-        <v>10.0968236923218</v>
+        <v>10.0968246459961</v>
       </c>
       <c r="H504" t="n">
         <v>1554916</v>
@@ -15014,7 +15014,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G505" t="n">
-        <v>10.1850061416626</v>
+        <v>10.185004234314</v>
       </c>
       <c r="H505" t="n">
         <v>670433</v>
@@ -15159,7 +15159,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G510" t="n">
-        <v>10.1850061416626</v>
+        <v>10.185004234314</v>
       </c>
       <c r="H510" t="n">
         <v>407999</v>
@@ -15188,7 +15188,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>10.1724081039429</v>
+        <v>10.1724071502686</v>
       </c>
       <c r="H511" t="n">
         <v>297422</v>
@@ -15246,7 +15246,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G513" t="n">
-        <v>10.4369525909424</v>
+        <v>10.4369535446167</v>
       </c>
       <c r="H513" t="n">
         <v>1589907</v>
@@ -15275,7 +15275,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>10.5188360214233</v>
+        <v>10.5188369750977</v>
       </c>
       <c r="H514" t="n">
         <v>829466</v>
@@ -15333,7 +15333,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G516" t="n">
-        <v>10.5188360214233</v>
+        <v>10.5188369750977</v>
       </c>
       <c r="H516" t="n">
         <v>716291</v>
@@ -15362,7 +15362,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G517" t="n">
-        <v>10.4306545257568</v>
+        <v>10.4306535720825</v>
       </c>
       <c r="H517" t="n">
         <v>693437</v>
@@ -15478,7 +15478,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G521" t="n">
-        <v>10.2668876647949</v>
+        <v>10.2668867111206</v>
       </c>
       <c r="H521" t="n">
         <v>725578</v>
@@ -15507,7 +15507,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G522" t="n">
-        <v>10.2605905532837</v>
+        <v>10.260591506958</v>
       </c>
       <c r="H522" t="n">
         <v>668306</v>
@@ -15623,7 +15623,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G526" t="n">
-        <v>10.3865633010864</v>
+        <v>10.3865623474121</v>
       </c>
       <c r="H526" t="n">
         <v>5455851</v>
@@ -15826,7 +15826,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>10.0842256546021</v>
+        <v>10.0842266082764</v>
       </c>
       <c r="H533" t="n">
         <v>799128</v>
@@ -15855,7 +15855,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G534" t="n">
-        <v>10.0401344299316</v>
+        <v>10.040135383606</v>
       </c>
       <c r="H534" t="n">
         <v>742592</v>
@@ -15884,7 +15884,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G535" t="n">
-        <v>9.84487533569336</v>
+        <v>9.84487438201904</v>
       </c>
       <c r="H535" t="n">
         <v>936865</v>
@@ -15942,7 +15942,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G537" t="n">
-        <v>9.55513572692871</v>
+        <v>9.55513477325439</v>
       </c>
       <c r="H537" t="n">
         <v>1474450</v>
@@ -16000,7 +16000,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G539" t="n">
-        <v>9.68110847473145</v>
+        <v>9.68110942840576</v>
       </c>
       <c r="H539" t="n">
         <v>949531</v>
@@ -16058,7 +16058,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>9.75669384002686</v>
+        <v>9.75669288635254</v>
       </c>
       <c r="H541" t="n">
         <v>729219</v>
@@ -16261,7 +16261,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G548" t="n">
-        <v>9.92675876617432</v>
+        <v>9.9267578125</v>
       </c>
       <c r="H548" t="n">
         <v>495278</v>
@@ -16290,7 +16290,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G549" t="n">
-        <v>9.95195388793945</v>
+        <v>9.95195293426514</v>
       </c>
       <c r="H549" t="n">
         <v>419034</v>
@@ -16348,7 +16348,7 @@
         <v>15.7349996566772</v>
       </c>
       <c r="G551" t="n">
-        <v>9.91101169586182</v>
+        <v>9.9110107421875</v>
       </c>
       <c r="H551" t="n">
         <v>461637</v>
@@ -16377,7 +16377,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G552" t="n">
-        <v>9.98659610748291</v>
+        <v>9.98659515380859</v>
       </c>
       <c r="H552" t="n">
         <v>1407444</v>
@@ -16406,7 +16406,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G553" t="n">
-        <v>10.1283178329468</v>
+        <v>10.1283168792725</v>
       </c>
       <c r="H553" t="n">
         <v>542147</v>
@@ -16435,7 +16435,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G554" t="n">
-        <v>9.99604320526123</v>
+        <v>9.99604415893555</v>
       </c>
       <c r="H554" t="n">
         <v>540965</v>
@@ -16464,7 +16464,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>9.79448413848877</v>
+        <v>9.79448509216309</v>
       </c>
       <c r="H555" t="n">
         <v>647195</v>
@@ -16493,7 +16493,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G556" t="n">
-        <v>9.25279712677002</v>
+        <v>9.2527961730957</v>
       </c>
       <c r="H556" t="n">
         <v>3331063</v>
@@ -16551,7 +16551,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G558" t="n">
-        <v>9.62441921234131</v>
+        <v>9.62442016601562</v>
       </c>
       <c r="H558" t="n">
         <v>793641</v>
@@ -16580,7 +16580,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G559" t="n">
-        <v>10.5125370025635</v>
+        <v>10.5125379562378</v>
       </c>
       <c r="H559" t="n">
         <v>4218694</v>
@@ -16638,7 +16638,7 @@
         <v>16.4050006866455</v>
       </c>
       <c r="G561" t="n">
-        <v>10.3330249786377</v>
+        <v>10.3330240249634</v>
       </c>
       <c r="H561" t="n">
         <v>1564944</v>
@@ -16696,7 +16696,7 @@
         <v>15.4250001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>9.71575164794922</v>
+        <v>9.71575260162354</v>
       </c>
       <c r="H563" t="n">
         <v>1198414</v>
@@ -16725,7 +16725,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G564" t="n">
-        <v>9.78818702697754</v>
+        <v>9.78818511962891</v>
       </c>
       <c r="H564" t="n">
         <v>678905</v>
@@ -16754,7 +16754,7 @@
         <v>15.4449996948242</v>
       </c>
       <c r="G565" t="n">
-        <v>9.72834968566895</v>
+        <v>9.72834873199463</v>
       </c>
       <c r="H565" t="n">
         <v>801840</v>
@@ -16783,7 +16783,7 @@
         <v>15.5</v>
       </c>
       <c r="G566" t="n">
-        <v>9.7629919052124</v>
+        <v>9.76299285888672</v>
       </c>
       <c r="H566" t="n">
         <v>615304</v>
@@ -16986,7 +16986,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G573" t="n">
-        <v>9.49844741821289</v>
+        <v>9.49844646453857</v>
       </c>
       <c r="H573" t="n">
         <v>706004</v>
@@ -17044,7 +17044,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G575" t="n">
-        <v>10.4306545257568</v>
+        <v>10.4306535720825</v>
       </c>
       <c r="H575" t="n">
         <v>6151477</v>
@@ -17160,7 +17160,7 @@
         <v>16.4850006103516</v>
       </c>
       <c r="G579" t="n">
-        <v>10.383415222168</v>
+        <v>10.3834142684937</v>
       </c>
       <c r="H579" t="n">
         <v>551762</v>
@@ -17218,7 +17218,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G581" t="n">
-        <v>10.2290954589844</v>
+        <v>10.2290945053101</v>
       </c>
       <c r="H581" t="n">
         <v>1139633</v>
@@ -17363,7 +17363,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G586" t="n">
-        <v>10.3708171844482</v>
+        <v>10.3708162307739</v>
       </c>
       <c r="H586" t="n">
         <v>592387</v>
@@ -17421,7 +17421,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G588" t="n">
-        <v>10.3739652633667</v>
+        <v>10.373966217041</v>
       </c>
       <c r="H588" t="n">
         <v>434421</v>
@@ -17450,7 +17450,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>10.4275054931641</v>
+        <v>10.4275045394897</v>
       </c>
       <c r="H589" t="n">
         <v>599454</v>
@@ -17537,7 +17537,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G592" t="n">
-        <v>10.5629272460938</v>
+        <v>10.5629281997681</v>
       </c>
       <c r="H592" t="n">
         <v>2494187</v>
@@ -17595,7 +17595,7 @@
         <v>16.4750003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>10.3771152496338</v>
+        <v>10.3771162033081</v>
       </c>
       <c r="H594" t="n">
         <v>837505</v>
@@ -17624,7 +17624,7 @@
         <v>16.5450000762939</v>
       </c>
       <c r="G595" t="n">
-        <v>10.4212064743042</v>
+        <v>10.4212074279785</v>
       </c>
       <c r="H595" t="n">
         <v>848180</v>
@@ -17682,7 +17682,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G597" t="n">
-        <v>10.6196165084839</v>
+        <v>10.6196174621582</v>
       </c>
       <c r="H597" t="n">
         <v>1593073</v>
@@ -17711,7 +17711,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G598" t="n">
-        <v>10.6448106765747</v>
+        <v>10.6448097229004</v>
       </c>
       <c r="H598" t="n">
         <v>854131</v>
@@ -17740,7 +17740,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G599" t="n">
-        <v>10.3739652633667</v>
+        <v>10.373966217041</v>
       </c>
       <c r="H599" t="n">
         <v>1195020</v>
@@ -17798,7 +17798,7 @@
         <v>16.3349990844727</v>
       </c>
       <c r="G601" t="n">
-        <v>10.2889337539673</v>
+        <v>10.288932800293</v>
       </c>
       <c r="H601" t="n">
         <v>665558</v>
@@ -17856,7 +17856,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>10.455849647522</v>
+        <v>10.4558506011963</v>
       </c>
       <c r="H603" t="n">
         <v>595792</v>
@@ -17885,7 +17885,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G604" t="n">
-        <v>10.4369525909424</v>
+        <v>10.4369535446167</v>
       </c>
       <c r="H604" t="n">
         <v>639974</v>
@@ -17972,7 +17972,7 @@
         <v>15.1949996948242</v>
       </c>
       <c r="G607" t="n">
-        <v>9.57088184356689</v>
+        <v>9.57088088989258</v>
       </c>
       <c r="H607" t="n">
         <v>968708</v>
@@ -18001,7 +18001,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G608" t="n">
-        <v>9.61182403564453</v>
+        <v>9.61182308197021</v>
       </c>
       <c r="H608" t="n">
         <v>623141</v>
@@ -18030,7 +18030,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G609" t="n">
-        <v>9.61182403564453</v>
+        <v>9.61182308197021</v>
       </c>
       <c r="H609" t="n">
         <v>567987</v>
@@ -18146,7 +18146,7 @@
         <v>14.5550003051758</v>
       </c>
       <c r="G613" t="n">
-        <v>9.16776466369629</v>
+        <v>9.16776371002197</v>
       </c>
       <c r="H613" t="n">
         <v>711444</v>
@@ -18407,7 +18407,7 @@
         <v>14</v>
       </c>
       <c r="G622" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H622" t="n">
         <v>544006</v>
@@ -18523,7 +18523,7 @@
         <v>14.3649997711182</v>
       </c>
       <c r="G626" t="n">
-        <v>9.04808902740479</v>
+        <v>9.04808807373047</v>
       </c>
       <c r="H626" t="n">
         <v>303853</v>
@@ -18552,7 +18552,7 @@
         <v>14.2550001144409</v>
       </c>
       <c r="G627" t="n">
-        <v>8.97880363464355</v>
+        <v>8.97880458831787</v>
       </c>
       <c r="H627" t="n">
         <v>611734</v>
@@ -18581,7 +18581,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>9.00714778900146</v>
+        <v>9.00714683532715</v>
       </c>
       <c r="H628" t="n">
         <v>381465</v>
@@ -18610,7 +18610,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G629" t="n">
-        <v>9.00714778900146</v>
+        <v>9.00714683532715</v>
       </c>
       <c r="H629" t="n">
         <v>704717</v>
@@ -18784,7 +18784,7 @@
         <v>14.375</v>
       </c>
       <c r="G635" t="n">
-        <v>9.05438804626465</v>
+        <v>9.05438709259033</v>
       </c>
       <c r="H635" t="n">
         <v>852977</v>
@@ -18813,7 +18813,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G636" t="n">
-        <v>9.04179000854492</v>
+        <v>9.04179096221924</v>
       </c>
       <c r="H636" t="n">
         <v>817333</v>
@@ -18842,7 +18842,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G637" t="n">
-        <v>8.62922477722168</v>
+        <v>8.62922382354736</v>
       </c>
       <c r="H637" t="n">
         <v>2494268</v>
@@ -18871,7 +18871,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G638" t="n">
-        <v>8.31429004669189</v>
+        <v>8.31428909301758</v>
       </c>
       <c r="H638" t="n">
         <v>1435283</v>
@@ -19016,7 +19016,7 @@
         <v>13.6549997329712</v>
       </c>
       <c r="G643" t="n">
-        <v>8.60087966918945</v>
+        <v>8.60088062286377</v>
       </c>
       <c r="H643" t="n">
         <v>796217</v>
@@ -19132,7 +19132,7 @@
         <v>13.7650003433228</v>
       </c>
       <c r="G647" t="n">
-        <v>8.67016696929932</v>
+        <v>8.670166015625</v>
       </c>
       <c r="H647" t="n">
         <v>380312</v>
@@ -19161,7 +19161,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G648" t="n">
-        <v>8.59773063659668</v>
+        <v>8.597731590271</v>
       </c>
       <c r="H648" t="n">
         <v>381823</v>
@@ -19277,7 +19277,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>8.79929065704346</v>
+        <v>8.79928970336914</v>
       </c>
       <c r="H652" t="n">
         <v>490461</v>
@@ -19393,7 +19393,7 @@
         <v>14</v>
       </c>
       <c r="G656" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H656" t="n">
         <v>370469</v>
@@ -19422,7 +19422,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>9.10162734985352</v>
+        <v>9.10162830352783</v>
       </c>
       <c r="H657" t="n">
         <v>762491</v>
@@ -19451,7 +19451,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G658" t="n">
-        <v>9.04493808746338</v>
+        <v>9.0449390411377</v>
       </c>
       <c r="H658" t="n">
         <v>2360024</v>
@@ -19480,7 +19480,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G659" t="n">
-        <v>9.14256954193115</v>
+        <v>9.14257049560547</v>
       </c>
       <c r="H659" t="n">
         <v>567304</v>
@@ -19509,7 +19509,7 @@
         <v>14.375</v>
       </c>
       <c r="G660" t="n">
-        <v>9.05438804626465</v>
+        <v>9.05438709259033</v>
       </c>
       <c r="H660" t="n">
         <v>286353</v>
@@ -19538,7 +19538,7 @@
         <v>14</v>
       </c>
       <c r="G661" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H661" t="n">
         <v>497999</v>
@@ -19596,7 +19596,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G663" t="n">
-        <v>8.82133674621582</v>
+        <v>8.8213357925415</v>
       </c>
       <c r="H663" t="n">
         <v>226667</v>
@@ -19654,7 +19654,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G665" t="n">
-        <v>8.98195266723633</v>
+        <v>8.98195362091064</v>
       </c>
       <c r="H665" t="n">
         <v>370059</v>
@@ -19741,7 +19741,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G668" t="n">
-        <v>8.7174072265625</v>
+        <v>8.71740627288818</v>
       </c>
       <c r="H668" t="n">
         <v>211818</v>
@@ -19770,7 +19770,7 @@
         <v>13.0450000762939</v>
       </c>
       <c r="G669" t="n">
-        <v>8.21666049957275</v>
+        <v>8.21665954589844</v>
       </c>
       <c r="H669" t="n">
         <v>1280841</v>
@@ -19886,7 +19886,7 @@
         <v>13.4750003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>8.48750400543213</v>
+        <v>8.48750495910645</v>
       </c>
       <c r="H673" t="n">
         <v>769111</v>
@@ -19944,7 +19944,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G675" t="n">
-        <v>8.33948421478271</v>
+        <v>8.33948516845703</v>
       </c>
       <c r="H675" t="n">
         <v>277983</v>
@@ -20002,7 +20002,7 @@
         <v>13.3249998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>8.39302444458008</v>
+        <v>8.39302349090576</v>
       </c>
       <c r="H677" t="n">
         <v>327923</v>
@@ -20060,7 +20060,7 @@
         <v>13.1850004196167</v>
       </c>
       <c r="G679" t="n">
-        <v>8.30484294891357</v>
+        <v>8.30484199523926</v>
       </c>
       <c r="H679" t="n">
         <v>214197</v>
@@ -20176,7 +20176,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G683" t="n">
-        <v>7.80724430084229</v>
+        <v>7.80724477767944</v>
       </c>
       <c r="H683" t="n">
         <v>796554</v>
@@ -20205,7 +20205,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>7.78519821166992</v>
+        <v>7.78519868850708</v>
       </c>
       <c r="H684" t="n">
         <v>1126358</v>
@@ -20234,7 +20234,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G685" t="n">
-        <v>7.7537055015564</v>
+        <v>7.75370502471924</v>
       </c>
       <c r="H685" t="n">
         <v>319739</v>
@@ -20263,7 +20263,7 @@
         <v>12.3249998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>7.76315355300903</v>
+        <v>7.76315259933472</v>
       </c>
       <c r="H686" t="n">
         <v>305034</v>
@@ -20321,7 +20321,7 @@
         <v>12.4849996566772</v>
       </c>
       <c r="G688" t="n">
-        <v>7.86393165588379</v>
+        <v>7.86393213272095</v>
       </c>
       <c r="H688" t="n">
         <v>883562</v>
@@ -20379,7 +20379,7 @@
         <v>12.6549997329712</v>
       </c>
       <c r="G690" t="n">
-        <v>7.97101020812988</v>
+        <v>7.9710111618042</v>
       </c>
       <c r="H690" t="n">
         <v>605862</v>
@@ -20495,7 +20495,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G694" t="n">
-        <v>8.25130367279053</v>
+        <v>8.25130271911621</v>
       </c>
       <c r="H694" t="n">
         <v>486143</v>
@@ -20524,7 +20524,7 @@
         <v>13.0249996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>8.20406150817871</v>
+        <v>8.20406246185303</v>
       </c>
       <c r="H695" t="n">
         <v>604172</v>
@@ -20553,7 +20553,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G696" t="n">
-        <v>8.25760173797607</v>
+        <v>8.25760078430176</v>
       </c>
       <c r="H696" t="n">
         <v>613406</v>
@@ -20582,7 +20582,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G697" t="n">
-        <v>8.26390075683594</v>
+        <v>8.26389980316162</v>
       </c>
       <c r="H697" t="n">
         <v>359749</v>
@@ -20669,7 +20669,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G700" t="n">
-        <v>8.76149749755859</v>
+        <v>8.76149845123291</v>
       </c>
       <c r="H700" t="n">
         <v>856266</v>
@@ -20698,7 +20698,7 @@
         <v>13.4549999237061</v>
       </c>
       <c r="G701" t="n">
-        <v>8.47490692138672</v>
+        <v>8.4749059677124</v>
       </c>
       <c r="H701" t="n">
         <v>979868</v>
@@ -20727,7 +20727,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G702" t="n">
-        <v>8.47805500030518</v>
+        <v>8.47805595397949</v>
       </c>
       <c r="H702" t="n">
         <v>566976</v>
@@ -20785,7 +20785,7 @@
         <v>13.7550001144409</v>
       </c>
       <c r="G704" t="n">
-        <v>8.66386699676514</v>
+        <v>8.66386795043945</v>
       </c>
       <c r="H704" t="n">
         <v>626939</v>
@@ -20872,7 +20872,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G707" t="n">
-        <v>8.4182186126709</v>
+        <v>8.41821765899658</v>
       </c>
       <c r="H707" t="n">
         <v>318606</v>
@@ -20901,7 +20901,7 @@
         <v>13.4449996948242</v>
       </c>
       <c r="G708" t="n">
-        <v>8.46860790252686</v>
+        <v>8.46860694885254</v>
       </c>
       <c r="H708" t="n">
         <v>322604</v>
@@ -20930,7 +20930,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G709" t="n">
-        <v>8.48435592651367</v>
+        <v>8.48435497283936</v>
       </c>
       <c r="H709" t="n">
         <v>638261</v>
@@ -21017,7 +21017,7 @@
         <v>13.1850004196167</v>
       </c>
       <c r="G712" t="n">
-        <v>8.30484294891357</v>
+        <v>8.30484199523926</v>
       </c>
       <c r="H712" t="n">
         <v>331373</v>
@@ -21046,7 +21046,7 @@
         <v>13.6350002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>8.58828449249268</v>
+        <v>8.58828353881836</v>
       </c>
       <c r="H713" t="n">
         <v>379575</v>
@@ -21162,7 +21162,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G717" t="n">
-        <v>8.08753681182861</v>
+        <v>8.0875358581543</v>
       </c>
       <c r="H717" t="n">
         <v>381415</v>
@@ -21220,7 +21220,7 @@
         <v>12.75</v>
       </c>
       <c r="G719" t="n">
-        <v>8.03084945678711</v>
+        <v>8.03084850311279</v>
       </c>
       <c r="H719" t="n">
         <v>443428</v>
@@ -21249,7 +21249,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G720" t="n">
-        <v>7.97415971755981</v>
+        <v>7.97415924072266</v>
       </c>
       <c r="H720" t="n">
         <v>657554</v>
@@ -21278,7 +21278,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G721" t="n">
-        <v>7.81039381027222</v>
+        <v>7.8103928565979</v>
       </c>
       <c r="H721" t="n">
         <v>284353</v>
@@ -21307,7 +21307,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G722" t="n">
-        <v>8.1190299987793</v>
+        <v>8.11903095245361</v>
       </c>
       <c r="H722" t="n">
         <v>419518</v>
@@ -21365,7 +21365,7 @@
         <v>13.3050003051758</v>
       </c>
       <c r="G724" t="n">
-        <v>8.38042545318604</v>
+        <v>8.38042640686035</v>
       </c>
       <c r="H724" t="n">
         <v>419726</v>
@@ -21394,7 +21394,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G725" t="n">
-        <v>8.74575138092041</v>
+        <v>8.74575042724609</v>
       </c>
       <c r="H725" t="n">
         <v>1012073</v>
@@ -21481,7 +21481,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>8.9441614151001</v>
+        <v>8.94416046142578</v>
       </c>
       <c r="H728" t="n">
         <v>1287681</v>
@@ -21510,7 +21510,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G729" t="n">
-        <v>8.90636825561523</v>
+        <v>8.90636730194092</v>
       </c>
       <c r="H729" t="n">
         <v>490390</v>
@@ -21597,7 +21597,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G732" t="n">
-        <v>8.31429004669189</v>
+        <v>8.31428909301758</v>
       </c>
       <c r="H732" t="n">
         <v>477706</v>
@@ -21626,7 +21626,7 @@
         <v>13.3050003051758</v>
       </c>
       <c r="G733" t="n">
-        <v>8.38042545318604</v>
+        <v>8.38042640686035</v>
       </c>
       <c r="H733" t="n">
         <v>359929</v>
@@ -21713,7 +21713,7 @@
         <v>12.4650001525879</v>
       </c>
       <c r="G736" t="n">
-        <v>7.85133504867554</v>
+        <v>7.8513355255127</v>
       </c>
       <c r="H736" t="n">
         <v>679998</v>
@@ -21742,7 +21742,7 @@
         <v>12.4350004196167</v>
       </c>
       <c r="G737" t="n">
-        <v>7.83243942260742</v>
+        <v>7.83243846893311</v>
       </c>
       <c r="H737" t="n">
         <v>437725</v>
@@ -21771,7 +21771,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G738" t="n">
-        <v>7.76000308990479</v>
+        <v>7.7600040435791</v>
       </c>
       <c r="H738" t="n">
         <v>563615</v>
@@ -21800,7 +21800,7 @@
         <v>12.6750001907349</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98360729217529</v>
+        <v>7.98360776901245</v>
       </c>
       <c r="H739" t="n">
         <v>833312</v>
@@ -21887,7 +21887,7 @@
         <v>13.3450002670288</v>
       </c>
       <c r="G742" t="n">
-        <v>8.40562152862549</v>
+        <v>8.40562057495117</v>
       </c>
       <c r="H742" t="n">
         <v>710755</v>
@@ -21945,7 +21945,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G744" t="n">
-        <v>8.59773063659668</v>
+        <v>8.597731590271</v>
       </c>
       <c r="H744" t="n">
         <v>620781</v>
@@ -22090,7 +22090,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G749" t="n">
-        <v>8.54734230041504</v>
+        <v>8.54734134674072</v>
       </c>
       <c r="H749" t="n">
         <v>430004</v>
@@ -22206,7 +22206,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G753" t="n">
-        <v>7.80724430084229</v>
+        <v>7.80724477767944</v>
       </c>
       <c r="H753" t="n">
         <v>912803</v>
@@ -22235,7 +22235,7 @@
         <v>12.7950000762939</v>
       </c>
       <c r="G754" t="n">
-        <v>8.05919170379639</v>
+        <v>8.0591926574707</v>
       </c>
       <c r="H754" t="n">
         <v>1011896</v>
@@ -22264,7 +22264,7 @@
         <v>12.75</v>
       </c>
       <c r="G755" t="n">
-        <v>8.03084945678711</v>
+        <v>8.03084850311279</v>
       </c>
       <c r="H755" t="n">
         <v>582759</v>
@@ -22351,7 +22351,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G758" t="n">
-        <v>8.23870468139648</v>
+        <v>8.2387056350708</v>
       </c>
       <c r="H758" t="n">
         <v>1184986</v>
@@ -22496,7 +22496,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G763" t="n">
-        <v>8.64182186126709</v>
+        <v>8.64182281494141</v>
       </c>
       <c r="H763" t="n">
         <v>1520852</v>
@@ -22641,7 +22641,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G768" t="n">
-        <v>8.64182186126709</v>
+        <v>8.64182281494141</v>
       </c>
       <c r="H768" t="n">
         <v>498393</v>
@@ -22670,7 +22670,7 @@
         <v>14</v>
       </c>
       <c r="G769" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H769" t="n">
         <v>564898</v>
@@ -22815,7 +22815,7 @@
         <v>14.7049999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>9.26224517822266</v>
+        <v>9.26224613189697</v>
       </c>
       <c r="H774" t="n">
         <v>591794</v>
@@ -22902,7 +22902,7 @@
         <v>14.375</v>
       </c>
       <c r="G777" t="n">
-        <v>9.05438804626465</v>
+        <v>9.05438709259033</v>
       </c>
       <c r="H777" t="n">
         <v>284820</v>
@@ -22960,7 +22960,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G779" t="n">
-        <v>8.86227703094482</v>
+        <v>8.86227798461914</v>
       </c>
       <c r="H779" t="n">
         <v>194933</v>
@@ -22989,7 +22989,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>9.03864097595215</v>
+        <v>9.03864192962646</v>
       </c>
       <c r="H780" t="n">
         <v>293855</v>
@@ -23076,7 +23076,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G783" t="n">
-        <v>9.25279712677002</v>
+        <v>9.2527961730957</v>
       </c>
       <c r="H783" t="n">
         <v>254918</v>
@@ -23134,7 +23134,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>9.03864097595215</v>
+        <v>9.03864192962646</v>
       </c>
       <c r="H785" t="n">
         <v>613922</v>
@@ -23163,7 +23163,7 @@
         <v>14.0649995803833</v>
       </c>
       <c r="G786" t="n">
-        <v>8.85912704467773</v>
+        <v>8.85912799835205</v>
       </c>
       <c r="H786" t="n">
         <v>731969</v>
@@ -23279,7 +23279,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G790" t="n">
-        <v>8.25130367279053</v>
+        <v>8.25130271911621</v>
       </c>
       <c r="H790" t="n">
         <v>838698</v>
@@ -23337,7 +23337,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G792" t="n">
-        <v>8.19776344299316</v>
+        <v>8.19776439666748</v>
       </c>
       <c r="H792" t="n">
         <v>464255</v>
@@ -23366,7 +23366,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G793" t="n">
-        <v>8.26390075683594</v>
+        <v>8.26389980316162</v>
       </c>
       <c r="H793" t="n">
         <v>360903</v>
@@ -23395,7 +23395,7 @@
         <v>13.1850004196167</v>
       </c>
       <c r="G794" t="n">
-        <v>8.30484294891357</v>
+        <v>8.30484199523926</v>
       </c>
       <c r="H794" t="n">
         <v>616464</v>
@@ -23424,7 +23424,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G795" t="n">
-        <v>8.26390075683594</v>
+        <v>8.26389980316162</v>
       </c>
       <c r="H795" t="n">
         <v>216214</v>
@@ -23482,7 +23482,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>8.56623840332031</v>
+        <v>8.566237449646</v>
       </c>
       <c r="H797" t="n">
         <v>791956</v>
@@ -23511,7 +23511,7 @@
         <v>13.8599996566772</v>
       </c>
       <c r="G798" t="n">
-        <v>8.73000526428223</v>
+        <v>8.73000431060791</v>
       </c>
       <c r="H798" t="n">
         <v>714255</v>
@@ -23569,7 +23569,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G800" t="n">
-        <v>8.95045948028564</v>
+        <v>8.95045852661133</v>
       </c>
       <c r="H800" t="n">
         <v>261342</v>
@@ -23598,7 +23598,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G801" t="n">
-        <v>8.95045948028564</v>
+        <v>8.95045852661133</v>
       </c>
       <c r="H801" t="n">
         <v>216635</v>
@@ -23627,7 +23627,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G802" t="n">
-        <v>8.95045948028564</v>
+        <v>8.95045852661133</v>
       </c>
       <c r="H802" t="n">
         <v>144113</v>
@@ -23714,7 +23714,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G805" t="n">
-        <v>8.81188678741455</v>
+        <v>8.81188774108887</v>
       </c>
       <c r="H805" t="n">
         <v>262013</v>
@@ -23743,7 +23743,7 @@
         <v>14</v>
       </c>
       <c r="G806" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H806" t="n">
         <v>485818</v>
@@ -23772,7 +23772,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G807" t="n">
-        <v>8.79929065704346</v>
+        <v>8.79928970336914</v>
       </c>
       <c r="H807" t="n">
         <v>230612</v>
@@ -23801,7 +23801,7 @@
         <v>14</v>
       </c>
       <c r="G808" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H808" t="n">
         <v>151357</v>
@@ -24091,7 +24091,7 @@
         <v>14.2749996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>8.99140071868896</v>
+        <v>8.99139976501465</v>
       </c>
       <c r="H818" t="n">
         <v>469208</v>
@@ -24149,7 +24149,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G820" t="n">
-        <v>8.86857604980469</v>
+        <v>8.86857509613037</v>
       </c>
       <c r="H820" t="n">
         <v>281882</v>
@@ -24207,7 +24207,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G822" t="n">
-        <v>8.61032867431641</v>
+        <v>8.61032962799072</v>
       </c>
       <c r="H822" t="n">
         <v>228894</v>
@@ -24294,7 +24294,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G825" t="n">
-        <v>8.54104328155518</v>
+        <v>8.54104423522949</v>
       </c>
       <c r="H825" t="n">
         <v>206352</v>
@@ -24410,7 +24410,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G829" t="n">
-        <v>8.87487316131592</v>
+        <v>8.87487411499023</v>
       </c>
       <c r="H829" t="n">
         <v>888470</v>
@@ -24468,7 +24468,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G831" t="n">
-        <v>8.837082862854</v>
+        <v>8.83708190917969</v>
       </c>
       <c r="H831" t="n">
         <v>205813</v>
@@ -24497,7 +24497,7 @@
         <v>13.9449996948242</v>
       </c>
       <c r="G832" t="n">
-        <v>8.78354263305664</v>
+        <v>8.78354358673096</v>
       </c>
       <c r="H832" t="n">
         <v>204787</v>
@@ -24526,7 +24526,7 @@
         <v>13.8050003051758</v>
       </c>
       <c r="G833" t="n">
-        <v>8.69536209106445</v>
+        <v>8.69536113739014</v>
       </c>
       <c r="H833" t="n">
         <v>443038</v>
@@ -24555,7 +24555,7 @@
         <v>13.6549997329712</v>
       </c>
       <c r="G834" t="n">
-        <v>8.60087966918945</v>
+        <v>8.60088062286377</v>
       </c>
       <c r="H834" t="n">
         <v>221615</v>
@@ -24700,7 +24700,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G839" t="n">
-        <v>8.837082862854</v>
+        <v>8.83708190917969</v>
       </c>
       <c r="H839" t="n">
         <v>301128</v>
@@ -24845,7 +24845,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G844" t="n">
-        <v>9.16146659851074</v>
+        <v>9.16146564483643</v>
       </c>
       <c r="H844" t="n">
         <v>268113</v>
@@ -24874,7 +24874,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G845" t="n">
-        <v>9.21815490722656</v>
+        <v>9.21815395355225</v>
       </c>
       <c r="H845" t="n">
         <v>210117</v>
@@ -24903,7 +24903,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G846" t="n">
-        <v>9.33467864990234</v>
+        <v>9.33467960357666</v>
       </c>
       <c r="H846" t="n">
         <v>802169</v>
@@ -24932,7 +24932,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G847" t="n">
-        <v>9.32208347320557</v>
+        <v>9.32208251953125</v>
       </c>
       <c r="H847" t="n">
         <v>257899</v>
@@ -24961,7 +24961,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G848" t="n">
-        <v>9.34097862243652</v>
+        <v>9.34097957611084</v>
       </c>
       <c r="H848" t="n">
         <v>260893</v>
@@ -25048,7 +25048,7 @@
         <v>14.6350002288818</v>
       </c>
       <c r="G851" t="n">
-        <v>9.21815490722656</v>
+        <v>9.21815395355225</v>
       </c>
       <c r="H851" t="n">
         <v>225993</v>
@@ -25135,7 +25135,7 @@
         <v>14.0249996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>8.83393287658691</v>
+        <v>8.8339319229126</v>
       </c>
       <c r="H854" t="n">
         <v>338352</v>
@@ -25164,7 +25164,7 @@
         <v>14</v>
       </c>
       <c r="G855" t="n">
-        <v>8.81818580627441</v>
+        <v>8.81818675994873</v>
       </c>
       <c r="H855" t="n">
         <v>245270</v>
@@ -25251,7 +25251,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G858" t="n">
-        <v>8.89377117156982</v>
+        <v>8.89377021789551</v>
       </c>
       <c r="H858" t="n">
         <v>161027</v>
@@ -25309,7 +25309,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G860" t="n">
-        <v>8.86227703094482</v>
+        <v>8.86227798461914</v>
       </c>
       <c r="H860" t="n">
         <v>202222</v>
@@ -25338,7 +25338,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>8.70795917510986</v>
+        <v>8.70795822143555</v>
       </c>
       <c r="H861" t="n">
         <v>184636</v>
@@ -25483,7 +25483,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G866" t="n">
-        <v>8.19461536407471</v>
+        <v>8.19461441040039</v>
       </c>
       <c r="H866" t="n">
         <v>334008</v>
@@ -25512,7 +25512,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G867" t="n">
-        <v>8.25760173797607</v>
+        <v>8.25760078430176</v>
       </c>
       <c r="H867" t="n">
         <v>273364</v>
@@ -25541,7 +25541,7 @@
         <v>13.0950002670288</v>
       </c>
       <c r="G868" t="n">
-        <v>8.24815464019775</v>
+        <v>8.24815368652344</v>
       </c>
       <c r="H868" t="n">
         <v>655675</v>
@@ -25599,7 +25599,7 @@
         <v>13.0550003051758</v>
       </c>
       <c r="G870" t="n">
-        <v>8.2229585647583</v>
+        <v>8.22295951843262</v>
       </c>
       <c r="H870" t="n">
         <v>461206</v>
@@ -25715,7 +25715,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G874" t="n">
-        <v>8.84967994689941</v>
+        <v>8.8496789932251</v>
       </c>
       <c r="H874" t="n">
         <v>1699970</v>
@@ -25802,7 +25802,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G877" t="n">
-        <v>9.14256954193115</v>
+        <v>9.14257049560547</v>
       </c>
       <c r="H877" t="n">
         <v>566778</v>
@@ -25831,7 +25831,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G878" t="n">
-        <v>9.11422538757324</v>
+        <v>9.11422443389893</v>
       </c>
       <c r="H878" t="n">
         <v>280889</v>
@@ -25889,7 +25889,7 @@
         <v>14.5</v>
       </c>
       <c r="G880" t="n">
-        <v>9.1331205368042</v>
+        <v>9.13312149047852</v>
       </c>
       <c r="H880" t="n">
         <v>465987</v>
@@ -25947,7 +25947,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G882" t="n">
-        <v>9.55513572692871</v>
+        <v>9.55513477325439</v>
       </c>
       <c r="H882" t="n">
         <v>1346388</v>
@@ -26034,7 +26034,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G885" t="n">
-        <v>9.09532928466797</v>
+        <v>9.09532833099365</v>
       </c>
       <c r="H885" t="n">
         <v>189995</v>
@@ -26092,7 +26092,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G887" t="n">
-        <v>9.04493808746338</v>
+        <v>9.0449390411377</v>
       </c>
       <c r="H887" t="n">
         <v>259836</v>
@@ -26121,7 +26121,7 @@
         <v>14.375</v>
       </c>
       <c r="G888" t="n">
-        <v>9.05438804626465</v>
+        <v>9.05438709259033</v>
       </c>
       <c r="H888" t="n">
         <v>231079</v>
@@ -26179,7 +26179,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G890" t="n">
-        <v>8.9441614151001</v>
+        <v>8.94416046142578</v>
       </c>
       <c r="H890" t="n">
         <v>500872</v>
@@ -26295,7 +26295,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G894" t="n">
-        <v>8.84967994689941</v>
+        <v>8.8496789932251</v>
       </c>
       <c r="H894" t="n">
         <v>296717</v>
@@ -26324,7 +26324,7 @@
         <v>13.9449996948242</v>
       </c>
       <c r="G895" t="n">
-        <v>8.78354263305664</v>
+        <v>8.78354358673096</v>
       </c>
       <c r="H895" t="n">
         <v>240805</v>
@@ -26382,7 +26382,7 @@
         <v>13.7449998855591</v>
       </c>
       <c r="G897" t="n">
-        <v>8.65756893157959</v>
+        <v>8.65756988525391</v>
       </c>
       <c r="H897" t="n">
         <v>559736</v>
@@ -26411,7 +26411,7 @@
         <v>13.7550001144409</v>
       </c>
       <c r="G898" t="n">
-        <v>8.66386699676514</v>
+        <v>8.66386795043945</v>
       </c>
       <c r="H898" t="n">
         <v>602223</v>
@@ -26469,7 +26469,7 @@
         <v>13.6350002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>8.58828449249268</v>
+        <v>8.58828353881836</v>
       </c>
       <c r="H900" t="n">
         <v>251630</v>
@@ -26527,7 +26527,7 @@
         <v>13.4849996566772</v>
       </c>
       <c r="G902" t="n">
-        <v>8.49380207061768</v>
+        <v>8.49380302429199</v>
       </c>
       <c r="H902" t="n">
         <v>279254</v>
@@ -26585,7 +26585,7 @@
         <v>13.3649997711182</v>
       </c>
       <c r="G904" t="n">
-        <v>8.4182186126709</v>
+        <v>8.41821765899658</v>
       </c>
       <c r="H904" t="n">
         <v>349713</v>
@@ -26614,7 +26614,7 @@
         <v>13.3050003051758</v>
       </c>
       <c r="G905" t="n">
-        <v>8.38042545318604</v>
+        <v>8.38042640686035</v>
       </c>
       <c r="H905" t="n">
         <v>301878</v>
@@ -26643,7 +26643,7 @@
         <v>13.414999961853</v>
       </c>
       <c r="G906" t="n">
-        <v>8.44971179962158</v>
+        <v>8.44971084594727</v>
       </c>
       <c r="H906" t="n">
         <v>246121</v>
@@ -26701,7 +26701,7 @@
         <v>13.4549999237061</v>
       </c>
       <c r="G908" t="n">
-        <v>8.47490692138672</v>
+        <v>8.4749059677124</v>
       </c>
       <c r="H908" t="n">
         <v>331943</v>
@@ -26730,7 +26730,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G909" t="n">
-        <v>8.45915985107422</v>
+        <v>8.45916080474854</v>
       </c>
       <c r="H909" t="n">
         <v>207137</v>
@@ -26759,7 +26759,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G910" t="n">
-        <v>8.28279590606689</v>
+        <v>8.28279685974121</v>
       </c>
       <c r="H910" t="n">
         <v>283266</v>
@@ -26788,7 +26788,7 @@
         <v>13.2550001144409</v>
       </c>
       <c r="G911" t="n">
-        <v>8.34893321990967</v>
+        <v>8.34893226623535</v>
       </c>
       <c r="H911" t="n">
         <v>201855</v>
@@ -26817,7 +26817,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G912" t="n">
-        <v>8.45915985107422</v>
+        <v>8.45916080474854</v>
       </c>
       <c r="H912" t="n">
         <v>276604</v>
@@ -26875,7 +26875,7 @@
         <v>13.1850004196167</v>
       </c>
       <c r="G914" t="n">
-        <v>8.30484294891357</v>
+        <v>8.30484199523926</v>
       </c>
       <c r="H914" t="n">
         <v>385974</v>
@@ -26904,7 +26904,7 @@
         <v>13.0249996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>8.20406150817871</v>
+        <v>8.20406246185303</v>
       </c>
       <c r="H915" t="n">
         <v>326623</v>
@@ -26962,7 +26962,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>8.37727832794189</v>
+        <v>8.37727737426758</v>
       </c>
       <c r="H917" t="n">
         <v>444874</v>
@@ -26991,7 +26991,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G918" t="n">
-        <v>8.16941928863525</v>
+        <v>8.16942024230957</v>
       </c>
       <c r="H918" t="n">
         <v>338016</v>
@@ -27020,7 +27020,7 @@
         <v>12.9650001525879</v>
       </c>
       <c r="G919" t="n">
-        <v>8.16626930236816</v>
+        <v>8.16627025604248</v>
       </c>
       <c r="H919" t="n">
         <v>280860</v>
@@ -27049,7 +27049,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G920" t="n">
-        <v>8.25130367279053</v>
+        <v>8.25130271911621</v>
       </c>
       <c r="H920" t="n">
         <v>358492</v>
@@ -27078,7 +27078,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>8.59773063659668</v>
+        <v>8.597731590271</v>
       </c>
       <c r="H921" t="n">
         <v>1184667</v>
@@ -27107,7 +27107,7 @@
         <v>15</v>
       </c>
       <c r="G922" t="n">
-        <v>9.4480562210083</v>
+        <v>9.44805717468262</v>
       </c>
       <c r="H922" t="n">
         <v>2418378</v>
@@ -27194,7 +27194,7 @@
         <v>14.6750001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>9.24334812164307</v>
+        <v>9.24334907531738</v>
       </c>
       <c r="H925" t="n">
         <v>414297</v>
@@ -27310,7 +27310,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G929" t="n">
-        <v>9.24019908905029</v>
+        <v>9.24020004272461</v>
       </c>
       <c r="H929" t="n">
         <v>250054</v>
@@ -27368,7 +27368,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G931" t="n">
-        <v>8.9441614151001</v>
+        <v>8.94416046142578</v>
       </c>
       <c r="H931" t="n">
         <v>356627</v>
@@ -27513,7 +27513,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G936" t="n">
-        <v>8.837082862854</v>
+        <v>8.83708190917969</v>
       </c>
       <c r="H936" t="n">
         <v>255846</v>
@@ -27832,7 +27832,7 @@
         <v>13.8050003051758</v>
       </c>
       <c r="G947" t="n">
-        <v>8.69536209106445</v>
+        <v>8.69536113739014</v>
       </c>
       <c r="H947" t="n">
         <v>1081374</v>
@@ -27890,7 +27890,7 @@
         <v>13.5749998092651</v>
       </c>
       <c r="G949" t="n">
-        <v>8.5504903793335</v>
+        <v>8.55049133300781</v>
       </c>
       <c r="H949" t="n">
         <v>242689</v>
@@ -27948,7 +27948,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G951" t="n">
-        <v>8.50955009460449</v>
+        <v>8.50954914093018</v>
       </c>
       <c r="H951" t="n">
         <v>280999</v>
@@ -27977,7 +27977,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G952" t="n">
-        <v>8.55364036560059</v>
+        <v>8.5536413192749</v>
       </c>
       <c r="H952" t="n">
         <v>327819</v>
@@ -28006,7 +28006,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G953" t="n">
-        <v>8.50955009460449</v>
+        <v>8.50954914093018</v>
       </c>
       <c r="H953" t="n">
         <v>261912</v>
@@ -28035,7 +28035,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G954" t="n">
-        <v>8.54734230041504</v>
+        <v>8.54734134674072</v>
       </c>
       <c r="H954" t="n">
         <v>515523</v>
@@ -28093,7 +28093,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.22610759735107</v>
+        <v>8.22610855102539</v>
       </c>
       <c r="H956" t="n">
         <v>729140</v>
@@ -28122,7 +28122,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G957" t="n">
-        <v>8.2072114944458</v>
+        <v>8.20721054077148</v>
       </c>
       <c r="H957" t="n">
         <v>254581</v>
@@ -28151,7 +28151,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G958" t="n">
-        <v>8.27334785461426</v>
+        <v>8.27334880828857</v>
       </c>
       <c r="H958" t="n">
         <v>275236</v>
@@ -28180,7 +28180,7 @@
         <v>12.9650001525879</v>
       </c>
       <c r="G959" t="n">
-        <v>8.16626930236816</v>
+        <v>8.16627025604248</v>
       </c>
       <c r="H959" t="n">
         <v>438762</v>
@@ -28238,7 +28238,7 @@
         <v>12.9250001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>8.14107418060303</v>
+        <v>8.14107513427734</v>
       </c>
       <c r="H961" t="n">
         <v>377440</v>
@@ -28296,7 +28296,7 @@
         <v>13.3450002670288</v>
       </c>
       <c r="G963" t="n">
-        <v>8.40562152862549</v>
+        <v>8.40562057495117</v>
       </c>
       <c r="H963" t="n">
         <v>489466</v>
@@ -28325,7 +28325,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G964" t="n">
-        <v>8.54734230041504</v>
+        <v>8.54734134674072</v>
       </c>
       <c r="H964" t="n">
         <v>830785</v>
@@ -28412,7 +28412,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G967" t="n">
-        <v>8.36153125762939</v>
+        <v>8.36153030395508</v>
       </c>
       <c r="H967" t="n">
         <v>214395</v>
@@ -28470,7 +28470,7 @@
         <v>13.4549999237061</v>
       </c>
       <c r="G969" t="n">
-        <v>8.47490692138672</v>
+        <v>8.4749059677124</v>
       </c>
       <c r="H969" t="n">
         <v>230338</v>
@@ -28528,7 +28528,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G971" t="n">
-        <v>8.52529716491699</v>
+        <v>8.52529621124268</v>
       </c>
       <c r="H971" t="n">
         <v>218241</v>
@@ -28557,7 +28557,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G972" t="n">
-        <v>8.54104328155518</v>
+        <v>8.54104423522949</v>
       </c>
       <c r="H972" t="n">
         <v>227065</v>
@@ -28644,7 +28644,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G975" t="n">
-        <v>8.55364036560059</v>
+        <v>8.5536413192749</v>
       </c>
       <c r="H975" t="n">
         <v>616663</v>
@@ -28673,7 +28673,7 @@
         <v>13.4049997329712</v>
       </c>
       <c r="G976" t="n">
-        <v>8.44341278076172</v>
+        <v>8.44341373443604</v>
       </c>
       <c r="H976" t="n">
         <v>310060</v>
@@ -28731,7 +28731,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G978" t="n">
-        <v>8.64182186126709</v>
+        <v>8.64182281494141</v>
       </c>
       <c r="H978" t="n">
         <v>247221</v>
@@ -28818,7 +28818,7 @@
         <v>13.5649995803833</v>
       </c>
       <c r="G981" t="n">
-        <v>8.54419136047363</v>
+        <v>8.54419231414795</v>
       </c>
       <c r="H981" t="n">
         <v>326606</v>
@@ -28876,7 +28876,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G983" t="n">
-        <v>8.54104328155518</v>
+        <v>8.54104423522949</v>
       </c>
       <c r="H983" t="n">
         <v>233924</v>
@@ -28934,7 +28934,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G985" t="n">
-        <v>8.56623840332031</v>
+        <v>8.566237449646</v>
       </c>
       <c r="H985" t="n">
         <v>1407536</v>
@@ -28992,7 +28992,7 @@
         <v>13.3950004577637</v>
       </c>
       <c r="G987" t="n">
-        <v>8.43711471557617</v>
+        <v>8.43711566925049</v>
       </c>
       <c r="H987" t="n">
         <v>515114</v>
@@ -29108,7 +29108,7 @@
         <v>13.4049997329712</v>
       </c>
       <c r="G991" t="n">
-        <v>8.44341278076172</v>
+        <v>8.44341373443604</v>
       </c>
       <c r="H991" t="n">
         <v>639147</v>
@@ -29195,7 +29195,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G994" t="n">
-        <v>8.64182186126709</v>
+        <v>8.64182281494141</v>
       </c>
       <c r="H994" t="n">
         <v>576719</v>
@@ -29253,7 +29253,7 @@
         <v>13.9449996948242</v>
       </c>
       <c r="G996" t="n">
-        <v>8.78354263305664</v>
+        <v>8.78354358673096</v>
       </c>
       <c r="H996" t="n">
         <v>614847</v>
@@ -29282,7 +29282,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G997" t="n">
-        <v>8.64182186126709</v>
+        <v>8.64182281494141</v>
       </c>
       <c r="H997" t="n">
         <v>1027218</v>
@@ -29369,7 +29369,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G1000" t="n">
-        <v>8.50955009460449</v>
+        <v>8.50954914093018</v>
       </c>
       <c r="H1000" t="n">
         <v>233256</v>
@@ -29572,7 +29572,7 @@
         <v>13.4849996566772</v>
       </c>
       <c r="G1007" t="n">
-        <v>8.49380207061768</v>
+        <v>8.49380302429199</v>
       </c>
       <c r="H1007" t="n">
         <v>502422</v>
@@ -29630,7 +29630,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1009" t="n">
-        <v>8.48435592651367</v>
+        <v>8.48435497283936</v>
       </c>
       <c r="H1009" t="n">
         <v>393844</v>
@@ -29688,7 +29688,7 @@
         <v>13.335000038147</v>
       </c>
       <c r="G1011" t="n">
-        <v>8.39932250976562</v>
+        <v>8.39932346343994</v>
       </c>
       <c r="H1011" t="n">
         <v>235891</v>
@@ -29717,7 +29717,7 @@
         <v>13.3450002670288</v>
       </c>
       <c r="G1012" t="n">
-        <v>8.40562152862549</v>
+        <v>8.40562057495117</v>
       </c>
       <c r="H1012" t="n">
         <v>229283</v>
@@ -29804,7 +29804,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>8.37727832794189</v>
+        <v>8.37727737426758</v>
       </c>
       <c r="H1015" t="n">
         <v>203490</v>
@@ -29833,7 +29833,7 @@
         <v>13.4750003814697</v>
       </c>
       <c r="G1016" t="n">
-        <v>8.48750400543213</v>
+        <v>8.48750495910645</v>
       </c>
       <c r="H1016" t="n">
         <v>258656</v>
@@ -29862,7 +29862,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G1017" t="n">
-        <v>8.50955009460449</v>
+        <v>8.50954914093018</v>
       </c>
       <c r="H1017" t="n">
         <v>377837</v>
@@ -29891,7 +29891,7 @@
         <v>13.5450000762939</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.53159618377686</v>
+        <v>8.53159427642822</v>
       </c>
       <c r="H1018" t="n">
         <v>230051</v>
@@ -30036,7 +30036,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>8.28279590606689</v>
+        <v>8.28279685974121</v>
       </c>
       <c r="H1023" t="n">
         <v>216224</v>
@@ -30094,7 +30094,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1025" t="n">
-        <v>8.16941928863525</v>
+        <v>8.16942024230957</v>
       </c>
       <c r="H1025" t="n">
         <v>296004</v>
@@ -30123,7 +30123,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.2072114944458</v>
+        <v>8.20721054077148</v>
       </c>
       <c r="H1026" t="n">
         <v>319993</v>
@@ -30152,7 +30152,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1027" t="n">
-        <v>8.19776344299316</v>
+        <v>8.19776439666748</v>
       </c>
       <c r="H1027" t="n">
         <v>134732</v>
@@ -30239,7 +30239,7 @@
         <v>12.6549997329712</v>
       </c>
       <c r="G1030" t="n">
-        <v>7.97101020812988</v>
+        <v>7.9710111618042</v>
       </c>
       <c r="H1030" t="n">
         <v>424553</v>
@@ -30268,7 +30268,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>7.90487384796143</v>
+        <v>7.90487337112427</v>
       </c>
       <c r="H1031" t="n">
         <v>360322</v>
@@ -30297,7 +30297,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>7.90487384796143</v>
+        <v>7.90487337112427</v>
       </c>
       <c r="H1032" t="n">
         <v>255316</v>
@@ -30355,7 +30355,7 @@
         <v>12.375</v>
       </c>
       <c r="G1034" t="n">
-        <v>7.79464769363403</v>
+        <v>7.79464721679688</v>
       </c>
       <c r="H1034" t="n">
         <v>222858</v>
@@ -30413,7 +30413,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>7.6718225479126</v>
+        <v>7.67182159423828</v>
       </c>
       <c r="H1036" t="n">
         <v>296897</v>
@@ -30471,7 +30471,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G1038" t="n">
-        <v>7.58364009857178</v>
+        <v>7.58364057540894</v>
       </c>
       <c r="H1038" t="n">
         <v>292932</v>
@@ -30500,7 +30500,7 @@
         <v>11.9750003814697</v>
       </c>
       <c r="G1039" t="n">
-        <v>7.54269886016846</v>
+        <v>7.5426983833313</v>
       </c>
       <c r="H1039" t="n">
         <v>406447</v>
@@ -30587,7 +30587,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G1042" t="n">
-        <v>7.47656154632568</v>
+        <v>7.47656202316284</v>
       </c>
       <c r="H1042" t="n">
         <v>288209</v>
@@ -30616,7 +30616,7 @@
         <v>11.8850002288818</v>
       </c>
       <c r="G1043" t="n">
-        <v>7.48601055145264</v>
+        <v>7.48601007461548</v>
       </c>
       <c r="H1043" t="n">
         <v>188108</v>
@@ -30645,7 +30645,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>7.46396589279175</v>
+        <v>7.46396541595459</v>
       </c>
       <c r="H1044" t="n">
         <v>381290</v>
@@ -30674,7 +30674,7 @@
         <v>11.9849996566772</v>
       </c>
       <c r="G1045" t="n">
-        <v>7.54899787902832</v>
+        <v>7.54899740219116</v>
       </c>
       <c r="H1045" t="n">
         <v>253560</v>
@@ -30703,7 +30703,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1046" t="n">
-        <v>7.49545812606812</v>
+        <v>7.49545860290527</v>
       </c>
       <c r="H1046" t="n">
         <v>477260</v>
@@ -30761,7 +30761,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1048" t="n">
-        <v>7.56474494934082</v>
+        <v>7.56474447250366</v>
       </c>
       <c r="H1048" t="n">
         <v>444424</v>
@@ -30790,7 +30790,7 @@
         <v>11.8649997711182</v>
       </c>
       <c r="G1049" t="n">
-        <v>7.47341299057007</v>
+        <v>7.47341203689575</v>
       </c>
       <c r="H1049" t="n">
         <v>407738</v>
@@ -30819,7 +30819,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1050" t="n">
-        <v>7.3253927230835</v>
+        <v>7.32539319992065</v>
       </c>
       <c r="H1050" t="n">
         <v>844378</v>
@@ -30906,7 +30906,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.70811891555786</v>
+        <v>6.70811939239502</v>
       </c>
       <c r="H1053" t="n">
         <v>1104852</v>
@@ -30935,7 +30935,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G1054" t="n">
-        <v>6.79630136489868</v>
+        <v>6.79630184173584</v>
       </c>
       <c r="H1054" t="n">
         <v>651505</v>
@@ -30964,7 +30964,7 @@
         <v>11.2749996185303</v>
       </c>
       <c r="G1055" t="n">
-        <v>7.1017894744873</v>
+        <v>7.10178852081299</v>
       </c>
       <c r="H1055" t="n">
         <v>877031</v>
@@ -31051,7 +31051,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.46876955032349</v>
+        <v>6.46877002716064</v>
       </c>
       <c r="H1058" t="n">
         <v>602803</v>
@@ -31109,7 +31109,7 @@
         <v>9.81750011444092</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.183753490448</v>
+        <v>6.18375301361084</v>
       </c>
       <c r="H1060" t="n">
         <v>558989</v>
@@ -31138,7 +31138,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1061" t="n">
-        <v>5.88299036026001</v>
+        <v>5.88298940658569</v>
       </c>
       <c r="H1061" t="n">
         <v>856268</v>
@@ -31283,7 +31283,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1066" t="n">
-        <v>4.31461238861084</v>
+        <v>4.31461191177368</v>
       </c>
       <c r="H1066" t="n">
         <v>1002891</v>
@@ -31428,7 +31428,7 @@
         <v>8.5</v>
       </c>
       <c r="G1071" t="n">
-        <v>5.3538990020752</v>
+        <v>5.35389852523804</v>
       </c>
       <c r="H1071" t="n">
         <v>608321</v>
@@ -31544,7 +31544,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.70032787322998</v>
+        <v>5.70032835006714</v>
       </c>
       <c r="H1075" t="n">
         <v>888894</v>
@@ -31573,7 +31573,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.87039184570312</v>
+        <v>5.87039232254028</v>
       </c>
       <c r="H1076" t="n">
         <v>276828</v>
@@ -31631,7 +31631,7 @@
         <v>9.67249965667725</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.0924220085144</v>
+        <v>6.09242153167725</v>
       </c>
       <c r="H1078" t="n">
         <v>270658</v>
@@ -31718,7 +31718,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.22626972198486</v>
+        <v>6.22626924514771</v>
       </c>
       <c r="H1081" t="n">
         <v>317322</v>
@@ -31747,7 +31747,7 @@
         <v>9.75500011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.14438629150391</v>
+        <v>6.14438533782959</v>
       </c>
       <c r="H1082" t="n">
         <v>311303</v>
@@ -31776,7 +31776,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1083" t="n">
-        <v>6.25461435317993</v>
+        <v>6.25461387634277</v>
       </c>
       <c r="H1083" t="n">
         <v>161072</v>
@@ -31805,7 +31805,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G1084" t="n">
-        <v>6.22626972198486</v>
+        <v>6.22626924514771</v>
       </c>
       <c r="H1084" t="n">
         <v>502100</v>
@@ -31921,7 +31921,7 @@
         <v>9.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.98376893997192</v>
+        <v>5.98376846313477</v>
       </c>
       <c r="H1088" t="n">
         <v>158398</v>
@@ -31950,7 +31950,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G1089" t="n">
-        <v>5.73182153701782</v>
+        <v>5.73182106018066</v>
       </c>
       <c r="H1089" t="n">
         <v>351846</v>
@@ -32008,7 +32008,7 @@
         <v>9.22999954223633</v>
       </c>
       <c r="G1091" t="n">
-        <v>5.81370449066162</v>
+        <v>5.81370401382446</v>
       </c>
       <c r="H1091" t="n">
         <v>105563</v>
@@ -32153,7 +32153,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.95227575302124</v>
+        <v>5.95227527618408</v>
       </c>
       <c r="H1096" t="n">
         <v>164738</v>
@@ -32298,7 +32298,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G1101" t="n">
-        <v>5.72552299499512</v>
+        <v>5.72552251815796</v>
       </c>
       <c r="H1101" t="n">
         <v>47489</v>
@@ -32356,7 +32356,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.54915904998779</v>
+        <v>5.54915952682495</v>
       </c>
       <c r="H1103" t="n">
         <v>145163</v>
@@ -32443,7 +32443,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.69717836380005</v>
+        <v>5.69717788696289</v>
       </c>
       <c r="H1106" t="n">
         <v>111063</v>
@@ -32530,7 +32530,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1109" t="n">
-        <v>5.34759998321533</v>
+        <v>5.34759950637817</v>
       </c>
       <c r="H1109" t="n">
         <v>236103</v>
@@ -32646,7 +32646,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.47208070755005</v>
+        <v>4.47208023071289</v>
       </c>
       <c r="H1113" t="n">
         <v>550047</v>
@@ -32762,7 +32762,7 @@
         <v>7.75</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.8814959526062</v>
+        <v>4.88149642944336</v>
       </c>
       <c r="H1117" t="n">
         <v>390298</v>
@@ -32791,7 +32791,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.02636575698853</v>
+        <v>5.02636623382568</v>
       </c>
       <c r="H1118" t="n">
         <v>398179</v>
@@ -33023,7 +33023,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.47672319412231</v>
+        <v>5.47672271728516</v>
       </c>
       <c r="H1126" t="n">
         <v>512522</v>
@@ -33168,7 +33168,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1131" t="n">
-        <v>4.98542404174805</v>
+        <v>4.98542451858521</v>
       </c>
       <c r="H1131" t="n">
         <v>489382</v>
@@ -33226,7 +33226,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.98857402801514</v>
+        <v>4.98857450485229</v>
       </c>
       <c r="H1133" t="n">
         <v>305333</v>
@@ -33284,7 +33284,7 @@
         <v>7.75</v>
       </c>
       <c r="G1135" t="n">
-        <v>4.8814959526062</v>
+        <v>4.88149642944336</v>
       </c>
       <c r="H1135" t="n">
         <v>511743</v>
@@ -33400,7 +33400,7 @@
         <v>7.75</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.8814959526062</v>
+        <v>4.88149642944336</v>
       </c>
       <c r="H1139" t="n">
         <v>309486</v>
@@ -33429,7 +33429,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.96652841567993</v>
+        <v>4.96652889251709</v>
       </c>
       <c r="H1140" t="n">
         <v>336649</v>
@@ -33458,7 +33458,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.98542404174805</v>
+        <v>4.98542451858521</v>
       </c>
       <c r="H1141" t="n">
         <v>274991</v>
@@ -33487,7 +33487,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.92243766784668</v>
+        <v>4.92243719100952</v>
       </c>
       <c r="H1142" t="n">
         <v>340749</v>
@@ -33516,7 +33516,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.04211282730103</v>
+        <v>5.04211330413818</v>
       </c>
       <c r="H1143" t="n">
         <v>528862</v>
@@ -33545,7 +33545,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.00747013092041</v>
+        <v>5.00746965408325</v>
       </c>
       <c r="H1144" t="n">
         <v>333487</v>
@@ -33661,7 +33661,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.74607419967651</v>
+        <v>4.74607372283936</v>
       </c>
       <c r="H1148" t="n">
         <v>413722</v>
@@ -33748,7 +33748,7 @@
         <v>7.5</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.72402811050415</v>
+        <v>4.72402858734131</v>
       </c>
       <c r="H1151" t="n">
         <v>408018</v>
@@ -33777,7 +33777,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78071641921997</v>
+        <v>4.78071737289429</v>
       </c>
       <c r="H1152" t="n">
         <v>432446</v>
@@ -33806,7 +33806,7 @@
         <v>7.66499996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.82795667648315</v>
+        <v>4.82795715332031</v>
       </c>
       <c r="H1153" t="n">
         <v>260313</v>
@@ -33835,7 +33835,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.81220960617065</v>
+        <v>4.81221008300781</v>
       </c>
       <c r="H1154" t="n">
         <v>169651</v>
@@ -33864,7 +33864,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.82480764389038</v>
+        <v>4.82480716705322</v>
       </c>
       <c r="H1155" t="n">
         <v>287172</v>
@@ -33951,7 +33951,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.81850910186768</v>
+        <v>4.81850862503052</v>
       </c>
       <c r="H1158" t="n">
         <v>247495</v>
@@ -33980,7 +33980,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>4.7523717880249</v>
+        <v>4.75237226486206</v>
       </c>
       <c r="H1159" t="n">
         <v>260185</v>
@@ -34009,7 +34009,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G1160" t="n">
-        <v>4.68623638153076</v>
+        <v>4.6862359046936</v>
       </c>
       <c r="H1160" t="n">
         <v>361760</v>
@@ -34038,7 +34038,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.78071641921997</v>
+        <v>4.78071737289429</v>
       </c>
       <c r="H1161" t="n">
         <v>205066</v>
@@ -34096,7 +34096,7 @@
         <v>7.625</v>
       </c>
       <c r="G1163" t="n">
-        <v>4.80276250839233</v>
+        <v>4.80276203155518</v>
       </c>
       <c r="H1163" t="n">
         <v>552779</v>
@@ -34154,7 +34154,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.67048931121826</v>
+        <v>4.67048978805542</v>
       </c>
       <c r="H1165" t="n">
         <v>332596</v>
@@ -34183,7 +34183,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1166" t="n">
-        <v>5.09565162658691</v>
+        <v>5.09565210342407</v>
       </c>
       <c r="H1166" t="n">
         <v>911144</v>
@@ -34212,7 +34212,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.07045698165894</v>
+        <v>5.07045745849609</v>
       </c>
       <c r="H1167" t="n">
         <v>903901</v>
@@ -34299,7 +34299,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.01376819610596</v>
+        <v>5.01376867294312</v>
       </c>
       <c r="H1170" t="n">
         <v>266976</v>
@@ -34328,7 +34328,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.07045698165894</v>
+        <v>5.07045745849609</v>
       </c>
       <c r="H1171" t="n">
         <v>316589</v>
@@ -34386,7 +34386,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.21217727661133</v>
+        <v>5.21217775344849</v>
       </c>
       <c r="H1173" t="n">
         <v>307873</v>
@@ -34415,7 +34415,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.17123603820801</v>
+        <v>5.17123651504517</v>
       </c>
       <c r="H1174" t="n">
         <v>232058</v>
@@ -34502,7 +34502,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G1177" t="n">
-        <v>5.09565162658691</v>
+        <v>5.09565210342407</v>
       </c>
       <c r="H1177" t="n">
         <v>196886</v>
@@ -34531,7 +34531,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G1178" t="n">
-        <v>5.06415891647339</v>
+        <v>5.06415843963623</v>
       </c>
       <c r="H1178" t="n">
         <v>115544</v>
@@ -34560,7 +34560,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1179" t="n">
-        <v>5.04841184616089</v>
+        <v>5.04841232299805</v>
       </c>
       <c r="H1179" t="n">
         <v>182623</v>
@@ -34618,7 +34618,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.98542404174805</v>
+        <v>4.98542451858521</v>
       </c>
       <c r="H1181" t="n">
         <v>331215</v>
@@ -34705,7 +34705,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.96337938308716</v>
+        <v>4.96337890625</v>
       </c>
       <c r="H1184" t="n">
         <v>183239</v>
@@ -34734,7 +34734,7 @@
         <v>7.75</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.8814959526062</v>
+        <v>4.88149642944336</v>
       </c>
       <c r="H1185" t="n">
         <v>253372</v>
@@ -34821,7 +34821,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.98542404174805</v>
+        <v>4.98542451858521</v>
       </c>
       <c r="H1188" t="n">
         <v>1167367</v>
@@ -34908,7 +34908,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1191" t="n">
-        <v>5.78850936889648</v>
+        <v>5.78850984573364</v>
       </c>
       <c r="H1191" t="n">
         <v>2405489</v>
@@ -35140,7 +35140,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1199" t="n">
-        <v>5.54915904998779</v>
+        <v>5.54915952682495</v>
       </c>
       <c r="H1199" t="n">
         <v>1690987</v>
@@ -35169,7 +35169,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.36964511871338</v>
+        <v>5.36964559555054</v>
       </c>
       <c r="H1200" t="n">
         <v>674270</v>
@@ -35314,7 +35314,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G1205" t="n">
-        <v>5.28146362304688</v>
+        <v>5.28146409988403</v>
       </c>
       <c r="H1205" t="n">
         <v>257027</v>
@@ -35517,7 +35517,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.36334705352783</v>
+        <v>5.36334753036499</v>
       </c>
       <c r="H1212" t="n">
         <v>206253</v>
@@ -35575,7 +35575,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.32240533828735</v>
+        <v>5.3224048614502</v>
       </c>
       <c r="H1214" t="n">
         <v>229742</v>
@@ -35604,7 +35604,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>5.22792482376099</v>
+        <v>5.22792530059814</v>
       </c>
       <c r="H1215" t="n">
         <v>222732</v>
@@ -35749,7 +35749,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.13029527664185</v>
+        <v>5.130295753479</v>
       </c>
       <c r="H1220" t="n">
         <v>146500</v>
@@ -35836,7 +35836,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.04211282730103</v>
+        <v>5.04211330413818</v>
       </c>
       <c r="H1223" t="n">
         <v>200334</v>
@@ -35952,7 +35952,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.63269758224487</v>
+        <v>4.63269662857056</v>
       </c>
       <c r="H1227" t="n">
         <v>402067</v>
@@ -35981,7 +35981,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.66104173660278</v>
+        <v>4.66104125976562</v>
       </c>
       <c r="H1228" t="n">
         <v>514559</v>
@@ -36039,7 +36039,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>4.65159320831299</v>
+        <v>4.65159368515015</v>
       </c>
       <c r="H1230" t="n">
         <v>158600</v>
@@ -36068,7 +36068,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.77756786346436</v>
+        <v>4.7775673866272</v>
       </c>
       <c r="H1231" t="n">
         <v>294586</v>
@@ -36126,7 +36126,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.90984010696411</v>
+        <v>4.90984058380127</v>
       </c>
       <c r="H1233" t="n">
         <v>262650</v>
@@ -36300,7 +36300,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.73811960220337</v>
+        <v>5.73811912536621</v>
       </c>
       <c r="H1239" t="n">
         <v>522417</v>
@@ -36358,7 +36358,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1241" t="n">
-        <v>6.2042236328125</v>
+        <v>6.20422315597534</v>
       </c>
       <c r="H1241" t="n">
         <v>845083</v>
@@ -36387,7 +36387,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>6.4057822227478</v>
+        <v>6.40578269958496</v>
       </c>
       <c r="H1242" t="n">
         <v>699300</v>
@@ -36416,7 +36416,7 @@
         <v>9.91499996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>6.24516534805298</v>
+        <v>6.24516582489014</v>
       </c>
       <c r="H1243" t="n">
         <v>615063</v>
@@ -36445,7 +36445,7 @@
         <v>9.93000030517578</v>
       </c>
       <c r="G1244" t="n">
-        <v>6.25461435317993</v>
+        <v>6.25461387634277</v>
       </c>
       <c r="H1244" t="n">
         <v>325582</v>
@@ -36474,7 +36474,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G1245" t="n">
-        <v>6.19792556762695</v>
+        <v>6.19792509078979</v>
       </c>
       <c r="H1245" t="n">
         <v>354705</v>
@@ -36503,7 +36503,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1246" t="n">
-        <v>6.32389879226685</v>
+        <v>6.323899269104</v>
       </c>
       <c r="H1246" t="n">
         <v>543926</v>
@@ -36532,7 +36532,7 @@
         <v>9.97500038146973</v>
       </c>
       <c r="G1247" t="n">
-        <v>6.28295803070068</v>
+        <v>6.28295755386353</v>
       </c>
       <c r="H1247" t="n">
         <v>407763</v>
@@ -36590,7 +36590,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G1249" t="n">
-        <v>6.25146436691284</v>
+        <v>6.25146389007568</v>
       </c>
       <c r="H1249" t="n">
         <v>547247</v>
@@ -36619,7 +36619,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G1250" t="n">
-        <v>6.22626972198486</v>
+        <v>6.22626924514771</v>
       </c>
       <c r="H1250" t="n">
         <v>403412</v>
@@ -36648,7 +36648,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G1251" t="n">
-        <v>6.38058662414551</v>
+        <v>6.38058710098267</v>
       </c>
       <c r="H1251" t="n">
         <v>425417</v>
@@ -36793,7 +36793,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1256" t="n">
-        <v>6.70182180404663</v>
+        <v>6.70182132720947</v>
       </c>
       <c r="H1256" t="n">
         <v>215386</v>
@@ -36851,7 +36851,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1258" t="n">
-        <v>6.67032814025879</v>
+        <v>6.67032861709595</v>
       </c>
       <c r="H1258" t="n">
         <v>298564</v>
@@ -36967,7 +36967,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.72701644897461</v>
+        <v>6.72701692581177</v>
       </c>
       <c r="H1262" t="n">
         <v>369792</v>
@@ -36996,7 +36996,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1263" t="n">
-        <v>6.63883447647095</v>
+        <v>6.63883495330811</v>
       </c>
       <c r="H1263" t="n">
         <v>392582</v>
@@ -37170,7 +37170,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1269" t="n">
-        <v>6.63883447647095</v>
+        <v>6.63883495330811</v>
       </c>
       <c r="H1269" t="n">
         <v>142649</v>
@@ -37257,7 +37257,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1272" t="n">
-        <v>6.67032814025879</v>
+        <v>6.67032861709595</v>
       </c>
       <c r="H1272" t="n">
         <v>214365</v>
@@ -37286,7 +37286,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G1273" t="n">
-        <v>6.72071743011475</v>
+        <v>6.7207179069519</v>
       </c>
       <c r="H1273" t="n">
         <v>219057</v>
@@ -37315,7 +37315,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1274" t="n">
-        <v>6.67662715911865</v>
+        <v>6.67662763595581</v>
       </c>
       <c r="H1274" t="n">
         <v>204052</v>
@@ -37344,7 +37344,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>6.67032814025879</v>
+        <v>6.67032861709595</v>
       </c>
       <c r="H1275" t="n">
         <v>179160</v>
@@ -37402,7 +37402,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1277" t="n">
-        <v>6.55695199966431</v>
+        <v>6.55695152282715</v>
       </c>
       <c r="H1277" t="n">
         <v>172172</v>
@@ -37460,7 +37460,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1279" t="n">
-        <v>6.67662715911865</v>
+        <v>6.67662763595581</v>
       </c>
       <c r="H1279" t="n">
         <v>392780</v>
@@ -37605,7 +37605,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1284" t="n">
-        <v>6.76480865478516</v>
+        <v>6.764808177948</v>
       </c>
       <c r="H1284" t="n">
         <v>425309</v>
@@ -37634,7 +37634,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.61993789672852</v>
+        <v>6.61993837356567</v>
       </c>
       <c r="H1285" t="n">
         <v>321970</v>
@@ -37663,7 +37663,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1286" t="n">
-        <v>6.50026226043701</v>
+        <v>6.50026273727417</v>
       </c>
       <c r="H1286" t="n">
         <v>377063</v>
@@ -37779,7 +37779,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G1290" t="n">
-        <v>6.73331546783447</v>
+        <v>6.73331499099731</v>
       </c>
       <c r="H1290" t="n">
         <v>244243</v>
@@ -37837,7 +37837,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1292" t="n">
-        <v>6.72701644897461</v>
+        <v>6.72701692581177</v>
       </c>
       <c r="H1292" t="n">
         <v>214135</v>
@@ -37924,7 +37924,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1295" t="n">
-        <v>6.89078283309937</v>
+        <v>6.89078235626221</v>
       </c>
       <c r="H1295" t="n">
         <v>321636</v>
@@ -37953,7 +37953,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.10493898391724</v>
+        <v>7.10493850708008</v>
       </c>
       <c r="H1296" t="n">
         <v>604719</v>
@@ -38011,7 +38011,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.97266530990601</v>
+        <v>6.97266483306885</v>
       </c>
       <c r="H1298" t="n">
         <v>236611</v>
@@ -38040,7 +38040,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1299" t="n">
-        <v>6.95377016067505</v>
+        <v>6.95376968383789</v>
       </c>
       <c r="H1299" t="n">
         <v>134788</v>
@@ -38156,7 +38156,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1303" t="n">
-        <v>7.09234142303467</v>
+        <v>7.09234189987183</v>
       </c>
       <c r="H1303" t="n">
         <v>140355</v>
@@ -38214,7 +38214,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1305" t="n">
-        <v>7.1616268157959</v>
+        <v>7.16162633895874</v>
       </c>
       <c r="H1305" t="n">
         <v>267055</v>
@@ -38330,7 +38330,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.49545812606812</v>
+        <v>7.49545860290527</v>
       </c>
       <c r="H1309" t="n">
         <v>952860</v>
@@ -38359,7 +38359,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.38838005065918</v>
+        <v>7.38838052749634</v>
       </c>
       <c r="H1310" t="n">
         <v>385043</v>
@@ -38388,7 +38388,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.49545812606812</v>
+        <v>7.49545860290527</v>
       </c>
       <c r="H1311" t="n">
         <v>236476</v>
@@ -38417,7 +38417,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1312" t="n">
-        <v>7.59623765945435</v>
+        <v>7.5962381362915</v>
       </c>
       <c r="H1312" t="n">
         <v>460289</v>
@@ -38446,7 +38446,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1313" t="n">
-        <v>7.82928991317749</v>
+        <v>7.82929039001465</v>
       </c>
       <c r="H1313" t="n">
         <v>596697</v>
@@ -38475,7 +38475,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1314" t="n">
-        <v>7.69701671600342</v>
+        <v>7.69701766967773</v>
       </c>
       <c r="H1314" t="n">
         <v>390030</v>
@@ -38504,7 +38504,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G1315" t="n">
-        <v>7.69701671600342</v>
+        <v>7.69701766967773</v>
       </c>
       <c r="H1315" t="n">
         <v>260070</v>
@@ -38562,7 +38562,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1317" t="n">
-        <v>8.08753681182861</v>
+        <v>8.0875358581543</v>
       </c>
       <c r="H1317" t="n">
         <v>686213</v>
@@ -38591,7 +38591,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1318" t="n">
-        <v>8.15052318572998</v>
+        <v>8.15052223205566</v>
       </c>
       <c r="H1318" t="n">
         <v>477435</v>
@@ -38707,7 +38707,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>8.31429004669189</v>
+        <v>8.31428909301758</v>
       </c>
       <c r="H1322" t="n">
         <v>214120</v>
@@ -38736,7 +38736,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1323" t="n">
-        <v>8.37097835540771</v>
+        <v>8.3709774017334</v>
       </c>
       <c r="H1323" t="n">
         <v>211484</v>
@@ -38794,7 +38794,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1325" t="n">
-        <v>8.48435592651367</v>
+        <v>8.48435497283936</v>
       </c>
       <c r="H1325" t="n">
         <v>338241</v>
@@ -38852,7 +38852,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G1327" t="n">
-        <v>8.23870468139648</v>
+        <v>8.2387056350708</v>
       </c>
       <c r="H1327" t="n">
         <v>291250</v>
@@ -38881,7 +38881,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1328" t="n">
-        <v>7.98675727844238</v>
+        <v>7.98675680160522</v>
       </c>
       <c r="H1328" t="n">
         <v>540893</v>
@@ -38968,7 +38968,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1331" t="n">
-        <v>7.98675727844238</v>
+        <v>7.98675680160522</v>
       </c>
       <c r="H1331" t="n">
         <v>203329</v>
@@ -38997,7 +38997,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G1332" t="n">
-        <v>7.91747236251831</v>
+        <v>7.91747188568115</v>
       </c>
       <c r="H1332" t="n">
         <v>231084</v>
@@ -39026,7 +39026,7 @@
         <v>12.2700004577637</v>
       </c>
       <c r="G1333" t="n">
-        <v>7.72851085662842</v>
+        <v>7.72851037979126</v>
       </c>
       <c r="H1333" t="n">
         <v>448430</v>
@@ -39055,7 +39055,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1334" t="n">
-        <v>7.7537055015564</v>
+        <v>7.75370502471924</v>
       </c>
       <c r="H1334" t="n">
         <v>192538</v>
@@ -39084,7 +39084,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1335" t="n">
-        <v>7.79779577255249</v>
+        <v>7.79779624938965</v>
       </c>
       <c r="H1335" t="n">
         <v>231422</v>
@@ -39113,7 +39113,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1336" t="n">
-        <v>7.95526361465454</v>
+        <v>7.9552640914917</v>
       </c>
       <c r="H1336" t="n">
         <v>422853</v>
@@ -39171,7 +39171,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>7.76000308990479</v>
+        <v>7.7600040435791</v>
       </c>
       <c r="H1338" t="n">
         <v>181914</v>
@@ -39200,7 +39200,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>7.70331573486328</v>
+        <v>7.70331621170044</v>
       </c>
       <c r="H1339" t="n">
         <v>116812</v>
@@ -39229,7 +39229,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1340" t="n">
-        <v>7.76000308990479</v>
+        <v>7.7600040435791</v>
       </c>
       <c r="H1340" t="n">
         <v>146907</v>
@@ -39287,7 +39287,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>7.77889966964722</v>
+        <v>7.77889919281006</v>
       </c>
       <c r="H1342" t="n">
         <v>198378</v>
@@ -39316,7 +39316,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1343" t="n">
-        <v>7.83558797836304</v>
+        <v>7.83558750152588</v>
       </c>
       <c r="H1343" t="n">
         <v>174305</v>
@@ -39345,7 +39345,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1344" t="n">
-        <v>7.76000308990479</v>
+        <v>7.7600040435791</v>
       </c>
       <c r="H1344" t="n">
         <v>142048</v>
@@ -39374,7 +39374,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>7.35058879852295</v>
+        <v>7.35058832168579</v>
       </c>
       <c r="H1345" t="n">
         <v>776140</v>
@@ -39432,7 +39432,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1347" t="n">
-        <v>7.445068359375</v>
+        <v>7.44506788253784</v>
       </c>
       <c r="H1347" t="n">
         <v>196225</v>
@@ -39461,7 +39461,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G1348" t="n">
-        <v>7.38838005065918</v>
+        <v>7.38838052749634</v>
       </c>
       <c r="H1348" t="n">
         <v>170269</v>
@@ -39490,7 +39490,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>7.43247079849243</v>
+        <v>7.43247127532959</v>
       </c>
       <c r="H1349" t="n">
         <v>128079</v>
@@ -39519,7 +39519,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1350" t="n">
-        <v>7.52695083618164</v>
+        <v>7.52695226669312</v>
       </c>
       <c r="H1350" t="n">
         <v>476988</v>
@@ -39606,7 +39606,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1353" t="n">
-        <v>8.37097835540771</v>
+        <v>8.3709774017334</v>
       </c>
       <c r="H1353" t="n">
         <v>551143</v>
@@ -39635,7 +39635,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1354" t="n">
-        <v>8.45915985107422</v>
+        <v>8.45916080474854</v>
       </c>
       <c r="H1354" t="n">
         <v>322623</v>
@@ -39664,7 +39664,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1355" t="n">
-        <v>8.56623840332031</v>
+        <v>8.566237449646</v>
       </c>
       <c r="H1355" t="n">
         <v>997455</v>
@@ -39693,7 +39693,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G1356" t="n">
-        <v>8.61032867431641</v>
+        <v>8.61032962799072</v>
       </c>
       <c r="H1356" t="n">
         <v>429858</v>
@@ -39867,7 +39867,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G1362" t="n">
-        <v>8.89377117156982</v>
+        <v>8.89377021789551</v>
       </c>
       <c r="H1362" t="n">
         <v>463208</v>
@@ -39925,7 +39925,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1364" t="n">
-        <v>8.90636825561523</v>
+        <v>8.90636730194092</v>
       </c>
       <c r="H1364" t="n">
         <v>427072</v>
@@ -40012,7 +40012,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1367" t="n">
-        <v>9.00714778900146</v>
+        <v>9.00714683532715</v>
       </c>
       <c r="H1367" t="n">
         <v>239477</v>
@@ -40099,7 +40099,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1370" t="n">
-        <v>9.04493808746338</v>
+        <v>9.0449390411377</v>
       </c>
       <c r="H1370" t="n">
         <v>236486</v>
@@ -40273,7 +40273,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1376" t="n">
-        <v>9.37247276306152</v>
+        <v>9.37247180938721</v>
       </c>
       <c r="H1376" t="n">
         <v>294238</v>
@@ -40302,7 +40302,7 @@
         <v>14.8299999237061</v>
       </c>
       <c r="G1377" t="n">
-        <v>9.34097862243652</v>
+        <v>9.34097957611084</v>
       </c>
       <c r="H1377" t="n">
         <v>305365</v>
@@ -40389,7 +40389,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1380" t="n">
-        <v>9.43546009063721</v>
+        <v>9.43545913696289</v>
       </c>
       <c r="H1380" t="n">
         <v>405067</v>
@@ -40418,7 +40418,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1381" t="n">
-        <v>9.32208347320557</v>
+        <v>9.32208251953125</v>
       </c>
       <c r="H1381" t="n">
         <v>252212</v>
@@ -40447,7 +40447,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G1382" t="n">
-        <v>9.24019908905029</v>
+        <v>9.24020004272461</v>
       </c>
       <c r="H1382" t="n">
         <v>191084</v>
@@ -40476,7 +40476,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G1383" t="n">
-        <v>9.27169227600098</v>
+        <v>9.27169322967529</v>
       </c>
       <c r="H1383" t="n">
         <v>231411</v>
@@ -40679,7 +40679,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G1390" t="n">
-        <v>9.15831565856934</v>
+        <v>9.15831661224365</v>
       </c>
       <c r="H1390" t="n">
         <v>264255</v>
@@ -40766,7 +40766,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G1393" t="n">
-        <v>9.61812114715576</v>
+        <v>9.61812210083008</v>
       </c>
       <c r="H1393" t="n">
         <v>1069512</v>
@@ -40795,7 +40795,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1394" t="n">
-        <v>9.46695327758789</v>
+        <v>9.46695232391357</v>
       </c>
       <c r="H1394" t="n">
         <v>422994</v>
@@ -40824,7 +40824,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1395" t="n">
-        <v>9.45435428619385</v>
+        <v>9.45435523986816</v>
       </c>
       <c r="H1395" t="n">
         <v>525544</v>
@@ -40882,7 +40882,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1397" t="n">
-        <v>9.61182403564453</v>
+        <v>9.61182308197021</v>
       </c>
       <c r="H1397" t="n">
         <v>403098</v>
@@ -40911,7 +40911,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1398" t="n">
-        <v>9.89526557922363</v>
+        <v>9.89526462554932</v>
       </c>
       <c r="H1398" t="n">
         <v>1004409</v>
@@ -40940,7 +40940,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1399" t="n">
-        <v>9.89526557922363</v>
+        <v>9.89526462554932</v>
       </c>
       <c r="H1399" t="n">
         <v>334651</v>
@@ -40969,7 +40969,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1400" t="n">
-        <v>9.97714805603027</v>
+        <v>9.97714900970459</v>
       </c>
       <c r="H1400" t="n">
         <v>1420987</v>
@@ -40998,7 +40998,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G1401" t="n">
-        <v>10.0716285705566</v>
+        <v>10.0716276168823</v>
       </c>
       <c r="H1401" t="n">
         <v>929007</v>
@@ -41056,7 +41056,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1403" t="n">
-        <v>9.92675876617432</v>
+        <v>9.9267578125</v>
       </c>
       <c r="H1403" t="n">
         <v>418892</v>
@@ -41143,7 +41143,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G1406" t="n">
-        <v>10.1598100662231</v>
+        <v>10.1598091125488</v>
       </c>
       <c r="H1406" t="n">
         <v>520946</v>
@@ -41172,7 +41172,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1407" t="n">
-        <v>10.0149402618408</v>
+        <v>10.0149393081665</v>
       </c>
       <c r="H1407" t="n">
         <v>453810</v>
@@ -41259,7 +41259,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1410" t="n">
-        <v>9.26407432556152</v>
+        <v>9.26407527923584</v>
       </c>
       <c r="H1410" t="n">
         <v>779178</v>
@@ -41317,7 +41317,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1412" t="n">
-        <v>9.58448600769043</v>
+        <v>9.58448696136475</v>
       </c>
       <c r="H1412" t="n">
         <v>435270</v>
@@ -41346,7 +41346,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G1413" t="n">
-        <v>9.48000335693359</v>
+        <v>9.48000431060791</v>
       </c>
       <c r="H1413" t="n">
         <v>587262</v>
@@ -41375,7 +41375,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1414" t="n">
-        <v>9.34766006469727</v>
+        <v>9.34765911102295</v>
       </c>
       <c r="H1414" t="n">
         <v>510130</v>
@@ -41549,7 +41549,7 @@
         <v>12.75</v>
       </c>
       <c r="G1420" t="n">
-        <v>8.88097476959229</v>
+        <v>8.88097381591797</v>
       </c>
       <c r="H1420" t="n">
         <v>252233</v>
@@ -41665,7 +41665,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G1424" t="n">
-        <v>9.21531677246094</v>
+        <v>9.21531581878662</v>
       </c>
       <c r="H1424" t="n">
         <v>264482</v>
@@ -41694,7 +41694,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1425" t="n">
-        <v>9.26407432556152</v>
+        <v>9.26407527923584</v>
       </c>
       <c r="H1425" t="n">
         <v>246661</v>
@@ -41926,7 +41926,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1433" t="n">
-        <v>9.18048858642578</v>
+        <v>9.18048763275146</v>
       </c>
       <c r="H1433" t="n">
         <v>208259</v>
@@ -41955,7 +41955,7 @@
         <v>13.25</v>
       </c>
       <c r="G1434" t="n">
-        <v>9.22924709320068</v>
+        <v>9.22924613952637</v>
       </c>
       <c r="H1434" t="n">
         <v>207225</v>
@@ -42071,7 +42071,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1438" t="n">
-        <v>9.27800369262695</v>
+        <v>9.27800464630127</v>
       </c>
       <c r="H1438" t="n">
         <v>290138</v>
@@ -42129,7 +42129,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1440" t="n">
-        <v>9.19441986083984</v>
+        <v>9.19441890716553</v>
       </c>
       <c r="H1440" t="n">
         <v>592713</v>
@@ -42158,7 +42158,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1441" t="n">
-        <v>9.45910739898682</v>
+        <v>9.45910835266113</v>
       </c>
       <c r="H1441" t="n">
         <v>447683</v>
@@ -42187,7 +42187,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G1442" t="n">
-        <v>9.21531677246094</v>
+        <v>9.21531581878662</v>
       </c>
       <c r="H1442" t="n">
         <v>481045</v>
@@ -42245,7 +42245,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1444" t="n">
-        <v>9.14566040039062</v>
+        <v>9.14566135406494</v>
       </c>
       <c r="H1444" t="n">
         <v>183535</v>
@@ -42274,7 +42274,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G1445" t="n">
-        <v>9.03421306610107</v>
+        <v>9.03421401977539</v>
       </c>
       <c r="H1445" t="n">
         <v>237251</v>
@@ -42332,7 +42332,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G1447" t="n">
-        <v>8.95759296417236</v>
+        <v>8.95759391784668</v>
       </c>
       <c r="H1447" t="n">
         <v>228682</v>
@@ -42506,7 +42506,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>8.60235500335693</v>
+        <v>8.60235404968262</v>
       </c>
       <c r="H1453" t="n">
         <v>647898</v>
@@ -42593,7 +42593,7 @@
         <v>12.625</v>
       </c>
       <c r="G1456" t="n">
-        <v>8.79390621185303</v>
+        <v>8.79390525817871</v>
       </c>
       <c r="H1456" t="n">
         <v>844227</v>
@@ -42825,7 +42825,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.65807914733887</v>
+        <v>8.65808010101318</v>
       </c>
       <c r="H1464" t="n">
         <v>393526</v>
@@ -42883,7 +42883,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1466" t="n">
-        <v>8.57449340820312</v>
+        <v>8.57449245452881</v>
       </c>
       <c r="H1466" t="n">
         <v>361727</v>
@@ -43028,7 +43028,7 @@
         <v>12.210000038147</v>
       </c>
       <c r="G1471" t="n">
-        <v>8.50483703613281</v>
+        <v>8.50483798980713</v>
       </c>
       <c r="H1471" t="n">
         <v>300803</v>
@@ -43086,7 +43086,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.60235500335693</v>
+        <v>8.60235404968262</v>
       </c>
       <c r="H1473" t="n">
         <v>363646</v>
@@ -43115,7 +43115,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1474" t="n">
-        <v>8.60235500335693</v>
+        <v>8.60235404968262</v>
       </c>
       <c r="H1474" t="n">
         <v>279368</v>
@@ -43202,7 +43202,7 @@
         <v>12.75</v>
       </c>
       <c r="G1477" t="n">
-        <v>8.88097476959229</v>
+        <v>8.88097381591797</v>
       </c>
       <c r="H1477" t="n">
         <v>625454</v>
@@ -43231,7 +43231,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.80435466766357</v>
+        <v>8.80435371398926</v>
       </c>
       <c r="H1478" t="n">
         <v>351763</v>
@@ -43289,7 +43289,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1480" t="n">
-        <v>8.60931968688965</v>
+        <v>8.60932064056396</v>
       </c>
       <c r="H1480" t="n">
         <v>438085</v>
@@ -43434,7 +43434,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.60235500335693</v>
+        <v>8.60235404968262</v>
       </c>
       <c r="H1485" t="n">
         <v>155253</v>
@@ -43463,7 +43463,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.56056213378906</v>
+        <v>8.56056118011475</v>
       </c>
       <c r="H1486" t="n">
         <v>250414</v>
@@ -43521,7 +43521,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1488" t="n">
-        <v>8.57449340820312</v>
+        <v>8.57449245452881</v>
       </c>
       <c r="H1488" t="n">
         <v>506369</v>
@@ -43695,7 +43695,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G1494" t="n">
-        <v>9.48000335693359</v>
+        <v>9.48000431060791</v>
       </c>
       <c r="H1494" t="n">
         <v>384832</v>
@@ -43724,7 +43724,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1495" t="n">
-        <v>9.26407432556152</v>
+        <v>9.26407527923584</v>
       </c>
       <c r="H1495" t="n">
         <v>1096191</v>
@@ -44188,7 +44188,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1511" t="n">
-        <v>8.28890800476074</v>
+        <v>8.28890895843506</v>
       </c>
       <c r="H1511" t="n">
         <v>549671</v>
@@ -44217,7 +44217,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1512" t="n">
-        <v>8.25408267974854</v>
+        <v>8.25408172607422</v>
       </c>
       <c r="H1512" t="n">
         <v>500</v>
@@ -44246,7 +44246,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1513" t="n">
-        <v>8.25408267974854</v>
+        <v>8.25408172607422</v>
       </c>
       <c r="H1513" t="n">
         <v>0</v>
@@ -44275,7 +44275,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.25408267974854</v>
+        <v>8.25408172607422</v>
       </c>
       <c r="H1514" t="n">
         <v>0</v>
@@ -44304,7 +44304,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>8.25408267974854</v>
+        <v>8.25408172607422</v>
       </c>
       <c r="H1515" t="n">
         <v>0</v>
@@ -44333,7 +44333,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.25408267974854</v>
+        <v>8.25408172607422</v>
       </c>
       <c r="H1516" t="n">
         <v>0</v>
@@ -44391,7 +44391,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1518" t="n">
-        <v>4.14445400238037</v>
+        <v>4.14445447921753</v>
       </c>
       <c r="H1518" t="n">
         <v>235</v>
@@ -44420,7 +44420,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1519" t="n">
-        <v>4.14445400238037</v>
+        <v>4.14445447921753</v>
       </c>
       <c r="H1519" t="n">
         <v>0</v>
@@ -44971,7 +44971,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.41958999633789</v>
+        <v>4.41959047317505</v>
       </c>
       <c r="H1538" t="n">
         <v>362338</v>
@@ -45116,7 +45116,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.88673186302185</v>
+        <v>3.88673210144043</v>
       </c>
       <c r="H1543" t="n">
         <v>703524</v>
@@ -45174,7 +45174,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.94593858718872</v>
+        <v>3.94593834877014</v>
       </c>
       <c r="H1545" t="n">
         <v>1319274</v>
@@ -45261,7 +45261,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G1548" t="n">
-        <v>3.99469661712646</v>
+        <v>3.99469685554504</v>
       </c>
       <c r="H1548" t="n">
         <v>652185</v>
@@ -45348,7 +45348,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.88324904441833</v>
+        <v>3.88324880599976</v>
       </c>
       <c r="H1551" t="n">
         <v>505887</v>
@@ -45406,7 +45406,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.84842157363892</v>
+        <v>3.8484218120575</v>
       </c>
       <c r="H1553" t="n">
         <v>352453</v>
@@ -45609,7 +45609,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G1560" t="n">
-        <v>3.99469661712646</v>
+        <v>3.99469685554504</v>
       </c>
       <c r="H1560" t="n">
         <v>669338</v>
@@ -45696,7 +45696,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.85538721084595</v>
+        <v>3.85538697242737</v>
       </c>
       <c r="H1563" t="n">
         <v>786782</v>
@@ -45783,7 +45783,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.82056021690369</v>
+        <v>3.82056045532227</v>
       </c>
       <c r="H1566" t="n">
         <v>581531</v>
@@ -45812,7 +45812,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.81707692146301</v>
+        <v>3.81707668304443</v>
       </c>
       <c r="H1567" t="n">
         <v>483994</v>
@@ -45870,7 +45870,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.80662894248962</v>
+        <v>3.8066291809082</v>
       </c>
       <c r="H1569" t="n">
         <v>1090981</v>
@@ -45957,7 +45957,7 @@
         <v>4.75</v>
       </c>
       <c r="G1572" t="n">
-        <v>3.30859756469727</v>
+        <v>3.30859780311584</v>
       </c>
       <c r="H1572" t="n">
         <v>1498535</v>
@@ -46015,7 +46015,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.83449077606201</v>
+        <v>3.83449101448059</v>
       </c>
       <c r="H1574" t="n">
         <v>787193</v>
@@ -46102,7 +46102,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.0887303352356</v>
+        <v>4.08873081207275</v>
       </c>
       <c r="H1577" t="n">
         <v>593839</v>
@@ -46131,7 +46131,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.0887303352356</v>
+        <v>4.08873081207275</v>
       </c>
       <c r="H1578" t="n">
         <v>0</v>
@@ -46160,7 +46160,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.02255868911743</v>
+        <v>4.02255821228027</v>
       </c>
       <c r="H1579" t="n">
         <v>1081936</v>
@@ -46218,7 +46218,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G1581" t="n">
-        <v>3.71607804298401</v>
+        <v>3.71607780456543</v>
       </c>
       <c r="H1581" t="n">
         <v>598602</v>
@@ -46363,7 +46363,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.8135941028595</v>
+        <v>3.81359434127808</v>
       </c>
       <c r="H1586" t="n">
         <v>155370</v>
@@ -46392,7 +46392,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G1587" t="n">
-        <v>3.77876734733582</v>
+        <v>3.77876687049866</v>
       </c>
       <c r="H1587" t="n">
         <v>201555</v>
@@ -46421,7 +46421,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.78224992752075</v>
+        <v>3.78225016593933</v>
       </c>
       <c r="H1588" t="n">
         <v>185640</v>
@@ -46479,7 +46479,7 @@
         <v>5.25</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.65687131881714</v>
+        <v>3.65687155723572</v>
       </c>
       <c r="H1590" t="n">
         <v>667111</v>
@@ -46508,7 +46508,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.6359748840332</v>
+        <v>3.63597464561462</v>
       </c>
       <c r="H1591" t="n">
         <v>468735</v>
@@ -46595,7 +46595,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.29466700553894</v>
+        <v>3.29466676712036</v>
       </c>
       <c r="H1594" t="n">
         <v>1005894</v>
@@ -46624,7 +46624,7 @@
         <v>4.77250003814697</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.32427048683167</v>
+        <v>3.32427024841309</v>
       </c>
       <c r="H1595" t="n">
         <v>480755</v>
@@ -46885,7 +46885,7 @@
         <v>4.625</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.22152948379517</v>
+        <v>3.22152972221375</v>
       </c>
       <c r="H1604" t="n">
         <v>589007</v>
@@ -47146,7 +47146,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.91853189468384</v>
+        <v>2.91853165626526</v>
       </c>
       <c r="H1613" t="n">
         <v>441735</v>
@@ -47204,7 +47204,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G1615" t="n">
-        <v>2.74787759780884</v>
+        <v>2.74787735939026</v>
       </c>
       <c r="H1615" t="n">
         <v>835248</v>
@@ -47262,7 +47262,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.86977338790894</v>
+        <v>2.86977314949036</v>
       </c>
       <c r="H1617" t="n">
         <v>484030</v>
@@ -47407,7 +47407,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.70260214805603</v>
+        <v>2.70260190963745</v>
       </c>
       <c r="H1622" t="n">
         <v>286888</v>
@@ -47465,7 +47465,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1624" t="n">
-        <v>2.69563627243042</v>
+        <v>2.695636510849</v>
       </c>
       <c r="H1624" t="n">
         <v>309942</v>
@@ -47581,7 +47581,7 @@
         <v>3.9449999332428</v>
       </c>
       <c r="G1628" t="n">
-        <v>2.74787759780884</v>
+        <v>2.74787735939026</v>
       </c>
       <c r="H1628" t="n">
         <v>1014229</v>
@@ -47610,7 +47610,7 @@
         <v>3.875</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.69911956787109</v>
+        <v>2.69911932945251</v>
       </c>
       <c r="H1629" t="n">
         <v>457961</v>
@@ -47697,7 +47697,7 @@
         <v>3.85500001907349</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.68518829345703</v>
+        <v>2.68518853187561</v>
       </c>
       <c r="H1632" t="n">
         <v>438317</v>
@@ -47755,7 +47755,7 @@
         <v>3.7425000667572</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.60682702064514</v>
+        <v>2.60682725906372</v>
       </c>
       <c r="H1634" t="n">
         <v>241341</v>
@@ -47871,7 +47871,7 @@
         <v>3.73250007629395</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.59986162185669</v>
+        <v>2.59986138343811</v>
       </c>
       <c r="H1638" t="n">
         <v>581048</v>
@@ -47900,7 +47900,7 @@
         <v>3.52250003814697</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.45358633995056</v>
+        <v>2.45358657836914</v>
       </c>
       <c r="H1639" t="n">
         <v>758159</v>
@@ -47987,7 +47987,7 @@
         <v>3.51250004768372</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.44662094116211</v>
+        <v>2.44662117958069</v>
       </c>
       <c r="H1642" t="n">
         <v>372652</v>
@@ -48045,7 +48045,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.41353535652161</v>
+        <v>2.41353511810303</v>
       </c>
       <c r="H1644" t="n">
         <v>366119</v>
@@ -48103,7 +48103,7 @@
         <v>3.48250007629395</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.42572498321533</v>
+        <v>2.42572474479675</v>
       </c>
       <c r="H1646" t="n">
         <v>213215</v>
@@ -48132,7 +48132,7 @@
         <v>3.40249991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.3700008392334</v>
+        <v>2.37000107765198</v>
       </c>
       <c r="H1647" t="n">
         <v>290840</v>
@@ -48161,7 +48161,7 @@
         <v>3.30749988555908</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.30382919311523</v>
+        <v>2.30382895469666</v>
       </c>
       <c r="H1648" t="n">
         <v>386522</v>
@@ -48451,7 +48451,7 @@
         <v>3.17249989509583</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.20979499816895</v>
+        <v>2.20979523658752</v>
       </c>
       <c r="H1658" t="n">
         <v>320151</v>
@@ -48596,7 +48596,7 @@
         <v>2.96749997138977</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.06700325012207</v>
+        <v>2.06700301170349</v>
       </c>
       <c r="H1663" t="n">
         <v>790704</v>
@@ -48712,7 +48712,7 @@
         <v>3.08750009536743</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.15058875083923</v>
+        <v>2.15058851242065</v>
       </c>
       <c r="H1667" t="n">
         <v>653387</v>
@@ -48886,7 +48886,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.15232992172241</v>
+        <v>2.15233016014099</v>
       </c>
       <c r="H1673" t="n">
         <v>529596</v>
@@ -48944,7 +48944,7 @@
         <v>3.07249999046326</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.14014053344727</v>
+        <v>2.14014029502869</v>
       </c>
       <c r="H1675" t="n">
         <v>465226</v>
@@ -48973,7 +48973,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.0931236743927</v>
+        <v>2.09312343597412</v>
       </c>
       <c r="H1676" t="n">
         <v>690292</v>
@@ -49118,7 +49118,7 @@
         <v>2.94749999046326</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.05307221412659</v>
+        <v>2.05307197570801</v>
       </c>
       <c r="H1681" t="n">
         <v>1208792</v>
@@ -49350,7 +49350,7 @@
         <v>2.87750005722046</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.00431394577026</v>
+        <v>2.00431418418884</v>
       </c>
       <c r="H1689" t="n">
         <v>496914</v>
@@ -49379,7 +49379,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G1690" t="n">
-        <v>2.03043413162231</v>
+        <v>2.03043437004089</v>
       </c>
       <c r="H1690" t="n">
         <v>230224</v>
@@ -49437,7 +49437,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1692" t="n">
-        <v>1.99212419986725</v>
+        <v>1.99212408065796</v>
       </c>
       <c r="H1692" t="n">
         <v>204775</v>
@@ -49495,7 +49495,7 @@
         <v>2.87750005722046</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.00431394577026</v>
+        <v>2.00431418418884</v>
       </c>
       <c r="H1694" t="n">
         <v>402693</v>
@@ -49524,7 +49524,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.01127934455872</v>
+        <v>2.01127910614014</v>
       </c>
       <c r="H1695" t="n">
         <v>394080</v>
@@ -49727,7 +49727,7 @@
         <v>2.78250002861023</v>
       </c>
       <c r="G1702" t="n">
-        <v>1.93814194202423</v>
+        <v>1.93814182281494</v>
       </c>
       <c r="H1702" t="n">
         <v>333178</v>
@@ -49756,7 +49756,7 @@
         <v>2.86249995231628</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.99386560916901</v>
+        <v>1.9938657283783</v>
       </c>
       <c r="H1703" t="n">
         <v>243949</v>
@@ -49785,7 +49785,7 @@
         <v>2.87249994277954</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.00083088874817</v>
+        <v>2.00083112716675</v>
       </c>
       <c r="H1704" t="n">
         <v>167563</v>
@@ -49843,7 +49843,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.89460778236389</v>
+        <v>1.89460790157318</v>
       </c>
       <c r="H1706" t="n">
         <v>796896</v>
@@ -49930,7 +49930,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>1.894899725914</v>
+        <v>1.89489984512329</v>
       </c>
       <c r="H1709" t="n">
         <v>1035736</v>
@@ -50075,7 +50075,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.76960456371307</v>
+        <v>1.76960444450378</v>
       </c>
       <c r="H1714" t="n">
         <v>1138540</v>
@@ -50104,7 +50104,7 @@
         <v>2.25</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.74021410942078</v>
+        <v>1.74021399021149</v>
       </c>
       <c r="H1715" t="n">
         <v>595479</v>
@@ -50162,7 +50162,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.6071845293045</v>
+        <v>1.60718441009521</v>
       </c>
       <c r="H1717" t="n">
         <v>1051607</v>
@@ -50191,7 +50191,7 @@
         <v>2.27099990844727</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.7564560174942</v>
+        <v>1.75645613670349</v>
       </c>
       <c r="H1718" t="n">
         <v>967189</v>
@@ -50307,7 +50307,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G1722" t="n">
-        <v>1.76960456371307</v>
+        <v>1.76960444450378</v>
       </c>
       <c r="H1722" t="n">
         <v>552690</v>
@@ -50481,7 +50481,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.68607425689697</v>
+        <v>1.68607413768768</v>
       </c>
       <c r="H1728" t="n">
         <v>752918</v>
@@ -50597,7 +50597,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.83766603469849</v>
+        <v>1.8376659154892</v>
       </c>
       <c r="H1732" t="n">
         <v>378580</v>
@@ -50684,7 +50684,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.91655588150024</v>
+        <v>1.91655600070953</v>
       </c>
       <c r="H1735" t="n">
         <v>192050</v>
@@ -50713,7 +50713,7 @@
         <v>2.40899991989136</v>
       </c>
       <c r="G1736" t="n">
-        <v>1.86318933963776</v>
+        <v>1.86318922042847</v>
       </c>
       <c r="H1736" t="n">
         <v>293686</v>
@@ -50771,7 +50771,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.90882158279419</v>
+        <v>1.9088214635849</v>
       </c>
       <c r="H1738" t="n">
         <v>510326</v>
@@ -50800,7 +50800,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.95290720462799</v>
+        <v>1.9529070854187</v>
       </c>
       <c r="H1739" t="n">
         <v>365865</v>
@@ -50829,7 +50829,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.96064126491547</v>
+        <v>1.96064114570618</v>
       </c>
       <c r="H1740" t="n">
         <v>380635</v>
@@ -50887,7 +50887,7 @@
         <v>2.43899989128113</v>
       </c>
       <c r="G1742" t="n">
-        <v>1.88639175891876</v>
+        <v>1.88639187812805</v>
       </c>
       <c r="H1742" t="n">
         <v>508838</v>
@@ -50916,7 +50916,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1743" t="n">
-        <v>1.87943136692047</v>
+        <v>1.87943124771118</v>
       </c>
       <c r="H1743" t="n">
         <v>1500465</v>
@@ -50945,7 +50945,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.98771107196808</v>
+        <v>1.98771119117737</v>
       </c>
       <c r="H1744" t="n">
         <v>841864</v>
@@ -50974,7 +50974,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.98771107196808</v>
+        <v>1.98771119117737</v>
       </c>
       <c r="H1745" t="n">
         <v>516489</v>
@@ -51003,7 +51003,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.96837556362152</v>
+        <v>1.96837544441223</v>
       </c>
       <c r="H1746" t="n">
         <v>291255</v>
@@ -51061,7 +51061,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.12306118011475</v>
+        <v>2.12306094169617</v>
       </c>
       <c r="H1748" t="n">
         <v>635042</v>
@@ -51351,7 +51351,7 @@
         <v>2.85249996185303</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.20620489120483</v>
+        <v>2.20620465278625</v>
       </c>
       <c r="H1758" t="n">
         <v>602571</v>
@@ -51409,7 +51409,7 @@
         <v>2.77250003814697</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.1443305015564</v>
+        <v>2.14433026313782</v>
       </c>
       <c r="H1760" t="n">
         <v>295725</v>
@@ -51438,7 +51438,7 @@
         <v>2.80749988555908</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.17140054702759</v>
+        <v>2.17140030860901</v>
       </c>
       <c r="H1761" t="n">
         <v>497603</v>
@@ -51496,7 +51496,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.2120053768158</v>
+        <v>2.21200513839722</v>
       </c>
       <c r="H1763" t="n">
         <v>371800</v>
@@ -51525,7 +51525,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.20427131652832</v>
+        <v>2.20427107810974</v>
       </c>
       <c r="H1764" t="n">
         <v>348195</v>
@@ -51583,7 +51583,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.11726045608521</v>
+        <v>2.11726069450378</v>
       </c>
       <c r="H1766" t="n">
         <v>484370</v>
@@ -51786,7 +51786,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.01864838600159</v>
+        <v>2.01864814758301</v>
       </c>
       <c r="H1773" t="n">
         <v>1155865</v>
@@ -51873,7 +51873,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.11726045608521</v>
+        <v>2.11726069450378</v>
       </c>
       <c r="H1776" t="n">
         <v>347402</v>
@@ -51989,7 +51989,7 @@
         <v>2.77250003814697</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.1443305015564</v>
+        <v>2.14433026313782</v>
       </c>
       <c r="H1780" t="n">
         <v>289941</v>
@@ -52047,7 +52047,7 @@
         <v>2.80749988555908</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.17140054702759</v>
+        <v>2.17140030860901</v>
       </c>
       <c r="H1782" t="n">
         <v>162404</v>
@@ -52134,7 +52134,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.36669135093689</v>
+        <v>2.36669111251831</v>
       </c>
       <c r="H1785" t="n">
         <v>401417</v>
@@ -52163,7 +52163,7 @@
         <v>3.09750008583069</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.39569497108459</v>
+        <v>2.39569473266602</v>
       </c>
       <c r="H1786" t="n">
         <v>329286</v>
@@ -52221,7 +52221,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1788" t="n">
-        <v>2.40149569511414</v>
+        <v>2.40149545669556</v>
       </c>
       <c r="H1788" t="n">
         <v>226241</v>
@@ -52279,7 +52279,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.38989400863647</v>
+        <v>2.3898937702179</v>
       </c>
       <c r="H1790" t="n">
         <v>202155</v>
@@ -52308,7 +52308,7 @@
         <v>2.9925000667572</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.31448483467102</v>
+        <v>2.31448459625244</v>
       </c>
       <c r="H1791" t="n">
         <v>568207</v>
@@ -52366,7 +52366,7 @@
         <v>3.06750011444092</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.37249207496643</v>
+        <v>2.37249183654785</v>
       </c>
       <c r="H1793" t="n">
         <v>333695</v>
@@ -52482,7 +52482,7 @@
         <v>2.9925000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.31448483467102</v>
+        <v>2.31448459625244</v>
       </c>
       <c r="H1797" t="n">
         <v>206747</v>
@@ -52540,7 +52540,7 @@
         <v>2.98749995231628</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.31061768531799</v>
+        <v>2.31061744689941</v>
       </c>
       <c r="H1799" t="n">
         <v>198399</v>
@@ -52598,7 +52598,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G1801" t="n">
-        <v>2.40149569511414</v>
+        <v>2.40149545669556</v>
       </c>
       <c r="H1801" t="n">
         <v>462935</v>
@@ -52627,7 +52627,7 @@
         <v>3.05250000953674</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.36089062690735</v>
+        <v>2.36089038848877</v>
       </c>
       <c r="H1802" t="n">
         <v>270918</v>
@@ -52656,7 +52656,7 @@
         <v>3.11249995231628</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.4072961807251</v>
+        <v>2.40729594230652</v>
       </c>
       <c r="H1803" t="n">
         <v>251554</v>
@@ -52714,7 +52714,7 @@
         <v>3.12249994277954</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.41503047943115</v>
+        <v>2.41503024101257</v>
       </c>
       <c r="H1805" t="n">
         <v>292128</v>
@@ -52743,7 +52743,7 @@
         <v>3.23250007629395</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.50010752677917</v>
+        <v>2.5001072883606</v>
       </c>
       <c r="H1806" t="n">
         <v>462951</v>
@@ -52801,7 +52801,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.59485268592834</v>
+        <v>2.59485244750977</v>
       </c>
       <c r="H1808" t="n">
         <v>365411</v>
@@ -52888,7 +52888,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.56004858016968</v>
+        <v>2.5600483417511</v>
       </c>
       <c r="H1811" t="n">
         <v>246418</v>
@@ -52946,7 +52946,7 @@
         <v>3.20250010490417</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.47690510749817</v>
+        <v>2.47690486907959</v>
       </c>
       <c r="H1813" t="n">
         <v>179088</v>
@@ -53004,7 +53004,7 @@
         <v>3.25</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.51364278793335</v>
+        <v>2.51364254951477</v>
       </c>
       <c r="H1815" t="n">
         <v>162492</v>
@@ -53323,7 +53323,7 @@
         <v>3.30749988555908</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.55811500549316</v>
+        <v>2.55811476707458</v>
       </c>
       <c r="H1826" t="n">
         <v>311873</v>
@@ -53526,7 +53526,7 @@
         <v>3.23250007629395</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.50010752677917</v>
+        <v>2.5001072883606</v>
       </c>
       <c r="H1833" t="n">
         <v>305684</v>
@@ -53613,7 +53613,7 @@
         <v>3.25</v>
       </c>
       <c r="G1836" t="n">
-        <v>2.51364278793335</v>
+        <v>2.51364254951477</v>
       </c>
       <c r="H1836" t="n">
         <v>122762</v>
@@ -53729,7 +53729,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1840" t="n">
-        <v>2.48270559310913</v>
+        <v>2.48270535469055</v>
       </c>
       <c r="H1840" t="n">
         <v>97820</v>
@@ -53758,7 +53758,7 @@
         <v>3.25250005722046</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.51557636260986</v>
+        <v>2.51557612419128</v>
       </c>
       <c r="H1841" t="n">
         <v>108653</v>
@@ -53816,7 +53816,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.44403409957886</v>
+        <v>2.44403386116028</v>
       </c>
       <c r="H1843" t="n">
         <v>136885</v>
@@ -53845,7 +53845,7 @@
         <v>3.12249994277954</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.41503047943115</v>
+        <v>2.41503024101257</v>
       </c>
       <c r="H1844" t="n">
         <v>125118</v>
@@ -53903,7 +53903,7 @@
         <v>3.1875</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.46530342102051</v>
+        <v>2.46530318260193</v>
       </c>
       <c r="H1846" t="n">
         <v>96845</v>
@@ -53961,7 +53961,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.4362998008728</v>
+        <v>2.43629956245422</v>
       </c>
       <c r="H1848" t="n">
         <v>125741</v>
@@ -54106,7 +54106,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.75727272033691</v>
+        <v>2.75727248191833</v>
       </c>
       <c r="H1853" t="n">
         <v>583125</v>
@@ -54135,7 +54135,7 @@
         <v>3.61500000953674</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.79594421386719</v>
+        <v>2.79594397544861</v>
       </c>
       <c r="H1854" t="n">
         <v>248260</v>
@@ -54193,7 +54193,7 @@
         <v>3.58249998092651</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.77080750465393</v>
+        <v>2.77080726623535</v>
       </c>
       <c r="H1856" t="n">
         <v>254276</v>
@@ -54338,7 +54338,7 @@
         <v>3.64750003814697</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.82108044624329</v>
+        <v>2.82108020782471</v>
       </c>
       <c r="H1861" t="n">
         <v>172677</v>
@@ -54425,7 +54425,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.66059422492981</v>
+        <v>2.66059398651123</v>
       </c>
       <c r="H1864" t="n">
         <v>114621</v>
@@ -54512,7 +54512,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.52524423599243</v>
+        <v>2.52524399757385</v>
       </c>
       <c r="H1867" t="n">
         <v>294856</v>
@@ -54860,7 +54860,7 @@
         <v>3.63750004768372</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.81334614753723</v>
+        <v>2.81334590911865</v>
       </c>
       <c r="H1879" t="n">
         <v>504631</v>
@@ -54889,7 +54889,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.75727272033691</v>
+        <v>2.75727248191833</v>
       </c>
       <c r="H1880" t="n">
         <v>146090</v>
@@ -54947,7 +54947,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.66059422492981</v>
+        <v>2.66059398651123</v>
       </c>
       <c r="H1882" t="n">
         <v>287505</v>
@@ -55121,7 +55121,7 @@
         <v>3.25</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.51364278793335</v>
+        <v>2.51364254951477</v>
       </c>
       <c r="H1888" t="n">
         <v>188632</v>
@@ -55150,7 +55150,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.52524423599243</v>
+        <v>2.52524399757385</v>
       </c>
       <c r="H1889" t="n">
         <v>200676</v>
@@ -55237,7 +55237,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.53297853469849</v>
+        <v>2.53297829627991</v>
       </c>
       <c r="H1892" t="n">
         <v>93516</v>
@@ -55266,7 +55266,7 @@
         <v>3.25</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.51364278793335</v>
+        <v>2.51364254951477</v>
       </c>
       <c r="H1893" t="n">
         <v>128228</v>
@@ -55353,7 +55353,7 @@
         <v>3.78250002861023</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.92549347877502</v>
+        <v>2.92549324035645</v>
       </c>
       <c r="H1896" t="n">
         <v>2552057</v>
@@ -55498,7 +55498,7 @@
         <v>3.57249999046326</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.76307344436646</v>
+        <v>2.76307320594788</v>
       </c>
       <c r="H1901" t="n">
         <v>187621</v>
@@ -55527,7 +55527,7 @@
         <v>3.52749991416931</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.72826910018921</v>
+        <v>2.72826886177063</v>
       </c>
       <c r="H1902" t="n">
         <v>192784</v>
@@ -55585,7 +55585,7 @@
         <v>3.46749997138977</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.68186354637146</v>
+        <v>2.68186330795288</v>
       </c>
       <c r="H1904" t="n">
         <v>135933</v>
@@ -55730,7 +55730,7 @@
         <v>3.51250004768372</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.71666789054871</v>
+        <v>2.71666765213013</v>
       </c>
       <c r="H1909" t="n">
         <v>184633</v>
@@ -55759,7 +55759,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.71860146522522</v>
+        <v>2.71860122680664</v>
       </c>
       <c r="H1910" t="n">
         <v>253085</v>
@@ -55875,7 +55875,7 @@
         <v>3.52749991416931</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.72826910018921</v>
+        <v>2.72826886177063</v>
       </c>
       <c r="H1914" t="n">
         <v>237368</v>
@@ -55933,7 +55933,7 @@
         <v>3.63750004768372</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.81334614753723</v>
+        <v>2.81334590911865</v>
       </c>
       <c r="H1916" t="n">
         <v>322345</v>
@@ -56049,7 +56049,7 @@
         <v>3.62750005722046</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.80561208724976</v>
+        <v>2.80561184883118</v>
       </c>
       <c r="H1920" t="n">
         <v>348133</v>
@@ -56078,7 +56078,7 @@
         <v>3.66499996185303</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.83461546897888</v>
+        <v>2.8346152305603</v>
       </c>
       <c r="H1921" t="n">
         <v>241498</v>
@@ -56165,7 +56165,7 @@
         <v>3.55749988555908</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.75147175788879</v>
+        <v>2.75147199630737</v>
       </c>
       <c r="H1924" t="n">
         <v>464210</v>
@@ -80009,6 +80009,35 @@
         <v>334661</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>2.88199996948242</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>2.94199991226196</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>2.84400010108948</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>2.93799996376038</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>2.93799996376038</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>341336</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/MFEB.MI.xlsx
+++ b/data/MFEB.MI.xlsx
@@ -485,7 +485,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G4" t="n">
-        <v>11.0110712051392</v>
+        <v>11.0110702514648</v>
       </c>
       <c r="H4" t="n">
         <v>1268392</v>
@@ -514,7 +514,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G5" t="n">
-        <v>10.9045343399048</v>
+        <v>10.9045333862305</v>
       </c>
       <c r="H5" t="n">
         <v>1852775</v>
@@ -543,7 +543,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G6" t="n">
-        <v>10.7353248596191</v>
+        <v>10.7353239059448</v>
       </c>
       <c r="H6" t="n">
         <v>1139315</v>
@@ -572,7 +572,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G7" t="n">
-        <v>10.2653007507324</v>
+        <v>10.2652997970581</v>
       </c>
       <c r="H7" t="n">
         <v>1391673</v>
@@ -601,7 +601,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G8" t="n">
-        <v>10.4219760894775</v>
+        <v>10.4219751358032</v>
       </c>
       <c r="H8" t="n">
         <v>1579409</v>
@@ -659,7 +659,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G10" t="n">
-        <v>10.1900978088379</v>
+        <v>10.1900987625122</v>
       </c>
       <c r="H10" t="n">
         <v>1503952</v>
@@ -688,7 +688,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G11" t="n">
-        <v>10.0459585189819</v>
+        <v>10.0459575653076</v>
       </c>
       <c r="H11" t="n">
         <v>1539157</v>
@@ -717,7 +717,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G12" t="n">
-        <v>9.70127391815186</v>
+        <v>9.70127296447754</v>
       </c>
       <c r="H12" t="n">
         <v>1418563</v>
@@ -775,7 +775,7 @@
         <v>14.5</v>
       </c>
       <c r="G14" t="n">
-        <v>9.08711051940918</v>
+        <v>9.0871114730835</v>
       </c>
       <c r="H14" t="n">
         <v>2017082</v>
@@ -862,7 +862,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>9.7764778137207</v>
+        <v>9.77647876739502</v>
       </c>
       <c r="H17" t="n">
         <v>1470151</v>
@@ -891,7 +891,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>9.80781173706055</v>
+        <v>9.80781269073486</v>
       </c>
       <c r="H18" t="n">
         <v>2247737</v>
@@ -920,7 +920,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G19" t="n">
-        <v>9.92061710357666</v>
+        <v>9.92061805725098</v>
       </c>
       <c r="H19" t="n">
         <v>1473178</v>
@@ -949,7 +949,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>9.65113830566406</v>
+        <v>9.65113735198975</v>
       </c>
       <c r="H20" t="n">
         <v>1097771</v>
@@ -1007,7 +1007,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G22" t="n">
-        <v>9.86421489715576</v>
+        <v>9.86421585083008</v>
       </c>
       <c r="H22" t="n">
         <v>1301906</v>
@@ -1065,7 +1065,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G24" t="n">
-        <v>9.50699806213379</v>
+        <v>9.50699710845947</v>
       </c>
       <c r="H24" t="n">
         <v>2187286</v>
@@ -1123,7 +1123,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G26" t="n">
-        <v>10.0835590362549</v>
+        <v>10.0835599899292</v>
       </c>
       <c r="H26" t="n">
         <v>2727909</v>
@@ -1152,7 +1152,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G27" t="n">
-        <v>9.19991779327393</v>
+        <v>9.19991588592529</v>
       </c>
       <c r="H27" t="n">
         <v>2096946</v>
@@ -1268,7 +1268,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G31" t="n">
-        <v>9.19364929199219</v>
+        <v>9.19364833831787</v>
       </c>
       <c r="H31" t="n">
         <v>1677204</v>
@@ -1297,7 +1297,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G32" t="n">
-        <v>9.61353588104248</v>
+        <v>9.6135368347168</v>
       </c>
       <c r="H32" t="n">
         <v>1798676</v>
@@ -1384,7 +1384,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G35" t="n">
-        <v>9.80154609680176</v>
+        <v>9.80154705047607</v>
       </c>
       <c r="H35" t="n">
         <v>1040298</v>
@@ -1413,7 +1413,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G36" t="n">
-        <v>10.133695602417</v>
+        <v>10.1336946487427</v>
       </c>
       <c r="H36" t="n">
         <v>3652672</v>
@@ -1442,7 +1442,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G37" t="n">
-        <v>10.2841024398804</v>
+        <v>10.2841033935547</v>
       </c>
       <c r="H37" t="n">
         <v>2085613</v>
@@ -1529,7 +1529,7 @@
         <v>15.75</v>
       </c>
       <c r="G40" t="n">
-        <v>9.8704833984375</v>
+        <v>9.87048244476318</v>
       </c>
       <c r="H40" t="n">
         <v>1605790</v>
@@ -1616,7 +1616,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G43" t="n">
-        <v>10.7603921890259</v>
+        <v>10.7603912353516</v>
       </c>
       <c r="H43" t="n">
         <v>1742306</v>
@@ -1645,7 +1645,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G44" t="n">
-        <v>10.6726560592651</v>
+        <v>10.6726551055908</v>
       </c>
       <c r="H44" t="n">
         <v>1384589</v>
@@ -1674,7 +1674,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G45" t="n">
-        <v>10.9609346389771</v>
+        <v>10.9609355926514</v>
       </c>
       <c r="H45" t="n">
         <v>1699458</v>
@@ -1703,7 +1703,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G46" t="n">
-        <v>10.9609346389771</v>
+        <v>10.9609355926514</v>
       </c>
       <c r="H46" t="n">
         <v>1369819</v>
@@ -1732,7 +1732,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G47" t="n">
-        <v>10.7353248596191</v>
+        <v>10.7353239059448</v>
       </c>
       <c r="H47" t="n">
         <v>1047692</v>
@@ -1848,7 +1848,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G51" t="n">
-        <v>11.5061616897583</v>
+        <v>11.5061626434326</v>
       </c>
       <c r="H51" t="n">
         <v>2312426</v>
@@ -1877,7 +1877,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G52" t="n">
-        <v>11.7380409240723</v>
+        <v>11.7380399703979</v>
       </c>
       <c r="H52" t="n">
         <v>1277405</v>
@@ -1906,7 +1906,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>11.7192392349243</v>
+        <v>11.7192401885986</v>
       </c>
       <c r="H53" t="n">
         <v>1653019</v>
@@ -1935,7 +1935,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G54" t="n">
-        <v>11.6127014160156</v>
+        <v>11.6127004623413</v>
       </c>
       <c r="H54" t="n">
         <v>1634789</v>
@@ -2022,7 +2022,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>11.7192392349243</v>
+        <v>11.7192401885986</v>
       </c>
       <c r="H57" t="n">
         <v>2294980</v>
@@ -2051,7 +2051,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G58" t="n">
-        <v>11.8571119308472</v>
+        <v>11.8571128845215</v>
       </c>
       <c r="H58" t="n">
         <v>1627974</v>
@@ -2080,7 +2080,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G59" t="n">
-        <v>11.4622945785522</v>
+        <v>11.4622936248779</v>
       </c>
       <c r="H59" t="n">
         <v>2571490</v>
@@ -2138,7 +2138,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G61" t="n">
-        <v>10.8857326507568</v>
+        <v>10.8857316970825</v>
       </c>
       <c r="H61" t="n">
         <v>1596311</v>
@@ -2196,7 +2196,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G63" t="n">
-        <v>11.362021446228</v>
+        <v>11.3620223999023</v>
       </c>
       <c r="H63" t="n">
         <v>1901194</v>
@@ -2225,7 +2225,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G64" t="n">
-        <v>11.2116136550903</v>
+        <v>11.2116146087646</v>
       </c>
       <c r="H64" t="n">
         <v>1891974</v>
@@ -2254,7 +2254,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G65" t="n">
-        <v>11.468560218811</v>
+        <v>11.4685611724854</v>
       </c>
       <c r="H65" t="n">
         <v>2065285</v>
@@ -2283,7 +2283,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G66" t="n">
-        <v>10.8167953491211</v>
+        <v>10.8167963027954</v>
       </c>
       <c r="H66" t="n">
         <v>2312805</v>
@@ -2312,7 +2312,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G67" t="n">
-        <v>10.8167953491211</v>
+        <v>10.8167963027954</v>
       </c>
       <c r="H67" t="n">
         <v>1717734</v>
@@ -2515,7 +2515,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>12.1704616546631</v>
+        <v>12.1704607009888</v>
       </c>
       <c r="H74" t="n">
         <v>1750019</v>
@@ -2544,7 +2544,7 @@
         <v>19.6700000762939</v>
       </c>
       <c r="G75" t="n">
-        <v>12.3271360397339</v>
+        <v>12.3271350860596</v>
       </c>
       <c r="H75" t="n">
         <v>1517301</v>
@@ -2631,7 +2631,7 @@
         <v>19.8099994659424</v>
       </c>
       <c r="G78" t="n">
-        <v>12.4148750305176</v>
+        <v>12.4148740768433</v>
       </c>
       <c r="H78" t="n">
         <v>1799957</v>
@@ -2660,7 +2660,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G79" t="n">
-        <v>12.4023399353027</v>
+        <v>12.4023389816284</v>
       </c>
       <c r="H79" t="n">
         <v>935741</v>
@@ -2689,7 +2689,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G80" t="n">
-        <v>12.3835401535034</v>
+        <v>12.3835391998291</v>
       </c>
       <c r="H80" t="n">
         <v>1121472</v>
@@ -2718,7 +2718,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G81" t="n">
-        <v>12.5715475082397</v>
+        <v>12.5715465545654</v>
       </c>
       <c r="H81" t="n">
         <v>1090052</v>
@@ -2747,7 +2747,7 @@
         <v>19.8700008392334</v>
       </c>
       <c r="G82" t="n">
-        <v>12.4524755477905</v>
+        <v>12.4524745941162</v>
       </c>
       <c r="H82" t="n">
         <v>2941463</v>
@@ -2776,7 +2776,7 @@
         <v>20.1100006103516</v>
       </c>
       <c r="G83" t="n">
-        <v>12.6028842926025</v>
+        <v>12.6028833389282</v>
       </c>
       <c r="H83" t="n">
         <v>1049059</v>
@@ -2834,7 +2834,7 @@
         <v>19.4899997711182</v>
       </c>
       <c r="G85" t="n">
-        <v>12.2143306732178</v>
+        <v>12.2143297195435</v>
       </c>
       <c r="H85" t="n">
         <v>1047755</v>
@@ -2863,7 +2863,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>11.9385833740234</v>
+        <v>11.9385843276978</v>
       </c>
       <c r="H86" t="n">
         <v>1411606</v>
@@ -2892,7 +2892,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G87" t="n">
-        <v>11.8195104598999</v>
+        <v>11.8195114135742</v>
       </c>
       <c r="H87" t="n">
         <v>1126967</v>
@@ -2950,7 +2950,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G89" t="n">
-        <v>12.1015243530273</v>
+        <v>12.101523399353</v>
       </c>
       <c r="H89" t="n">
         <v>1016505</v>
@@ -3008,7 +3008,7 @@
         <v>19.5900001525879</v>
       </c>
       <c r="G91" t="n">
-        <v>12.2770004272461</v>
+        <v>12.2769994735718</v>
       </c>
       <c r="H91" t="n">
         <v>942593</v>
@@ -3066,7 +3066,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G93" t="n">
-        <v>11.6440343856812</v>
+        <v>11.6440353393555</v>
       </c>
       <c r="H93" t="n">
         <v>1147356</v>
@@ -3095,7 +3095,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G94" t="n">
-        <v>11.6879043579102</v>
+        <v>11.6879053115845</v>
       </c>
       <c r="H94" t="n">
         <v>884124</v>
@@ -3124,7 +3124,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G95" t="n">
-        <v>11.618968963623</v>
+        <v>11.6189680099487</v>
       </c>
       <c r="H95" t="n">
         <v>783093</v>
@@ -3153,7 +3153,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G96" t="n">
-        <v>11.9699172973633</v>
+        <v>11.9699192047119</v>
       </c>
       <c r="H96" t="n">
         <v>1614264</v>
@@ -3240,7 +3240,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>12.4399423599243</v>
+        <v>12.43994140625</v>
       </c>
       <c r="H99" t="n">
         <v>1053915</v>
@@ -3269,7 +3269,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G100" t="n">
-        <v>12.3580589294434</v>
+        <v>12.3580598831177</v>
       </c>
       <c r="H100" t="n">
         <v>693881</v>
@@ -3298,7 +3298,7 @@
         <v>20</v>
       </c>
       <c r="G101" t="n">
-        <v>12.5974102020264</v>
+        <v>12.5974082946777</v>
       </c>
       <c r="H101" t="n">
         <v>1002511</v>
@@ -3356,7 +3356,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G103" t="n">
-        <v>12.8178634643555</v>
+        <v>12.8178625106812</v>
       </c>
       <c r="H103" t="n">
         <v>814469</v>
@@ -3385,7 +3385,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G104" t="n">
-        <v>12.7233848571777</v>
+        <v>12.7233829498291</v>
       </c>
       <c r="H104" t="n">
         <v>541279</v>
@@ -3414,7 +3414,7 @@
         <v>20.25</v>
       </c>
       <c r="G105" t="n">
-        <v>12.7548761367798</v>
+        <v>12.7548751831055</v>
       </c>
       <c r="H105" t="n">
         <v>260598</v>
@@ -3472,7 +3472,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G107" t="n">
-        <v>12.5722131729126</v>
+        <v>12.5722122192383</v>
       </c>
       <c r="H107" t="n">
         <v>615703</v>
@@ -3530,7 +3530,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G109" t="n">
-        <v>12.3013696670532</v>
+        <v>12.3013715744019</v>
       </c>
       <c r="H109" t="n">
         <v>922911</v>
@@ -3559,7 +3559,7 @@
         <v>19.4099998474121</v>
       </c>
       <c r="G110" t="n">
-        <v>12.2257852554321</v>
+        <v>12.2257843017578</v>
       </c>
       <c r="H110" t="n">
         <v>609987</v>
@@ -3617,7 +3617,7 @@
         <v>19.8299999237061</v>
       </c>
       <c r="G112" t="n">
-        <v>12.4903316497803</v>
+        <v>12.490330696106</v>
       </c>
       <c r="H112" t="n">
         <v>554877</v>
@@ -3733,7 +3733,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G116" t="n">
-        <v>11.1172132492065</v>
+        <v>11.1172122955322</v>
       </c>
       <c r="H116" t="n">
         <v>1212517</v>
@@ -3762,7 +3762,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G117" t="n">
-        <v>11.066822052002</v>
+        <v>11.0668230056763</v>
       </c>
       <c r="H117" t="n">
         <v>1136973</v>
@@ -3791,7 +3791,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G118" t="n">
-        <v>11.02903175354</v>
+        <v>11.0290327072144</v>
       </c>
       <c r="H118" t="n">
         <v>1101905</v>
@@ -3820,7 +3820,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G119" t="n">
-        <v>11.3628635406494</v>
+        <v>11.3628644943237</v>
       </c>
       <c r="H119" t="n">
         <v>1010646</v>
@@ -3849,7 +3849,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>11.9045505523682</v>
+        <v>11.9045515060425</v>
       </c>
       <c r="H120" t="n">
         <v>1061050</v>
@@ -3878,7 +3878,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G121" t="n">
-        <v>11.942343711853</v>
+        <v>11.9423446655273</v>
       </c>
       <c r="H121" t="n">
         <v>777222</v>
@@ -3907,7 +3907,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G122" t="n">
-        <v>11.7155904769897</v>
+        <v>11.7155895233154</v>
       </c>
       <c r="H122" t="n">
         <v>789206</v>
@@ -3936,7 +3936,7 @@
         <v>19.6299991607666</v>
       </c>
       <c r="G123" t="n">
-        <v>12.3643560409546</v>
+        <v>12.3643550872803</v>
       </c>
       <c r="H123" t="n">
         <v>1016975</v>
@@ -3994,7 +3994,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G125" t="n">
-        <v>9.54883575439453</v>
+        <v>9.54883670806885</v>
       </c>
       <c r="H125" t="n">
         <v>2002294</v>
@@ -4023,7 +4023,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G126" t="n">
-        <v>9.8070821762085</v>
+        <v>9.80708312988281</v>
       </c>
       <c r="H126" t="n">
         <v>1326585</v>
@@ -4081,7 +4081,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G128" t="n">
-        <v>9.86377143859863</v>
+        <v>9.86377048492432</v>
       </c>
       <c r="H128" t="n">
         <v>1849568</v>
@@ -4110,7 +4110,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G129" t="n">
-        <v>10.0842266082764</v>
+        <v>10.0842256546021</v>
       </c>
       <c r="H129" t="n">
         <v>1099550</v>
@@ -4139,7 +4139,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G130" t="n">
-        <v>9.62442016601562</v>
+        <v>9.62441921234131</v>
       </c>
       <c r="H130" t="n">
         <v>727152</v>
@@ -4168,7 +4168,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G131" t="n">
-        <v>9.80078506469727</v>
+        <v>9.80078411102295</v>
       </c>
       <c r="H131" t="n">
         <v>1415622</v>
@@ -4255,7 +4255,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G134" t="n">
-        <v>10.1094198226929</v>
+        <v>10.1094207763672</v>
       </c>
       <c r="H134" t="n">
         <v>1393609</v>
@@ -4313,7 +4313,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G136" t="n">
-        <v>10.7959794998169</v>
+        <v>10.7959785461426</v>
       </c>
       <c r="H136" t="n">
         <v>933358</v>
@@ -4371,7 +4371,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G138" t="n">
-        <v>10.4684476852417</v>
+        <v>10.4684467315674</v>
       </c>
       <c r="H138" t="n">
         <v>951907</v>
@@ -4400,7 +4400,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G139" t="n">
-        <v>10.3676671981812</v>
+        <v>10.3676662445068</v>
       </c>
       <c r="H139" t="n">
         <v>641452</v>
@@ -4429,7 +4429,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>10.3613691329956</v>
+        <v>10.3613681793213</v>
       </c>
       <c r="H140" t="n">
         <v>663026</v>
@@ -4458,7 +4458,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G141" t="n">
-        <v>10.1724071502686</v>
+        <v>10.1724081039429</v>
       </c>
       <c r="H141" t="n">
         <v>672156</v>
@@ -4574,7 +4574,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G145" t="n">
-        <v>10.1724071502686</v>
+        <v>10.1724081039429</v>
       </c>
       <c r="H145" t="n">
         <v>511193</v>
@@ -4632,7 +4632,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>9.57402992248535</v>
+        <v>9.57403087615967</v>
       </c>
       <c r="H147" t="n">
         <v>1504123</v>
@@ -4661,7 +4661,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G148" t="n">
-        <v>9.30318737030029</v>
+        <v>9.30318546295166</v>
       </c>
       <c r="H148" t="n">
         <v>1171880</v>
@@ -4690,7 +4690,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G149" t="n">
-        <v>8.52844619750977</v>
+        <v>8.52844524383545</v>
       </c>
       <c r="H149" t="n">
         <v>5005510</v>
@@ -4719,7 +4719,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G150" t="n">
-        <v>8.40247249603271</v>
+        <v>8.4024715423584</v>
       </c>
       <c r="H150" t="n">
         <v>1987814</v>
@@ -4748,7 +4748,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G151" t="n">
-        <v>8.16312122344971</v>
+        <v>8.16312026977539</v>
       </c>
       <c r="H151" t="n">
         <v>1918096</v>
@@ -4806,7 +4806,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G153" t="n">
-        <v>8.40877056121826</v>
+        <v>8.40877151489258</v>
       </c>
       <c r="H153" t="n">
         <v>1451640</v>
@@ -4835,7 +4835,7 @@
         <v>13.75</v>
       </c>
       <c r="G154" t="n">
-        <v>8.66071891784668</v>
+        <v>8.66071796417236</v>
       </c>
       <c r="H154" t="n">
         <v>1634919</v>
@@ -5038,7 +5038,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G161" t="n">
-        <v>8.40877056121826</v>
+        <v>8.40877151489258</v>
       </c>
       <c r="H161" t="n">
         <v>784925</v>
@@ -5067,7 +5067,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G162" t="n">
-        <v>8.82448482513428</v>
+        <v>8.82448577880859</v>
       </c>
       <c r="H162" t="n">
         <v>2037809</v>
@@ -5096,7 +5096,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G163" t="n">
-        <v>8.64812088012695</v>
+        <v>8.64812183380127</v>
       </c>
       <c r="H163" t="n">
         <v>1223699</v>
@@ -5125,7 +5125,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G164" t="n">
-        <v>8.6859130859375</v>
+        <v>8.68591403961182</v>
       </c>
       <c r="H164" t="n">
         <v>1585086</v>
@@ -5212,7 +5212,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G167" t="n">
-        <v>8.99454975128174</v>
+        <v>8.99454879760742</v>
       </c>
       <c r="H167" t="n">
         <v>1182183</v>
@@ -5241,7 +5241,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G168" t="n">
-        <v>8.95045852661133</v>
+        <v>8.95045948028564</v>
       </c>
       <c r="H168" t="n">
         <v>1311813</v>
@@ -5328,7 +5328,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G171" t="n">
-        <v>8.93156242370605</v>
+        <v>8.93156337738037</v>
       </c>
       <c r="H171" t="n">
         <v>931270</v>
@@ -5386,7 +5386,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G173" t="n">
-        <v>9.24649810791016</v>
+        <v>9.24649906158447</v>
       </c>
       <c r="H173" t="n">
         <v>1284363</v>
@@ -5444,7 +5444,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G175" t="n">
-        <v>9.20870494842529</v>
+        <v>9.20870590209961</v>
       </c>
       <c r="H175" t="n">
         <v>1096481</v>
@@ -5473,7 +5473,7 @@
         <v>14.75</v>
       </c>
       <c r="G176" t="n">
-        <v>9.29058837890625</v>
+        <v>9.29059028625488</v>
       </c>
       <c r="H176" t="n">
         <v>996378</v>
@@ -5502,7 +5502,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24649810791016</v>
+        <v>9.24649906158447</v>
       </c>
       <c r="H177" t="n">
         <v>829964</v>
@@ -5531,7 +5531,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G178" t="n">
-        <v>9.10162830352783</v>
+        <v>9.10162734985352</v>
       </c>
       <c r="H178" t="n">
         <v>950590</v>
@@ -5589,7 +5589,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G180" t="n">
-        <v>8.54104423522949</v>
+        <v>8.54104328155518</v>
       </c>
       <c r="H180" t="n">
         <v>1625492</v>
@@ -5618,7 +5618,7 @@
         <v>13.75</v>
       </c>
       <c r="G181" t="n">
-        <v>8.66071891784668</v>
+        <v>8.66071796417236</v>
       </c>
       <c r="H181" t="n">
         <v>1384896</v>
@@ -5705,7 +5705,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G184" t="n">
-        <v>8.82448482513428</v>
+        <v>8.82448577880859</v>
       </c>
       <c r="H184" t="n">
         <v>723788</v>
@@ -5734,7 +5734,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G185" t="n">
-        <v>8.52844619750977</v>
+        <v>8.52844524383545</v>
       </c>
       <c r="H185" t="n">
         <v>869473</v>
@@ -5763,7 +5763,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G186" t="n">
-        <v>8.54734134674072</v>
+        <v>8.54734230041504</v>
       </c>
       <c r="H186" t="n">
         <v>651282</v>
@@ -5792,7 +5792,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G187" t="n">
-        <v>8.64812088012695</v>
+        <v>8.64812183380127</v>
       </c>
       <c r="H187" t="n">
         <v>723230</v>
@@ -5821,7 +5821,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G188" t="n">
-        <v>8.76149845123291</v>
+        <v>8.76149749755859</v>
       </c>
       <c r="H188" t="n">
         <v>922708</v>
@@ -5879,7 +5879,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G190" t="n">
-        <v>8.6859130859375</v>
+        <v>8.68591403961182</v>
       </c>
       <c r="H190" t="n">
         <v>801255</v>
@@ -5966,7 +5966,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G193" t="n">
-        <v>8.79928970336914</v>
+        <v>8.79929065704346</v>
       </c>
       <c r="H193" t="n">
         <v>1335974</v>
@@ -6024,7 +6024,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G195" t="n">
-        <v>8.81188774108887</v>
+        <v>8.81188678741455</v>
       </c>
       <c r="H195" t="n">
         <v>844305</v>
@@ -6111,7 +6111,7 @@
         <v>13.5</v>
       </c>
       <c r="G198" t="n">
-        <v>8.50325107574463</v>
+        <v>8.50325012207031</v>
       </c>
       <c r="H198" t="n">
         <v>1227203</v>
@@ -6140,7 +6140,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G199" t="n">
-        <v>8.54734134674072</v>
+        <v>8.54734230041504</v>
       </c>
       <c r="H199" t="n">
         <v>1379248</v>
@@ -6227,7 +6227,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G202" t="n">
-        <v>8.20721054077148</v>
+        <v>8.2072114944458</v>
       </c>
       <c r="H202" t="n">
         <v>2787358</v>
@@ -6285,7 +6285,7 @@
         <v>13.25</v>
       </c>
       <c r="G204" t="n">
-        <v>8.34578323364258</v>
+        <v>8.34578418731689</v>
       </c>
       <c r="H204" t="n">
         <v>1011092</v>
@@ -6343,7 +6343,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G206" t="n">
-        <v>8.54104423522949</v>
+        <v>8.54104328155518</v>
       </c>
       <c r="H206" t="n">
         <v>730084</v>
@@ -6401,7 +6401,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G208" t="n">
-        <v>8.23240566253662</v>
+        <v>8.23240661621094</v>
       </c>
       <c r="H208" t="n">
         <v>1267545</v>
@@ -6430,7 +6430,7 @@
         <v>13.25</v>
       </c>
       <c r="G209" t="n">
-        <v>8.34578323364258</v>
+        <v>8.34578418731689</v>
       </c>
       <c r="H209" t="n">
         <v>1227739</v>
@@ -6459,7 +6459,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G210" t="n">
-        <v>8.26389980316162</v>
+        <v>8.2638988494873</v>
       </c>
       <c r="H210" t="n">
         <v>1092158</v>
@@ -6517,7 +6517,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>8.27019882202148</v>
+        <v>8.27019786834717</v>
       </c>
       <c r="H212" t="n">
         <v>1220444</v>
@@ -6546,7 +6546,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G213" t="n">
-        <v>8.20091438293457</v>
+        <v>8.20091247558594</v>
       </c>
       <c r="H213" t="n">
         <v>1298636</v>
@@ -6575,7 +6575,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G214" t="n">
-        <v>8.20091438293457</v>
+        <v>8.20091247558594</v>
       </c>
       <c r="H214" t="n">
         <v>1141131</v>
@@ -6604,7 +6604,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G215" t="n">
-        <v>8.15682315826416</v>
+        <v>8.15682220458984</v>
       </c>
       <c r="H215" t="n">
         <v>1115334</v>
@@ -6633,7 +6633,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>7.84188604354858</v>
+        <v>7.8418869972229</v>
       </c>
       <c r="H216" t="n">
         <v>2063953</v>
@@ -6662,7 +6662,7 @@
         <v>12.25</v>
       </c>
       <c r="G217" t="n">
-        <v>7.71591281890869</v>
+        <v>7.71591329574585</v>
       </c>
       <c r="H217" t="n">
         <v>2414557</v>
@@ -6691,7 +6691,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G218" t="n">
-        <v>7.62143278121948</v>
+        <v>7.62143182754517</v>
       </c>
       <c r="H218" t="n">
         <v>1128128</v>
@@ -6720,7 +6720,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G219" t="n">
-        <v>7.64032888412476</v>
+        <v>7.6403284072876</v>
       </c>
       <c r="H219" t="n">
         <v>923117</v>
@@ -6749,7 +6749,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G220" t="n">
-        <v>7.62143278121948</v>
+        <v>7.62143182754517</v>
       </c>
       <c r="H220" t="n">
         <v>795000</v>
@@ -6807,7 +6807,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G222" t="n">
-        <v>7.36318492889404</v>
+        <v>7.3631854057312</v>
       </c>
       <c r="H222" t="n">
         <v>1639210</v>
@@ -6865,7 +6865,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G224" t="n">
-        <v>7.36318492889404</v>
+        <v>7.3631854057312</v>
       </c>
       <c r="H224" t="n">
         <v>1415172</v>
@@ -6981,7 +6981,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G228" t="n">
-        <v>7.18052339553833</v>
+        <v>7.18052291870117</v>
       </c>
       <c r="H228" t="n">
         <v>1611437</v>
@@ -7068,7 +7068,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G231" t="n">
-        <v>7.28760004043579</v>
+        <v>7.28760147094727</v>
       </c>
       <c r="H231" t="n">
         <v>896267</v>
@@ -7126,7 +7126,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G233" t="n">
-        <v>7.23721122741699</v>
+        <v>7.23721075057983</v>
       </c>
       <c r="H233" t="n">
         <v>831731</v>
@@ -7155,7 +7155,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G234" t="n">
-        <v>7.04195117950439</v>
+        <v>7.04195213317871</v>
       </c>
       <c r="H234" t="n">
         <v>1442837</v>
@@ -7184,7 +7184,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G235" t="n">
-        <v>7.19312047958374</v>
+        <v>7.19312000274658</v>
       </c>
       <c r="H235" t="n">
         <v>1191850</v>
@@ -7213,7 +7213,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G236" t="n">
-        <v>7.1994194984436</v>
+        <v>7.19941902160645</v>
       </c>
       <c r="H236" t="n">
         <v>1209794</v>
@@ -7271,7 +7271,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G238" t="n">
-        <v>7.48916006088257</v>
+        <v>7.48915958404541</v>
       </c>
       <c r="H238" t="n">
         <v>2229232</v>
@@ -7358,7 +7358,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G241" t="n">
-        <v>8.16312122344971</v>
+        <v>8.16312026977539</v>
       </c>
       <c r="H241" t="n">
         <v>2106761</v>
@@ -7503,7 +7503,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G246" t="n">
-        <v>11.4006567001343</v>
+        <v>11.4006547927856</v>
       </c>
       <c r="H246" t="n">
         <v>16601084</v>
@@ -7532,7 +7532,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G247" t="n">
-        <v>11.2242908477783</v>
+        <v>11.224289894104</v>
       </c>
       <c r="H247" t="n">
         <v>9584317</v>
@@ -7677,7 +7677,7 @@
         <v>20</v>
       </c>
       <c r="G252" t="n">
-        <v>12.5974102020264</v>
+        <v>12.5974082946777</v>
       </c>
       <c r="H252" t="n">
         <v>10849610</v>
@@ -7735,7 +7735,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G254" t="n">
-        <v>12.9816303253174</v>
+        <v>12.9816312789917</v>
       </c>
       <c r="H254" t="n">
         <v>5467799</v>
@@ -7764,7 +7764,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G255" t="n">
-        <v>12.8871469497681</v>
+        <v>12.8871479034424</v>
       </c>
       <c r="H255" t="n">
         <v>3550302</v>
@@ -7793,7 +7793,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G256" t="n">
-        <v>12.8178634643555</v>
+        <v>12.8178625106812</v>
       </c>
       <c r="H256" t="n">
         <v>1834829</v>
@@ -7851,7 +7851,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G258" t="n">
-        <v>13.0761108398438</v>
+        <v>13.0761098861694</v>
       </c>
       <c r="H258" t="n">
         <v>1847315</v>
@@ -7880,7 +7880,7 @@
         <v>20.5</v>
       </c>
       <c r="G259" t="n">
-        <v>12.9123449325562</v>
+        <v>12.9123439788818</v>
       </c>
       <c r="H259" t="n">
         <v>4140544</v>
@@ -7967,7 +7967,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>13.1327981948853</v>
+        <v>13.1327991485596</v>
       </c>
       <c r="H262" t="n">
         <v>1497601</v>
@@ -8054,7 +8054,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G265" t="n">
-        <v>13.7374725341797</v>
+        <v>13.737473487854</v>
       </c>
       <c r="H265" t="n">
         <v>5695306</v>
@@ -8083,7 +8083,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G266" t="n">
-        <v>13.1894874572754</v>
+        <v>13.1894865036011</v>
       </c>
       <c r="H266" t="n">
         <v>2794844</v>
@@ -8170,7 +8170,7 @@
         <v>20.8700008392334</v>
       </c>
       <c r="G269" t="n">
-        <v>13.1453981399536</v>
+        <v>13.1453971862793</v>
       </c>
       <c r="H269" t="n">
         <v>3203978</v>
@@ -8199,7 +8199,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G270" t="n">
-        <v>13.258770942688</v>
+        <v>13.2587728500366</v>
       </c>
       <c r="H270" t="n">
         <v>1563844</v>
@@ -8257,7 +8257,7 @@
         <v>21.3400001525879</v>
       </c>
       <c r="G272" t="n">
-        <v>13.4414358139038</v>
+        <v>13.4414348602295</v>
       </c>
       <c r="H272" t="n">
         <v>2196155</v>
@@ -8286,7 +8286,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G273" t="n">
-        <v>13.302864074707</v>
+        <v>13.3028650283813</v>
       </c>
       <c r="H273" t="n">
         <v>1658398</v>
@@ -8315,7 +8315,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>13.2902679443359</v>
+        <v>13.2902669906616</v>
       </c>
       <c r="H274" t="n">
         <v>1838822</v>
@@ -8344,7 +8344,7 @@
         <v>20.5</v>
       </c>
       <c r="G275" t="n">
-        <v>12.9123449325562</v>
+        <v>12.9123439788818</v>
       </c>
       <c r="H275" t="n">
         <v>1805725</v>
@@ -8402,7 +8402,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G277" t="n">
-        <v>12.8997468948364</v>
+        <v>12.8997459411621</v>
       </c>
       <c r="H277" t="n">
         <v>475230</v>
@@ -8460,7 +8460,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G279" t="n">
-        <v>12.4588384628296</v>
+        <v>12.4588375091553</v>
       </c>
       <c r="H279" t="n">
         <v>878876</v>
@@ -8489,7 +8489,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>12.3769540786743</v>
+        <v>12.3769550323486</v>
       </c>
       <c r="H280" t="n">
         <v>860032</v>
@@ -8518,7 +8518,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>12.4714345932007</v>
+        <v>12.4714336395264</v>
       </c>
       <c r="H281" t="n">
         <v>661827</v>
@@ -8576,7 +8576,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G283" t="n">
-        <v>12.1627969741821</v>
+        <v>12.1627979278564</v>
       </c>
       <c r="H283" t="n">
         <v>869754</v>
@@ -8605,7 +8605,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G284" t="n">
-        <v>11.9990329742432</v>
+        <v>11.9990310668945</v>
       </c>
       <c r="H284" t="n">
         <v>1146615</v>
@@ -8692,7 +8692,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G287" t="n">
-        <v>12.1439018249512</v>
+        <v>12.1439027786255</v>
       </c>
       <c r="H287" t="n">
         <v>562772</v>
@@ -8721,7 +8721,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3832521438599</v>
+        <v>12.3832530975342</v>
       </c>
       <c r="H288" t="n">
         <v>901859</v>
@@ -8750,7 +8750,7 @@
         <v>19.5</v>
       </c>
       <c r="G289" t="n">
-        <v>12.2824735641479</v>
+        <v>12.2824726104736</v>
       </c>
       <c r="H289" t="n">
         <v>786441</v>
@@ -8779,7 +8779,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G290" t="n">
-        <v>12.1439018249512</v>
+        <v>12.1439027786255</v>
       </c>
       <c r="H290" t="n">
         <v>685389</v>
@@ -8837,7 +8837,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G292" t="n">
-        <v>12.4336433410645</v>
+        <v>12.4336423873901</v>
       </c>
       <c r="H292" t="n">
         <v>1478762</v>
@@ -8866,7 +8866,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G293" t="n">
-        <v>12.4084463119507</v>
+        <v>12.4084482192993</v>
       </c>
       <c r="H293" t="n">
         <v>575906</v>
@@ -8895,7 +8895,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G294" t="n">
-        <v>12.553318977356</v>
+        <v>12.5533180236816</v>
       </c>
       <c r="H294" t="n">
         <v>948237</v>
@@ -8982,7 +8982,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G297" t="n">
-        <v>12.0998115539551</v>
+        <v>12.0998106002808</v>
       </c>
       <c r="H297" t="n">
         <v>832241</v>
@@ -9040,7 +9040,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G299" t="n">
-        <v>12.2383842468262</v>
+        <v>12.2383832931519</v>
       </c>
       <c r="H299" t="n">
         <v>586693</v>
@@ -9098,7 +9098,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G301" t="n">
-        <v>12.2509803771973</v>
+        <v>12.2509813308716</v>
       </c>
       <c r="H301" t="n">
         <v>657783</v>
@@ -9127,7 +9127,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G302" t="n">
-        <v>12.1564998626709</v>
+        <v>12.1564989089966</v>
       </c>
       <c r="H302" t="n">
         <v>657498</v>
@@ -9156,7 +9156,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G303" t="n">
-        <v>12.1313047409058</v>
+        <v>12.1313037872314</v>
       </c>
       <c r="H303" t="n">
         <v>566595</v>
@@ -9214,7 +9214,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G305" t="n">
-        <v>12.3580589294434</v>
+        <v>12.3580598831177</v>
       </c>
       <c r="H305" t="n">
         <v>950220</v>
@@ -9272,7 +9272,7 @@
         <v>20.1299991607666</v>
       </c>
       <c r="G307" t="n">
-        <v>12.6792917251587</v>
+        <v>12.6792907714844</v>
       </c>
       <c r="H307" t="n">
         <v>967060</v>
@@ -9330,7 +9330,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G309" t="n">
-        <v>12.4588384628296</v>
+        <v>12.4588375091553</v>
       </c>
       <c r="H309" t="n">
         <v>755947</v>
@@ -9388,7 +9388,7 @@
         <v>19.75</v>
       </c>
       <c r="G311" t="n">
-        <v>12.4399423599243</v>
+        <v>12.43994140625</v>
       </c>
       <c r="H311" t="n">
         <v>1169141</v>
@@ -9417,7 +9417,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>12.4084463119507</v>
+        <v>12.4084482192993</v>
       </c>
       <c r="H312" t="n">
         <v>4763949</v>
@@ -9475,7 +9475,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G314" t="n">
-        <v>12.2698755264282</v>
+        <v>12.2698764801025</v>
       </c>
       <c r="H314" t="n">
         <v>1016442</v>
@@ -9504,7 +9504,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G315" t="n">
-        <v>12.1061096191406</v>
+        <v>12.1061086654663</v>
       </c>
       <c r="H315" t="n">
         <v>957590</v>
@@ -9533,7 +9533,7 @@
         <v>19.25</v>
       </c>
       <c r="G316" t="n">
-        <v>12.1250047683716</v>
+        <v>12.1250057220459</v>
       </c>
       <c r="H316" t="n">
         <v>638721</v>
@@ -9736,7 +9736,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G323" t="n">
-        <v>12.0935115814209</v>
+        <v>12.0935134887695</v>
       </c>
       <c r="H323" t="n">
         <v>566698</v>
@@ -9794,7 +9794,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>11.9360466003418</v>
+        <v>11.9360456466675</v>
       </c>
       <c r="H325" t="n">
         <v>943255</v>
@@ -9823,7 +9823,7 @@
         <v>18.7299995422363</v>
       </c>
       <c r="G326" t="n">
-        <v>11.7974729537964</v>
+        <v>11.7974720001221</v>
       </c>
       <c r="H326" t="n">
         <v>1226932</v>
@@ -9852,7 +9852,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G327" t="n">
-        <v>11.5833177566528</v>
+        <v>11.5833168029785</v>
       </c>
       <c r="H327" t="n">
         <v>1032334</v>
@@ -9881,7 +9881,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G328" t="n">
-        <v>11.6022138595581</v>
+        <v>11.6022148132324</v>
       </c>
       <c r="H328" t="n">
         <v>1065647</v>
@@ -9939,7 +9939,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>11.5455236434937</v>
+        <v>11.545524597168</v>
       </c>
       <c r="H330" t="n">
         <v>472290</v>
@@ -9968,7 +9968,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G331" t="n">
-        <v>11.4384469985962</v>
+        <v>11.4384460449219</v>
       </c>
       <c r="H331" t="n">
         <v>651493</v>
@@ -10084,7 +10084,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G335" t="n">
-        <v>11.4258489608765</v>
+        <v>11.4258499145508</v>
       </c>
       <c r="H335" t="n">
         <v>1502737</v>
@@ -10113,7 +10113,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>12.0305261611938</v>
+        <v>12.0305252075195</v>
       </c>
       <c r="H336" t="n">
         <v>1527622</v>
@@ -10142,7 +10142,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G337" t="n">
-        <v>12.1187086105347</v>
+        <v>12.1187076568604</v>
       </c>
       <c r="H337" t="n">
         <v>986622</v>
@@ -10258,7 +10258,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G341" t="n">
-        <v>11.7092914581299</v>
+        <v>11.7092924118042</v>
       </c>
       <c r="H341" t="n">
         <v>1283272</v>
@@ -10316,7 +10316,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G343" t="n">
-        <v>11.5770196914673</v>
+        <v>11.577018737793</v>
       </c>
       <c r="H343" t="n">
         <v>577148</v>
@@ -10345,7 +10345,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G344" t="n">
-        <v>11.6589021682739</v>
+        <v>11.6589012145996</v>
       </c>
       <c r="H344" t="n">
         <v>854951</v>
@@ -10432,7 +10432,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G347" t="n">
-        <v>11.8730583190918</v>
+        <v>11.8730573654175</v>
       </c>
       <c r="H347" t="n">
         <v>736647</v>
@@ -10461,7 +10461,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>11.5833177566528</v>
+        <v>11.5833168029785</v>
       </c>
       <c r="H348" t="n">
         <v>939676</v>
@@ -10548,7 +10548,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>11.6840963363647</v>
+        <v>11.6840953826904</v>
       </c>
       <c r="H351" t="n">
         <v>951645</v>
@@ -10577,7 +10577,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G352" t="n">
-        <v>11.4384469985962</v>
+        <v>11.4384460449219</v>
       </c>
       <c r="H352" t="n">
         <v>917669</v>
@@ -10606,7 +10606,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G353" t="n">
-        <v>11.4762382507324</v>
+        <v>11.4762401580811</v>
       </c>
       <c r="H353" t="n">
         <v>907620</v>
@@ -10635,7 +10635,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G354" t="n">
-        <v>11.4258489608765</v>
+        <v>11.4258499145508</v>
       </c>
       <c r="H354" t="n">
         <v>734812</v>
@@ -10664,7 +10664,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G355" t="n">
-        <v>11.3880577087402</v>
+        <v>11.3880586624146</v>
       </c>
       <c r="H355" t="n">
         <v>552045</v>
@@ -10693,7 +10693,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G356" t="n">
-        <v>11.3754596710205</v>
+        <v>11.3754587173462</v>
       </c>
       <c r="H356" t="n">
         <v>506210</v>
@@ -10722,7 +10722,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G357" t="n">
-        <v>11.3502645492554</v>
+        <v>11.3502655029297</v>
       </c>
       <c r="H357" t="n">
         <v>471915</v>
@@ -10838,7 +10838,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G361" t="n">
-        <v>11.5896158218384</v>
+        <v>11.5896148681641</v>
       </c>
       <c r="H361" t="n">
         <v>1128647</v>
@@ -10867,7 +10867,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G362" t="n">
-        <v>11.066822052002</v>
+        <v>11.0668230056763</v>
       </c>
       <c r="H362" t="n">
         <v>2149371</v>
@@ -10896,7 +10896,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G363" t="n">
-        <v>11.110915184021</v>
+        <v>11.1109142303467</v>
       </c>
       <c r="H363" t="n">
         <v>587033</v>
@@ -10983,7 +10983,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G366" t="n">
-        <v>10.9282512664795</v>
+        <v>10.9282531738281</v>
       </c>
       <c r="H366" t="n">
         <v>767011</v>
@@ -11041,7 +11041,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G368" t="n">
-        <v>10.9282512664795</v>
+        <v>10.9282531738281</v>
       </c>
       <c r="H368" t="n">
         <v>481370</v>
@@ -11099,7 +11099,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G370" t="n">
-        <v>10.903058052063</v>
+        <v>10.9030570983887</v>
       </c>
       <c r="H370" t="n">
         <v>687443</v>
@@ -11186,7 +11186,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G373" t="n">
-        <v>10.9912405014038</v>
+        <v>10.9912395477295</v>
       </c>
       <c r="H373" t="n">
         <v>501531</v>
@@ -11244,7 +11244,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G375" t="n">
-        <v>10.8400707244873</v>
+        <v>10.840069770813</v>
       </c>
       <c r="H375" t="n">
         <v>484837</v>
@@ -11331,7 +11331,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G378" t="n">
-        <v>10.9282512664795</v>
+        <v>10.9282531738281</v>
       </c>
       <c r="H378" t="n">
         <v>677469</v>
@@ -11360,7 +11360,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G379" t="n">
-        <v>10.9912405014038</v>
+        <v>10.9912395477295</v>
       </c>
       <c r="H379" t="n">
         <v>789328</v>
@@ -11418,7 +11418,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G381" t="n">
-        <v>10.7959794998169</v>
+        <v>10.7959785461426</v>
       </c>
       <c r="H381" t="n">
         <v>439358</v>
@@ -11447,7 +11447,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G382" t="n">
-        <v>11.0731220245361</v>
+        <v>11.0731210708618</v>
       </c>
       <c r="H382" t="n">
         <v>714915</v>
@@ -11476,7 +11476,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.0101337432861</v>
+        <v>11.0101346969604</v>
       </c>
       <c r="H383" t="n">
         <v>571437</v>
@@ -11505,7 +11505,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G384" t="n">
-        <v>10.8400707244873</v>
+        <v>10.840069770813</v>
       </c>
       <c r="H384" t="n">
         <v>546106</v>
@@ -11534,7 +11534,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>10.7707843780518</v>
+        <v>10.7707834243774</v>
       </c>
       <c r="H385" t="n">
         <v>486323</v>
@@ -11650,7 +11650,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G389" t="n">
-        <v>10.1409149169922</v>
+        <v>10.1409139633179</v>
       </c>
       <c r="H389" t="n">
         <v>1318386</v>
@@ -11679,7 +11679,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G390" t="n">
-        <v>10.0716276168823</v>
+        <v>10.0716285705566</v>
       </c>
       <c r="H390" t="n">
         <v>658861</v>
@@ -11737,7 +11737,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>10.2983818054199</v>
+        <v>10.2983808517456</v>
       </c>
       <c r="H392" t="n">
         <v>685967</v>
@@ -11824,7 +11824,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G395" t="n">
-        <v>10.4873418807983</v>
+        <v>10.487343788147</v>
       </c>
       <c r="H395" t="n">
         <v>517663</v>
@@ -11853,7 +11853,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>10.4873418807983</v>
+        <v>10.487343788147</v>
       </c>
       <c r="H396" t="n">
         <v>414782</v>
@@ -11969,7 +11969,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G400" t="n">
-        <v>10.4936418533325</v>
+        <v>10.4936408996582</v>
       </c>
       <c r="H400" t="n">
         <v>514449</v>
@@ -12085,7 +12085,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>10.4936418533325</v>
+        <v>10.4936408996582</v>
       </c>
       <c r="H404" t="n">
         <v>558214</v>
@@ -12143,7 +12143,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G406" t="n">
-        <v>10.3424730300903</v>
+        <v>10.342472076416</v>
       </c>
       <c r="H406" t="n">
         <v>677671</v>
@@ -12172,7 +12172,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>10.4558506011963</v>
+        <v>10.455849647522</v>
       </c>
       <c r="H407" t="n">
         <v>564518</v>
@@ -12346,7 +12346,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G413" t="n">
-        <v>10.7959794998169</v>
+        <v>10.7959785461426</v>
       </c>
       <c r="H413" t="n">
         <v>343194</v>
@@ -12375,7 +12375,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G414" t="n">
-        <v>10.5566282272339</v>
+        <v>10.5566291809082</v>
       </c>
       <c r="H414" t="n">
         <v>511632</v>
@@ -12404,7 +12404,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G415" t="n">
-        <v>10.632212638855</v>
+        <v>10.6322116851807</v>
       </c>
       <c r="H415" t="n">
         <v>287188</v>
@@ -12433,7 +12433,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G416" t="n">
-        <v>10.72669506073</v>
+        <v>10.7266941070557</v>
       </c>
       <c r="H416" t="n">
         <v>478602</v>
@@ -12491,7 +12491,7 @@
         <v>17.1100006103516</v>
       </c>
       <c r="G418" t="n">
-        <v>10.7770824432373</v>
+        <v>10.7770833969116</v>
       </c>
       <c r="H418" t="n">
         <v>507115</v>
@@ -12549,7 +12549,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G420" t="n">
-        <v>10.6826028823853</v>
+        <v>10.6826019287109</v>
       </c>
       <c r="H420" t="n">
         <v>545700</v>
@@ -12578,7 +12578,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G421" t="n">
-        <v>10.4999408721924</v>
+        <v>10.4999399185181</v>
       </c>
       <c r="H421" t="n">
         <v>597099</v>
@@ -12694,7 +12694,7 @@
         <v>15.7299995422363</v>
       </c>
       <c r="G425" t="n">
-        <v>9.90786075592041</v>
+        <v>9.90786170959473</v>
       </c>
       <c r="H425" t="n">
         <v>1248740</v>
@@ -12781,7 +12781,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G428" t="n">
-        <v>9.70000457763672</v>
+        <v>9.70000553131104</v>
       </c>
       <c r="H428" t="n">
         <v>1183632</v>
@@ -12810,7 +12810,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G429" t="n">
-        <v>9.56143474578857</v>
+        <v>9.56143379211426</v>
       </c>
       <c r="H429" t="n">
         <v>597460</v>
@@ -12839,7 +12839,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G430" t="n">
-        <v>9.61182308197021</v>
+        <v>9.61182403564453</v>
       </c>
       <c r="H430" t="n">
         <v>653766</v>
@@ -12955,7 +12955,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G434" t="n">
-        <v>9.7314977645874</v>
+        <v>9.73149871826172</v>
       </c>
       <c r="H434" t="n">
         <v>1177278</v>
@@ -12984,7 +12984,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G435" t="n">
-        <v>9.74409580230713</v>
+        <v>9.74409675598145</v>
       </c>
       <c r="H435" t="n">
         <v>781903</v>
@@ -13042,7 +13042,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G437" t="n">
-        <v>9.22130393981934</v>
+        <v>9.22130298614502</v>
       </c>
       <c r="H437" t="n">
         <v>2834103</v>
@@ -13129,7 +13129,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G440" t="n">
-        <v>9.11422443389893</v>
+        <v>9.11422538757324</v>
       </c>
       <c r="H440" t="n">
         <v>1161398</v>
@@ -13187,7 +13187,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G442" t="n">
-        <v>9.14571952819824</v>
+        <v>9.14571857452393</v>
       </c>
       <c r="H442" t="n">
         <v>822692</v>
@@ -13245,7 +13245,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G444" t="n">
-        <v>9.24649810791016</v>
+        <v>9.24649906158447</v>
       </c>
       <c r="H444" t="n">
         <v>1396726</v>
@@ -13274,7 +13274,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G445" t="n">
-        <v>9.1646146774292</v>
+        <v>9.16461563110352</v>
       </c>
       <c r="H445" t="n">
         <v>1078891</v>
@@ -13361,7 +13361,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G448" t="n">
-        <v>9.22130393981934</v>
+        <v>9.22130298614502</v>
       </c>
       <c r="H448" t="n">
         <v>775718</v>
@@ -13477,7 +13477,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G452" t="n">
-        <v>9.1646146774292</v>
+        <v>9.16461563110352</v>
       </c>
       <c r="H452" t="n">
         <v>1037224</v>
@@ -13593,7 +13593,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G456" t="n">
-        <v>10.0212383270264</v>
+        <v>10.0212392807007</v>
       </c>
       <c r="H456" t="n">
         <v>2272470</v>
@@ -13651,7 +13651,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G458" t="n">
-        <v>10.040135383606</v>
+        <v>10.0401344299316</v>
       </c>
       <c r="H458" t="n">
         <v>1416943</v>
@@ -13709,7 +13709,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G460" t="n">
-        <v>9.80078506469727</v>
+        <v>9.80078411102295</v>
       </c>
       <c r="H460" t="n">
         <v>1073135</v>
@@ -13796,7 +13796,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G463" t="n">
-        <v>9.66851139068604</v>
+        <v>9.66851043701172</v>
       </c>
       <c r="H463" t="n">
         <v>619673</v>
@@ -13825,7 +13825,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G464" t="n">
-        <v>9.52993965148926</v>
+        <v>9.52994060516357</v>
       </c>
       <c r="H464" t="n">
         <v>531753</v>
@@ -13854,7 +13854,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>9.57402992248535</v>
+        <v>9.57403087615967</v>
       </c>
       <c r="H465" t="n">
         <v>627759</v>
@@ -13941,7 +13941,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G468" t="n">
-        <v>9.74409580230713</v>
+        <v>9.74409675598145</v>
       </c>
       <c r="H468" t="n">
         <v>1599671</v>
@@ -13970,7 +13970,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G469" t="n">
-        <v>9.70000457763672</v>
+        <v>9.70000553131104</v>
       </c>
       <c r="H469" t="n">
         <v>1464694</v>
@@ -13999,7 +13999,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G470" t="n">
-        <v>9.93305778503418</v>
+        <v>9.93305587768555</v>
       </c>
       <c r="H470" t="n">
         <v>1990808</v>
@@ -14028,7 +14028,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>9.88896656036377</v>
+        <v>9.88896560668945</v>
       </c>
       <c r="H471" t="n">
         <v>1054168</v>
@@ -14057,7 +14057,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G472" t="n">
-        <v>9.66851139068604</v>
+        <v>9.66851043701172</v>
       </c>
       <c r="H472" t="n">
         <v>1368308</v>
@@ -14086,7 +14086,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G473" t="n">
-        <v>9.70630264282227</v>
+        <v>9.70630359649658</v>
       </c>
       <c r="H473" t="n">
         <v>818435</v>
@@ -14115,7 +14115,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>9.70000457763672</v>
+        <v>9.70000553131104</v>
       </c>
       <c r="H474" t="n">
         <v>944720</v>
@@ -14202,7 +14202,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G477" t="n">
-        <v>9.08273220062256</v>
+        <v>9.08273124694824</v>
       </c>
       <c r="H477" t="n">
         <v>1138318</v>
@@ -14231,7 +14231,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G478" t="n">
-        <v>8.96305561065674</v>
+        <v>8.96305656433105</v>
       </c>
       <c r="H478" t="n">
         <v>1330328</v>
@@ -14376,7 +14376,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G483" t="n">
-        <v>9.26539325714111</v>
+        <v>9.26539421081543</v>
       </c>
       <c r="H483" t="n">
         <v>804106</v>
@@ -14434,7 +14434,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G485" t="n">
-        <v>9.61182308197021</v>
+        <v>9.61182403564453</v>
       </c>
       <c r="H485" t="n">
         <v>1125880</v>
@@ -14492,7 +14492,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G487" t="n">
-        <v>9.68740653991699</v>
+        <v>9.68740749359131</v>
       </c>
       <c r="H487" t="n">
         <v>718545</v>
@@ -14521,7 +14521,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G488" t="n">
-        <v>10.0842266082764</v>
+        <v>10.0842256546021</v>
       </c>
       <c r="H488" t="n">
         <v>4395102</v>
@@ -14579,7 +14579,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G490" t="n">
-        <v>10.1346158981323</v>
+        <v>10.134614944458</v>
       </c>
       <c r="H490" t="n">
         <v>1236071</v>
@@ -14753,7 +14753,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>10.1724071502686</v>
+        <v>10.1724081039429</v>
       </c>
       <c r="H496" t="n">
         <v>1387530</v>
@@ -14869,7 +14869,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G500" t="n">
-        <v>10.5566282272339</v>
+        <v>10.5566291809082</v>
       </c>
       <c r="H500" t="n">
         <v>1405049</v>
@@ -14956,7 +14956,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G503" t="n">
-        <v>10.3424730300903</v>
+        <v>10.342472076416</v>
       </c>
       <c r="H503" t="n">
         <v>1295184</v>
@@ -14985,7 +14985,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G504" t="n">
-        <v>10.0968246459961</v>
+        <v>10.0968236923218</v>
       </c>
       <c r="H504" t="n">
         <v>1554916</v>
@@ -15014,7 +15014,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G505" t="n">
-        <v>10.185004234314</v>
+        <v>10.1850051879883</v>
       </c>
       <c r="H505" t="n">
         <v>670433</v>
@@ -15159,7 +15159,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G510" t="n">
-        <v>10.185004234314</v>
+        <v>10.1850051879883</v>
       </c>
       <c r="H510" t="n">
         <v>407999</v>
@@ -15188,7 +15188,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>10.1724071502686</v>
+        <v>10.1724081039429</v>
       </c>
       <c r="H511" t="n">
         <v>297422</v>
@@ -15217,7 +15217,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G512" t="n">
-        <v>10.1346158981323</v>
+        <v>10.134614944458</v>
       </c>
       <c r="H512" t="n">
         <v>442380</v>
@@ -15304,7 +15304,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>10.581823348999</v>
+        <v>10.5818243026733</v>
       </c>
       <c r="H515" t="n">
         <v>746394</v>
@@ -15362,7 +15362,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G517" t="n">
-        <v>10.4306535720825</v>
+        <v>10.4306545257568</v>
       </c>
       <c r="H517" t="n">
         <v>693437</v>
@@ -15391,7 +15391,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G518" t="n">
-        <v>10.3613691329956</v>
+        <v>10.3613681793213</v>
       </c>
       <c r="H518" t="n">
         <v>675134</v>
@@ -15507,7 +15507,7 @@
         <v>16.2900009155273</v>
       </c>
       <c r="G522" t="n">
-        <v>10.260591506958</v>
+        <v>10.2605905532837</v>
       </c>
       <c r="H522" t="n">
         <v>668306</v>
@@ -15565,7 +15565,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G524" t="n">
-        <v>10.247992515564</v>
+        <v>10.2479934692383</v>
       </c>
       <c r="H524" t="n">
         <v>663049</v>
@@ -15594,7 +15594,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G525" t="n">
-        <v>10.1157178878784</v>
+        <v>10.1157188415527</v>
       </c>
       <c r="H525" t="n">
         <v>1106081</v>
@@ -15623,7 +15623,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G526" t="n">
-        <v>10.3865623474121</v>
+        <v>10.3865633010864</v>
       </c>
       <c r="H526" t="n">
         <v>5455851</v>
@@ -15681,7 +15681,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>10.2983818054199</v>
+        <v>10.2983808517456</v>
       </c>
       <c r="H528" t="n">
         <v>776164</v>
@@ -15797,7 +15797,7 @@
         <v>16.0249996185303</v>
       </c>
       <c r="G532" t="n">
-        <v>10.093674659729</v>
+        <v>10.0936737060547</v>
       </c>
       <c r="H532" t="n">
         <v>908548</v>
@@ -15826,7 +15826,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G533" t="n">
-        <v>10.0842266082764</v>
+        <v>10.0842256546021</v>
       </c>
       <c r="H533" t="n">
         <v>799128</v>
@@ -15855,7 +15855,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G534" t="n">
-        <v>10.040135383606</v>
+        <v>10.0401344299316</v>
       </c>
       <c r="H534" t="n">
         <v>742592</v>
@@ -15913,7 +15913,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>9.70000457763672</v>
+        <v>9.70000553131104</v>
       </c>
       <c r="H536" t="n">
         <v>1285745</v>
@@ -15971,7 +15971,7 @@
         <v>15.8149995803833</v>
       </c>
       <c r="G538" t="n">
-        <v>9.96140098571777</v>
+        <v>9.96140003204346</v>
       </c>
       <c r="H538" t="n">
         <v>1763664</v>
@@ -16058,7 +16058,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G541" t="n">
-        <v>9.75669288635254</v>
+        <v>9.75669193267822</v>
       </c>
       <c r="H541" t="n">
         <v>729219</v>
@@ -16087,7 +16087,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G542" t="n">
-        <v>9.74409580230713</v>
+        <v>9.74409675598145</v>
       </c>
       <c r="H542" t="n">
         <v>967398</v>
@@ -16116,7 +16116,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G543" t="n">
-        <v>9.89211463928223</v>
+        <v>9.89211559295654</v>
       </c>
       <c r="H543" t="n">
         <v>1004805</v>
@@ -16145,7 +16145,7 @@
         <v>15.8649997711182</v>
       </c>
       <c r="G544" t="n">
-        <v>9.99289417266846</v>
+        <v>9.99289512634277</v>
       </c>
       <c r="H544" t="n">
         <v>553212</v>
@@ -16174,7 +16174,7 @@
         <v>16.2250003814697</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2196483612061</v>
+        <v>10.2196474075317</v>
       </c>
       <c r="H545" t="n">
         <v>805177</v>
@@ -16319,7 +16319,7 @@
         <v>15.8649997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>9.99289417266846</v>
+        <v>9.99289512634277</v>
       </c>
       <c r="H550" t="n">
         <v>408311</v>
@@ -16435,7 +16435,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G554" t="n">
-        <v>9.99604415893555</v>
+        <v>9.99604320526123</v>
       </c>
       <c r="H554" t="n">
         <v>540965</v>
@@ -16551,7 +16551,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G558" t="n">
-        <v>9.62442016601562</v>
+        <v>9.62441921234131</v>
       </c>
       <c r="H558" t="n">
         <v>793641</v>
@@ -16638,7 +16638,7 @@
         <v>16.4050006866455</v>
       </c>
       <c r="G561" t="n">
-        <v>10.3330240249634</v>
+        <v>10.3330249786377</v>
       </c>
       <c r="H561" t="n">
         <v>1564944</v>
@@ -16667,7 +16667,7 @@
         <v>15.7250003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>9.90471267700195</v>
+        <v>9.90471363067627</v>
       </c>
       <c r="H562" t="n">
         <v>2067483</v>
@@ -16696,7 +16696,7 @@
         <v>15.4250001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>9.71575260162354</v>
+        <v>9.71575164794922</v>
       </c>
       <c r="H563" t="n">
         <v>1198414</v>
@@ -16725,7 +16725,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G564" t="n">
-        <v>9.78818511962891</v>
+        <v>9.78818702697754</v>
       </c>
       <c r="H564" t="n">
         <v>678905</v>
@@ -16812,7 +16812,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G567" t="n">
-        <v>9.75039291381836</v>
+        <v>9.75039386749268</v>
       </c>
       <c r="H567" t="n">
         <v>372040</v>
@@ -16841,7 +16841,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G568" t="n">
-        <v>9.55198574066162</v>
+        <v>9.5519847869873</v>
       </c>
       <c r="H568" t="n">
         <v>1192123</v>
@@ -16870,7 +16870,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G569" t="n">
-        <v>9.5992259979248</v>
+        <v>9.59922504425049</v>
       </c>
       <c r="H569" t="n">
         <v>700086</v>
@@ -16928,7 +16928,7 @@
         <v>14.8549995422363</v>
       </c>
       <c r="G571" t="n">
-        <v>9.35672473907471</v>
+        <v>9.35672569274902</v>
       </c>
       <c r="H571" t="n">
         <v>789684</v>
@@ -17015,7 +17015,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G574" t="n">
-        <v>9.80078506469727</v>
+        <v>9.80078411102295</v>
       </c>
       <c r="H574" t="n">
         <v>986113</v>
@@ -17044,7 +17044,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G575" t="n">
-        <v>10.4306535720825</v>
+        <v>10.4306545257568</v>
       </c>
       <c r="H575" t="n">
         <v>6151477</v>
@@ -17131,7 +17131,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G578" t="n">
-        <v>10.4936418533325</v>
+        <v>10.4936408996582</v>
       </c>
       <c r="H578" t="n">
         <v>906470</v>
@@ -17189,7 +17189,7 @@
         <v>16.6949996948242</v>
       </c>
       <c r="G580" t="n">
-        <v>10.5156869888306</v>
+        <v>10.5156860351562</v>
       </c>
       <c r="H580" t="n">
         <v>1212365</v>
@@ -17218,7 +17218,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G581" t="n">
-        <v>10.2290945053101</v>
+        <v>10.2290954589844</v>
       </c>
       <c r="H581" t="n">
         <v>1139633</v>
@@ -17247,7 +17247,7 @@
         <v>16.2250003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>10.2196483612061</v>
+        <v>10.2196474075317</v>
       </c>
       <c r="H582" t="n">
         <v>744064</v>
@@ -17305,7 +17305,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G584" t="n">
-        <v>10.247992515564</v>
+        <v>10.2479934692383</v>
       </c>
       <c r="H584" t="n">
         <v>597697</v>
@@ -17363,7 +17363,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G586" t="n">
-        <v>10.3708162307739</v>
+        <v>10.3708171844482</v>
       </c>
       <c r="H586" t="n">
         <v>592387</v>
@@ -17450,7 +17450,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G589" t="n">
-        <v>10.4275045394897</v>
+        <v>10.4275054931641</v>
       </c>
       <c r="H589" t="n">
         <v>599454</v>
@@ -17624,7 +17624,7 @@
         <v>16.5450000762939</v>
       </c>
       <c r="G595" t="n">
-        <v>10.4212074279785</v>
+        <v>10.4212064743042</v>
       </c>
       <c r="H595" t="n">
         <v>848180</v>
@@ -17682,7 +17682,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G597" t="n">
-        <v>10.6196174621582</v>
+        <v>10.6196155548096</v>
       </c>
       <c r="H597" t="n">
         <v>1593073</v>
@@ -17711,7 +17711,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G598" t="n">
-        <v>10.6448097229004</v>
+        <v>10.6448106765747</v>
       </c>
       <c r="H598" t="n">
         <v>854131</v>
@@ -17769,7 +17769,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>10.3613691329956</v>
+        <v>10.3613681793213</v>
       </c>
       <c r="H600" t="n">
         <v>875701</v>
@@ -17827,7 +17827,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G602" t="n">
-        <v>10.3613691329956</v>
+        <v>10.3613681793213</v>
       </c>
       <c r="H602" t="n">
         <v>490285</v>
@@ -17856,7 +17856,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G603" t="n">
-        <v>10.4558506011963</v>
+        <v>10.455849647522</v>
       </c>
       <c r="H603" t="n">
         <v>595792</v>
@@ -18001,7 +18001,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G608" t="n">
-        <v>9.61182308197021</v>
+        <v>9.61182403564453</v>
       </c>
       <c r="H608" t="n">
         <v>623141</v>
@@ -18030,7 +18030,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G609" t="n">
-        <v>9.61182308197021</v>
+        <v>9.61182403564453</v>
       </c>
       <c r="H609" t="n">
         <v>567987</v>
@@ -18059,7 +18059,7 @@
         <v>15.3050003051758</v>
       </c>
       <c r="G610" t="n">
-        <v>9.64016819000244</v>
+        <v>9.64016723632812</v>
       </c>
       <c r="H610" t="n">
         <v>670845</v>
@@ -18175,7 +18175,7 @@
         <v>13.875</v>
       </c>
       <c r="G614" t="n">
-        <v>8.73945236206055</v>
+        <v>8.73945331573486</v>
       </c>
       <c r="H614" t="n">
         <v>1657795</v>
@@ -18262,7 +18262,7 @@
         <v>14.4449996948242</v>
       </c>
       <c r="G617" t="n">
-        <v>9.09847927093506</v>
+        <v>9.09847831726074</v>
       </c>
       <c r="H617" t="n">
         <v>736954</v>
@@ -18291,7 +18291,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G618" t="n">
-        <v>9.15201759338379</v>
+        <v>9.15201663970947</v>
       </c>
       <c r="H618" t="n">
         <v>362744</v>
@@ -18349,7 +18349,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G620" t="n">
-        <v>9.0921802520752</v>
+        <v>9.09218120574951</v>
       </c>
       <c r="H620" t="n">
         <v>525850</v>
@@ -18378,7 +18378,7 @@
         <v>14.3050003051758</v>
       </c>
       <c r="G621" t="n">
-        <v>9.01029586791992</v>
+        <v>9.01029682159424</v>
       </c>
       <c r="H621" t="n">
         <v>521054</v>
@@ -18436,7 +18436,7 @@
         <v>14.3050003051758</v>
       </c>
       <c r="G623" t="n">
-        <v>9.01029586791992</v>
+        <v>9.01029682159424</v>
       </c>
       <c r="H623" t="n">
         <v>646951</v>
@@ -18523,7 +18523,7 @@
         <v>14.3649997711182</v>
       </c>
       <c r="G626" t="n">
-        <v>9.04808807373047</v>
+        <v>9.04808902740479</v>
       </c>
       <c r="H626" t="n">
         <v>303853</v>
@@ -18552,7 +18552,7 @@
         <v>14.2550001144409</v>
       </c>
       <c r="G627" t="n">
-        <v>8.97880458831787</v>
+        <v>8.97880363464355</v>
       </c>
       <c r="H627" t="n">
         <v>611734</v>
@@ -18581,7 +18581,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G628" t="n">
-        <v>9.00714683532715</v>
+        <v>9.00714778900146</v>
       </c>
       <c r="H628" t="n">
         <v>381465</v>
@@ -18610,7 +18610,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G629" t="n">
-        <v>9.00714683532715</v>
+        <v>9.00714778900146</v>
       </c>
       <c r="H629" t="n">
         <v>704717</v>
@@ -18697,7 +18697,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G632" t="n">
-        <v>9.0921802520752</v>
+        <v>9.09218120574951</v>
       </c>
       <c r="H632" t="n">
         <v>752017</v>
@@ -18784,7 +18784,7 @@
         <v>14.375</v>
       </c>
       <c r="G635" t="n">
-        <v>9.05438709259033</v>
+        <v>9.05438613891602</v>
       </c>
       <c r="H635" t="n">
         <v>852977</v>
@@ -18900,7 +18900,7 @@
         <v>12.8549995422363</v>
       </c>
       <c r="G639" t="n">
-        <v>8.09698390960693</v>
+        <v>8.09698486328125</v>
       </c>
       <c r="H639" t="n">
         <v>1080026</v>
@@ -18958,7 +18958,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G641" t="n">
-        <v>8.21351051330566</v>
+        <v>8.21351146697998</v>
       </c>
       <c r="H641" t="n">
         <v>1367622</v>
@@ -18987,7 +18987,7 @@
         <v>13.2849998474121</v>
       </c>
       <c r="G642" t="n">
-        <v>8.36782836914062</v>
+        <v>8.36782932281494</v>
       </c>
       <c r="H642" t="n">
         <v>1114059</v>
@@ -19103,7 +19103,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G646" t="n">
-        <v>8.73630332946777</v>
+        <v>8.73630237579346</v>
       </c>
       <c r="H646" t="n">
         <v>497935</v>
@@ -19132,7 +19132,7 @@
         <v>13.7650003433228</v>
       </c>
       <c r="G647" t="n">
-        <v>8.670166015625</v>
+        <v>8.67016696929932</v>
       </c>
       <c r="H647" t="n">
         <v>380312</v>
@@ -19219,7 +19219,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G650" t="n">
-        <v>8.84023094177246</v>
+        <v>8.84023189544678</v>
       </c>
       <c r="H650" t="n">
         <v>507802</v>
@@ -19248,7 +19248,7 @@
         <v>13.8649997711182</v>
       </c>
       <c r="G651" t="n">
-        <v>8.73315334320068</v>
+        <v>8.733154296875</v>
       </c>
       <c r="H651" t="n">
         <v>355288</v>
@@ -19277,7 +19277,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G652" t="n">
-        <v>8.79928970336914</v>
+        <v>8.79929065704346</v>
       </c>
       <c r="H652" t="n">
         <v>490461</v>
@@ -19422,7 +19422,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G657" t="n">
-        <v>9.10162830352783</v>
+        <v>9.10162734985352</v>
       </c>
       <c r="H657" t="n">
         <v>762491</v>
@@ -19480,7 +19480,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G659" t="n">
-        <v>9.14257049560547</v>
+        <v>9.14256954193115</v>
       </c>
       <c r="H659" t="n">
         <v>567304</v>
@@ -19509,7 +19509,7 @@
         <v>14.375</v>
       </c>
       <c r="G660" t="n">
-        <v>9.05438709259033</v>
+        <v>9.05438613891602</v>
       </c>
       <c r="H660" t="n">
         <v>286353</v>
@@ -19596,7 +19596,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G663" t="n">
-        <v>8.8213357925415</v>
+        <v>8.82133483886719</v>
       </c>
       <c r="H663" t="n">
         <v>226667</v>
@@ -19654,7 +19654,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G665" t="n">
-        <v>8.98195362091064</v>
+        <v>8.98195266723633</v>
       </c>
       <c r="H665" t="n">
         <v>370059</v>
@@ -19712,7 +19712,7 @@
         <v>13.914999961853</v>
       </c>
       <c r="G667" t="n">
-        <v>8.76464748382568</v>
+        <v>8.7646484375</v>
       </c>
       <c r="H667" t="n">
         <v>321962</v>
@@ -19741,7 +19741,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G668" t="n">
-        <v>8.71740627288818</v>
+        <v>8.7174072265625</v>
       </c>
       <c r="H668" t="n">
         <v>211818</v>
@@ -19886,7 +19886,7 @@
         <v>13.4750003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>8.48750495910645</v>
+        <v>8.48750400543213</v>
       </c>
       <c r="H673" t="n">
         <v>769111</v>
@@ -20002,7 +20002,7 @@
         <v>13.3249998092651</v>
       </c>
       <c r="G677" t="n">
-        <v>8.39302349090576</v>
+        <v>8.39302444458008</v>
       </c>
       <c r="H677" t="n">
         <v>327923</v>
@@ -20089,7 +20089,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G680" t="n">
-        <v>8.20091438293457</v>
+        <v>8.20091247558594</v>
       </c>
       <c r="H680" t="n">
         <v>316909</v>
@@ -20176,7 +20176,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G683" t="n">
-        <v>7.80724477767944</v>
+        <v>7.80724382400513</v>
       </c>
       <c r="H683" t="n">
         <v>796554</v>
@@ -20205,7 +20205,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G684" t="n">
-        <v>7.78519868850708</v>
+        <v>7.78519821166992</v>
       </c>
       <c r="H684" t="n">
         <v>1126358</v>
@@ -20234,7 +20234,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G685" t="n">
-        <v>7.75370502471924</v>
+        <v>7.75370454788208</v>
       </c>
       <c r="H685" t="n">
         <v>319739</v>
@@ -20263,7 +20263,7 @@
         <v>12.3249998092651</v>
       </c>
       <c r="G686" t="n">
-        <v>7.76315259933472</v>
+        <v>7.76315355300903</v>
       </c>
       <c r="H686" t="n">
         <v>305034</v>
@@ -20321,7 +20321,7 @@
         <v>12.4849996566772</v>
       </c>
       <c r="G688" t="n">
-        <v>7.86393213272095</v>
+        <v>7.86393165588379</v>
       </c>
       <c r="H688" t="n">
         <v>883562</v>
@@ -20350,7 +20350,7 @@
         <v>12.664999961853</v>
       </c>
       <c r="G689" t="n">
-        <v>7.97730922698975</v>
+        <v>7.97730875015259</v>
       </c>
       <c r="H689" t="n">
         <v>901715</v>
@@ -20379,7 +20379,7 @@
         <v>12.6549997329712</v>
       </c>
       <c r="G690" t="n">
-        <v>7.9710111618042</v>
+        <v>7.97101020812988</v>
       </c>
       <c r="H690" t="n">
         <v>605862</v>
@@ -20408,7 +20408,7 @@
         <v>12.7550001144409</v>
       </c>
       <c r="G691" t="n">
-        <v>8.03399753570557</v>
+        <v>8.03399848937988</v>
       </c>
       <c r="H691" t="n">
         <v>575207</v>
@@ -20437,7 +20437,7 @@
         <v>13.125</v>
       </c>
       <c r="G692" t="n">
-        <v>8.26704883575439</v>
+        <v>8.26704978942871</v>
       </c>
       <c r="H692" t="n">
         <v>864788</v>
@@ -20466,7 +20466,7 @@
         <v>13.125</v>
       </c>
       <c r="G693" t="n">
-        <v>8.26704883575439</v>
+        <v>8.26704978942871</v>
       </c>
       <c r="H693" t="n">
         <v>511540</v>
@@ -20524,7 +20524,7 @@
         <v>13.0249996185303</v>
       </c>
       <c r="G695" t="n">
-        <v>8.20406246185303</v>
+        <v>8.20406150817871</v>
       </c>
       <c r="H695" t="n">
         <v>604172</v>
@@ -20553,7 +20553,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G696" t="n">
-        <v>8.25760078430176</v>
+        <v>8.25760173797607</v>
       </c>
       <c r="H696" t="n">
         <v>613406</v>
@@ -20582,7 +20582,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G697" t="n">
-        <v>8.26389980316162</v>
+        <v>8.2638988494873</v>
       </c>
       <c r="H697" t="n">
         <v>359749</v>
@@ -20669,7 +20669,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G700" t="n">
-        <v>8.76149845123291</v>
+        <v>8.76149749755859</v>
       </c>
       <c r="H700" t="n">
         <v>856266</v>
@@ -20843,7 +20843,7 @@
         <v>13.7849998474121</v>
       </c>
       <c r="G706" t="n">
-        <v>8.68276309967041</v>
+        <v>8.68276405334473</v>
       </c>
       <c r="H706" t="n">
         <v>635632</v>
@@ -20901,7 +20901,7 @@
         <v>13.4449996948242</v>
       </c>
       <c r="G708" t="n">
-        <v>8.46860694885254</v>
+        <v>8.46860790252686</v>
       </c>
       <c r="H708" t="n">
         <v>322604</v>
@@ -20959,7 +20959,7 @@
         <v>13.125</v>
       </c>
       <c r="G710" t="n">
-        <v>8.26704883575439</v>
+        <v>8.26704978942871</v>
       </c>
       <c r="H710" t="n">
         <v>535848</v>
@@ -20988,7 +20988,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G711" t="n">
-        <v>8.27019882202148</v>
+        <v>8.27019786834717</v>
       </c>
       <c r="H711" t="n">
         <v>406875</v>
@@ -21046,7 +21046,7 @@
         <v>13.6350002288818</v>
       </c>
       <c r="G713" t="n">
-        <v>8.58828353881836</v>
+        <v>8.58828258514404</v>
       </c>
       <c r="H713" t="n">
         <v>379575</v>
@@ -21104,7 +21104,7 @@
         <v>12.9449996948242</v>
       </c>
       <c r="G715" t="n">
-        <v>8.15367317199707</v>
+        <v>8.15367221832275</v>
       </c>
       <c r="H715" t="n">
         <v>695107</v>
@@ -21133,7 +21133,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G716" t="n">
-        <v>8.20091438293457</v>
+        <v>8.20091247558594</v>
       </c>
       <c r="H716" t="n">
         <v>538122</v>
@@ -21220,7 +21220,7 @@
         <v>12.75</v>
       </c>
       <c r="G719" t="n">
-        <v>8.03084850311279</v>
+        <v>8.03084754943848</v>
       </c>
       <c r="H719" t="n">
         <v>443428</v>
@@ -21249,7 +21249,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G720" t="n">
-        <v>7.97415924072266</v>
+        <v>7.97415971755981</v>
       </c>
       <c r="H720" t="n">
         <v>657554</v>
@@ -21278,7 +21278,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G721" t="n">
-        <v>7.8103928565979</v>
+        <v>7.81039333343506</v>
       </c>
       <c r="H721" t="n">
         <v>284353</v>
@@ -21307,7 +21307,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G722" t="n">
-        <v>8.11903095245361</v>
+        <v>8.1190299987793</v>
       </c>
       <c r="H722" t="n">
         <v>419518</v>
@@ -21336,7 +21336,7 @@
         <v>13.0749998092651</v>
       </c>
       <c r="G723" t="n">
-        <v>8.23555660247803</v>
+        <v>8.23555564880371</v>
       </c>
       <c r="H723" t="n">
         <v>534440</v>
@@ -21365,7 +21365,7 @@
         <v>13.3050003051758</v>
       </c>
       <c r="G724" t="n">
-        <v>8.38042640686035</v>
+        <v>8.38042545318604</v>
       </c>
       <c r="H724" t="n">
         <v>419726</v>
@@ -21423,7 +21423,7 @@
         <v>13.9049997329712</v>
       </c>
       <c r="G726" t="n">
-        <v>8.75834941864014</v>
+        <v>8.75834846496582</v>
       </c>
       <c r="H726" t="n">
         <v>950583</v>
@@ -21452,7 +21452,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G727" t="n">
-        <v>8.73630332946777</v>
+        <v>8.73630237579346</v>
       </c>
       <c r="H727" t="n">
         <v>294555</v>
@@ -21510,7 +21510,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G729" t="n">
-        <v>8.90636730194092</v>
+        <v>8.90636825561523</v>
       </c>
       <c r="H729" t="n">
         <v>490390</v>
@@ -21626,7 +21626,7 @@
         <v>13.3050003051758</v>
       </c>
       <c r="G733" t="n">
-        <v>8.38042640686035</v>
+        <v>8.38042545318604</v>
       </c>
       <c r="H733" t="n">
         <v>359929</v>
@@ -21655,7 +21655,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G734" t="n">
-        <v>7.80409479141235</v>
+        <v>7.80409526824951</v>
       </c>
       <c r="H734" t="n">
         <v>3886655</v>
@@ -21684,7 +21684,7 @@
         <v>12.414999961853</v>
       </c>
       <c r="G735" t="n">
-        <v>7.81984186172485</v>
+        <v>7.8198413848877</v>
       </c>
       <c r="H735" t="n">
         <v>1377106</v>
@@ -21713,7 +21713,7 @@
         <v>12.4650001525879</v>
       </c>
       <c r="G736" t="n">
-        <v>7.8513355255127</v>
+        <v>7.85133600234985</v>
       </c>
       <c r="H736" t="n">
         <v>679998</v>
@@ -21742,7 +21742,7 @@
         <v>12.4350004196167</v>
       </c>
       <c r="G737" t="n">
-        <v>7.83243846893311</v>
+        <v>7.83243894577026</v>
       </c>
       <c r="H737" t="n">
         <v>437725</v>
@@ -21771,7 +21771,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G738" t="n">
-        <v>7.7600040435791</v>
+        <v>7.76000452041626</v>
       </c>
       <c r="H738" t="n">
         <v>563615</v>
@@ -21800,7 +21800,7 @@
         <v>12.6750001907349</v>
       </c>
       <c r="G739" t="n">
-        <v>7.98360776901245</v>
+        <v>7.98360872268677</v>
       </c>
       <c r="H739" t="n">
         <v>833312</v>
@@ -21829,7 +21829,7 @@
         <v>12.6850004196167</v>
       </c>
       <c r="G740" t="n">
-        <v>7.98990678787231</v>
+        <v>7.98990726470947</v>
       </c>
       <c r="H740" t="n">
         <v>426686</v>
@@ -21858,7 +21858,7 @@
         <v>12.9449996948242</v>
       </c>
       <c r="G741" t="n">
-        <v>8.15367317199707</v>
+        <v>8.15367221832275</v>
       </c>
       <c r="H741" t="n">
         <v>783214</v>
@@ -21974,7 +21974,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G745" t="n">
-        <v>8.65441989898682</v>
+        <v>8.6544189453125</v>
       </c>
       <c r="H745" t="n">
         <v>351143</v>
@@ -22090,7 +22090,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G749" t="n">
-        <v>8.54734134674072</v>
+        <v>8.54734230041504</v>
       </c>
       <c r="H749" t="n">
         <v>430004</v>
@@ -22119,7 +22119,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G750" t="n">
-        <v>8.16312122344971</v>
+        <v>8.16312026977539</v>
       </c>
       <c r="H750" t="n">
         <v>1842863</v>
@@ -22148,7 +22148,7 @@
         <v>13</v>
       </c>
       <c r="G751" t="n">
-        <v>8.18831539154053</v>
+        <v>8.18831634521484</v>
       </c>
       <c r="H751" t="n">
         <v>613702</v>
@@ -22206,7 +22206,7 @@
         <v>12.3950004577637</v>
       </c>
       <c r="G753" t="n">
-        <v>7.80724477767944</v>
+        <v>7.80724382400513</v>
       </c>
       <c r="H753" t="n">
         <v>912803</v>
@@ -22264,7 +22264,7 @@
         <v>12.75</v>
       </c>
       <c r="G755" t="n">
-        <v>8.03084850311279</v>
+        <v>8.03084754943848</v>
       </c>
       <c r="H755" t="n">
         <v>582759</v>
@@ -22293,7 +22293,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>7.99935436248779</v>
+        <v>7.99935531616211</v>
       </c>
       <c r="H756" t="n">
         <v>508385</v>
@@ -22322,7 +22322,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G757" t="n">
-        <v>8.16312122344971</v>
+        <v>8.16312026977539</v>
       </c>
       <c r="H757" t="n">
         <v>1400230</v>
@@ -22409,7 +22409,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G760" t="n">
-        <v>8.16312122344971</v>
+        <v>8.16312026977539</v>
       </c>
       <c r="H760" t="n">
         <v>1588168</v>
@@ -22438,7 +22438,7 @@
         <v>13.210000038147</v>
       </c>
       <c r="G761" t="n">
-        <v>8.32058906555176</v>
+        <v>8.32058811187744</v>
       </c>
       <c r="H761" t="n">
         <v>3598695</v>
@@ -22467,7 +22467,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G762" t="n">
-        <v>8.22925567626953</v>
+        <v>8.22925662994385</v>
       </c>
       <c r="H762" t="n">
         <v>925106</v>
@@ -22496,7 +22496,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G763" t="n">
-        <v>8.64182281494141</v>
+        <v>8.64182376861572</v>
       </c>
       <c r="H763" t="n">
         <v>1520852</v>
@@ -22525,7 +22525,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G764" t="n">
-        <v>8.8654260635376</v>
+        <v>8.86542701721191</v>
       </c>
       <c r="H764" t="n">
         <v>699801</v>
@@ -22583,7 +22583,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G766" t="n">
-        <v>8.71425819396973</v>
+        <v>8.71425724029541</v>
       </c>
       <c r="H766" t="n">
         <v>959533</v>
@@ -22612,7 +22612,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G767" t="n">
-        <v>8.74890041351318</v>
+        <v>8.7489013671875</v>
       </c>
       <c r="H767" t="n">
         <v>827965</v>
@@ -22641,7 +22641,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G768" t="n">
-        <v>8.64182281494141</v>
+        <v>8.64182376861572</v>
       </c>
       <c r="H768" t="n">
         <v>498393</v>
@@ -22699,7 +22699,7 @@
         <v>14.1149997711182</v>
       </c>
       <c r="G770" t="n">
-        <v>8.89062118530273</v>
+        <v>8.89062213897705</v>
       </c>
       <c r="H770" t="n">
         <v>393173</v>
@@ -22728,7 +22728,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G771" t="n">
-        <v>9.1646146774292</v>
+        <v>9.16461563110352</v>
       </c>
       <c r="H771" t="n">
         <v>973873</v>
@@ -22786,7 +22786,7 @@
         <v>14.8050003051758</v>
       </c>
       <c r="G773" t="n">
-        <v>9.32523155212402</v>
+        <v>9.32523250579834</v>
       </c>
       <c r="H773" t="n">
         <v>975649</v>
@@ -22815,7 +22815,7 @@
         <v>14.7049999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>9.26224613189697</v>
+        <v>9.26224422454834</v>
       </c>
       <c r="H774" t="n">
         <v>591794</v>
@@ -22873,7 +22873,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G776" t="n">
-        <v>8.90007019042969</v>
+        <v>8.90006923675537</v>
       </c>
       <c r="H776" t="n">
         <v>461595</v>
@@ -22902,7 +22902,7 @@
         <v>14.375</v>
       </c>
       <c r="G777" t="n">
-        <v>9.05438709259033</v>
+        <v>9.05438613891602</v>
       </c>
       <c r="H777" t="n">
         <v>284820</v>
@@ -22960,7 +22960,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G779" t="n">
-        <v>8.86227798461914</v>
+        <v>8.86227703094482</v>
       </c>
       <c r="H779" t="n">
         <v>194933</v>
@@ -22989,7 +22989,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>9.03864192962646</v>
+        <v>9.03864097595215</v>
       </c>
       <c r="H780" t="n">
         <v>293855</v>
@@ -23047,7 +23047,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G782" t="n">
-        <v>9.22130393981934</v>
+        <v>9.22130298614502</v>
       </c>
       <c r="H782" t="n">
         <v>375281</v>
@@ -23105,7 +23105,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G784" t="n">
-        <v>9.24649810791016</v>
+        <v>9.24649906158447</v>
       </c>
       <c r="H784" t="n">
         <v>217247</v>
@@ -23134,7 +23134,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G785" t="n">
-        <v>9.03864192962646</v>
+        <v>9.03864097595215</v>
       </c>
       <c r="H785" t="n">
         <v>613922</v>
@@ -23163,7 +23163,7 @@
         <v>14.0649995803833</v>
       </c>
       <c r="G786" t="n">
-        <v>8.85912799835205</v>
+        <v>8.85912704467773</v>
       </c>
       <c r="H786" t="n">
         <v>731969</v>
@@ -23250,7 +23250,7 @@
         <v>13.75</v>
       </c>
       <c r="G789" t="n">
-        <v>8.66071891784668</v>
+        <v>8.66071796417236</v>
       </c>
       <c r="H789" t="n">
         <v>277124</v>
@@ -23308,7 +23308,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G791" t="n">
-        <v>8.0434455871582</v>
+        <v>8.04344654083252</v>
       </c>
       <c r="H791" t="n">
         <v>467784</v>
@@ -23366,7 +23366,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G793" t="n">
-        <v>8.26389980316162</v>
+        <v>8.2638988494873</v>
       </c>
       <c r="H793" t="n">
         <v>360903</v>
@@ -23424,7 +23424,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G795" t="n">
-        <v>8.26389980316162</v>
+        <v>8.2638988494873</v>
       </c>
       <c r="H795" t="n">
         <v>216214</v>
@@ -23453,7 +23453,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G796" t="n">
-        <v>8.28909492492676</v>
+        <v>8.28909397125244</v>
       </c>
       <c r="H796" t="n">
         <v>350304</v>
@@ -23540,7 +23540,7 @@
         <v>14.2349996566772</v>
       </c>
       <c r="G799" t="n">
-        <v>8.96620464324951</v>
+        <v>8.96620559692383</v>
       </c>
       <c r="H799" t="n">
         <v>1046626</v>
@@ -23569,7 +23569,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G800" t="n">
-        <v>8.95045852661133</v>
+        <v>8.95045948028564</v>
       </c>
       <c r="H800" t="n">
         <v>261342</v>
@@ -23598,7 +23598,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G801" t="n">
-        <v>8.95045852661133</v>
+        <v>8.95045948028564</v>
       </c>
       <c r="H801" t="n">
         <v>216635</v>
@@ -23627,7 +23627,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G802" t="n">
-        <v>8.95045852661133</v>
+        <v>8.95045948028564</v>
       </c>
       <c r="H802" t="n">
         <v>144113</v>
@@ -23656,7 +23656,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G803" t="n">
-        <v>8.82448482513428</v>
+        <v>8.82448577880859</v>
       </c>
       <c r="H803" t="n">
         <v>294759</v>
@@ -23685,7 +23685,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G804" t="n">
-        <v>8.73630332946777</v>
+        <v>8.73630237579346</v>
       </c>
       <c r="H804" t="n">
         <v>389912</v>
@@ -23714,7 +23714,7 @@
         <v>13.9899997711182</v>
       </c>
       <c r="G805" t="n">
-        <v>8.81188774108887</v>
+        <v>8.81188678741455</v>
       </c>
       <c r="H805" t="n">
         <v>262013</v>
@@ -23772,7 +23772,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G807" t="n">
-        <v>8.79928970336914</v>
+        <v>8.79929065704346</v>
       </c>
       <c r="H807" t="n">
         <v>230612</v>
@@ -23830,7 +23830,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G809" t="n">
-        <v>8.95675754547119</v>
+        <v>8.95675849914551</v>
       </c>
       <c r="H809" t="n">
         <v>311399</v>
@@ -23859,7 +23859,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G810" t="n">
-        <v>8.93156242370605</v>
+        <v>8.93156337738037</v>
       </c>
       <c r="H810" t="n">
         <v>285655</v>
@@ -23946,7 +23946,7 @@
         <v>13.9849996566772</v>
       </c>
       <c r="G813" t="n">
-        <v>8.80873870849609</v>
+        <v>8.80873775482178</v>
       </c>
       <c r="H813" t="n">
         <v>185648</v>
@@ -23975,7 +23975,7 @@
         <v>13.8149995803833</v>
       </c>
       <c r="G814" t="n">
-        <v>8.70166110992432</v>
+        <v>8.70166015625</v>
       </c>
       <c r="H814" t="n">
         <v>968778</v>
@@ -24004,7 +24004,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G815" t="n">
-        <v>8.9126672744751</v>
+        <v>8.91266632080078</v>
       </c>
       <c r="H815" t="n">
         <v>826896</v>
@@ -24033,7 +24033,7 @@
         <v>14.0749998092651</v>
       </c>
       <c r="G816" t="n">
-        <v>8.8654260635376</v>
+        <v>8.86542701721191</v>
       </c>
       <c r="H816" t="n">
         <v>462247</v>
@@ -24178,7 +24178,7 @@
         <v>13.875</v>
       </c>
       <c r="G821" t="n">
-        <v>8.73945236206055</v>
+        <v>8.73945331573486</v>
       </c>
       <c r="H821" t="n">
         <v>300988</v>
@@ -24207,7 +24207,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G822" t="n">
-        <v>8.61032962799072</v>
+        <v>8.61032867431641</v>
       </c>
       <c r="H822" t="n">
         <v>228894</v>
@@ -24294,7 +24294,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G825" t="n">
-        <v>8.54104423522949</v>
+        <v>8.54104328155518</v>
       </c>
       <c r="H825" t="n">
         <v>206352</v>
@@ -24352,7 +24352,7 @@
         <v>13.6850004196167</v>
       </c>
       <c r="G827" t="n">
-        <v>8.61977767944336</v>
+        <v>8.61977672576904</v>
       </c>
       <c r="H827" t="n">
         <v>310178</v>
@@ -24381,7 +24381,7 @@
         <v>13.664999961853</v>
       </c>
       <c r="G828" t="n">
-        <v>8.60718059539795</v>
+        <v>8.60717964172363</v>
       </c>
       <c r="H828" t="n">
         <v>266215</v>
@@ -24468,7 +24468,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G831" t="n">
-        <v>8.83708190917969</v>
+        <v>8.83708095550537</v>
       </c>
       <c r="H831" t="n">
         <v>205813</v>
@@ -24497,7 +24497,7 @@
         <v>13.9449996948242</v>
       </c>
       <c r="G832" t="n">
-        <v>8.78354358673096</v>
+        <v>8.78354263305664</v>
       </c>
       <c r="H832" t="n">
         <v>204787</v>
@@ -24526,7 +24526,7 @@
         <v>13.8050003051758</v>
       </c>
       <c r="G833" t="n">
-        <v>8.69536113739014</v>
+        <v>8.69536209106445</v>
       </c>
       <c r="H833" t="n">
         <v>443038</v>
@@ -24584,7 +24584,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G835" t="n">
-        <v>8.60403060913086</v>
+        <v>8.60402965545654</v>
       </c>
       <c r="H835" t="n">
         <v>244585</v>
@@ -24642,7 +24642,7 @@
         <v>13.914999961853</v>
       </c>
       <c r="G837" t="n">
-        <v>8.76464748382568</v>
+        <v>8.7646484375</v>
       </c>
       <c r="H837" t="n">
         <v>265152</v>
@@ -24671,7 +24671,7 @@
         <v>13.9849996566772</v>
       </c>
       <c r="G838" t="n">
-        <v>8.80873870849609</v>
+        <v>8.80873775482178</v>
       </c>
       <c r="H838" t="n">
         <v>193495</v>
@@ -24700,7 +24700,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G839" t="n">
-        <v>8.83708190917969</v>
+        <v>8.83708095550537</v>
       </c>
       <c r="H839" t="n">
         <v>301128</v>
@@ -24903,7 +24903,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G846" t="n">
-        <v>9.33467960357666</v>
+        <v>9.33468055725098</v>
       </c>
       <c r="H846" t="n">
         <v>802169</v>
@@ -25077,7 +25077,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G852" t="n">
-        <v>9.0921802520752</v>
+        <v>9.09218120574951</v>
       </c>
       <c r="H852" t="n">
         <v>266466</v>
@@ -25135,7 +25135,7 @@
         <v>14.0249996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>8.8339319229126</v>
+        <v>8.83393287658691</v>
       </c>
       <c r="H854" t="n">
         <v>338352</v>
@@ -25193,7 +25193,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G856" t="n">
-        <v>8.95675754547119</v>
+        <v>8.95675849914551</v>
       </c>
       <c r="H856" t="n">
         <v>847355</v>
@@ -25222,7 +25222,7 @@
         <v>14.1149997711182</v>
       </c>
       <c r="G857" t="n">
-        <v>8.89062118530273</v>
+        <v>8.89062213897705</v>
       </c>
       <c r="H857" t="n">
         <v>407117</v>
@@ -25280,7 +25280,7 @@
         <v>13.9849996566772</v>
       </c>
       <c r="G859" t="n">
-        <v>8.80873870849609</v>
+        <v>8.80873775482178</v>
       </c>
       <c r="H859" t="n">
         <v>194466</v>
@@ -25309,7 +25309,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G860" t="n">
-        <v>8.86227798461914</v>
+        <v>8.86227703094482</v>
       </c>
       <c r="H860" t="n">
         <v>202222</v>
@@ -25338,7 +25338,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>8.70795822143555</v>
+        <v>8.70795917510986</v>
       </c>
       <c r="H861" t="n">
         <v>184636</v>
@@ -25367,7 +25367,7 @@
         <v>13</v>
       </c>
       <c r="G862" t="n">
-        <v>8.18831539154053</v>
+        <v>8.18831634521484</v>
       </c>
       <c r="H862" t="n">
         <v>637723</v>
@@ -25396,7 +25396,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G863" t="n">
-        <v>8.23240566253662</v>
+        <v>8.23240661621094</v>
       </c>
       <c r="H863" t="n">
         <v>368280</v>
@@ -25512,7 +25512,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G867" t="n">
-        <v>8.25760078430176</v>
+        <v>8.25760173797607</v>
       </c>
       <c r="H867" t="n">
         <v>273364</v>
@@ -25628,7 +25628,7 @@
         <v>13.1049995422363</v>
       </c>
       <c r="G871" t="n">
-        <v>8.25445175170898</v>
+        <v>8.2544527053833</v>
       </c>
       <c r="H871" t="n">
         <v>284391</v>
@@ -25715,7 +25715,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G874" t="n">
-        <v>8.8496789932251</v>
+        <v>8.84967994689941</v>
       </c>
       <c r="H874" t="n">
         <v>1699970</v>
@@ -25744,7 +25744,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G875" t="n">
-        <v>8.93156242370605</v>
+        <v>8.93156337738037</v>
       </c>
       <c r="H875" t="n">
         <v>556394</v>
@@ -25802,7 +25802,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G877" t="n">
-        <v>9.14257049560547</v>
+        <v>9.14256954193115</v>
       </c>
       <c r="H877" t="n">
         <v>566778</v>
@@ -25831,7 +25831,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G878" t="n">
-        <v>9.11422443389893</v>
+        <v>9.11422538757324</v>
       </c>
       <c r="H878" t="n">
         <v>280889</v>
@@ -26034,7 +26034,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G885" t="n">
-        <v>9.09532833099365</v>
+        <v>9.09532928466797</v>
       </c>
       <c r="H885" t="n">
         <v>189995</v>
@@ -26121,7 +26121,7 @@
         <v>14.375</v>
       </c>
       <c r="G888" t="n">
-        <v>9.05438709259033</v>
+        <v>9.05438613891602</v>
       </c>
       <c r="H888" t="n">
         <v>231079</v>
@@ -26208,7 +26208,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G891" t="n">
-        <v>8.9693546295166</v>
+        <v>8.96935367584229</v>
       </c>
       <c r="H891" t="n">
         <v>245365</v>
@@ -26237,7 +26237,7 @@
         <v>14.3450002670288</v>
       </c>
       <c r="G892" t="n">
-        <v>9.03549194335938</v>
+        <v>9.03549098968506</v>
       </c>
       <c r="H892" t="n">
         <v>295399</v>
@@ -26295,7 +26295,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G894" t="n">
-        <v>8.8496789932251</v>
+        <v>8.84967994689941</v>
       </c>
       <c r="H894" t="n">
         <v>296717</v>
@@ -26324,7 +26324,7 @@
         <v>13.9449996948242</v>
       </c>
       <c r="G895" t="n">
-        <v>8.78354358673096</v>
+        <v>8.78354263305664</v>
       </c>
       <c r="H895" t="n">
         <v>240805</v>
@@ -26353,7 +26353,7 @@
         <v>13.9750003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>8.80243968963623</v>
+        <v>8.80244064331055</v>
       </c>
       <c r="H896" t="n">
         <v>201676</v>
@@ -26382,7 +26382,7 @@
         <v>13.7449998855591</v>
       </c>
       <c r="G897" t="n">
-        <v>8.65756988525391</v>
+        <v>8.65756893157959</v>
       </c>
       <c r="H897" t="n">
         <v>559736</v>
@@ -26440,7 +26440,7 @@
         <v>13.5950002670288</v>
       </c>
       <c r="G899" t="n">
-        <v>8.56308937072754</v>
+        <v>8.56308841705322</v>
       </c>
       <c r="H899" t="n">
         <v>443577</v>
@@ -26469,7 +26469,7 @@
         <v>13.6350002288818</v>
       </c>
       <c r="G900" t="n">
-        <v>8.58828353881836</v>
+        <v>8.58828258514404</v>
       </c>
       <c r="H900" t="n">
         <v>251630</v>
@@ -26556,7 +26556,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G903" t="n">
-        <v>8.41506767272949</v>
+        <v>8.41506958007812</v>
       </c>
       <c r="H903" t="n">
         <v>317888</v>
@@ -26614,7 +26614,7 @@
         <v>13.3050003051758</v>
       </c>
       <c r="G905" t="n">
-        <v>8.38042640686035</v>
+        <v>8.38042545318604</v>
       </c>
       <c r="H905" t="n">
         <v>301878</v>
@@ -26788,7 +26788,7 @@
         <v>13.2550001144409</v>
       </c>
       <c r="G911" t="n">
-        <v>8.34893226623535</v>
+        <v>8.34893321990967</v>
       </c>
       <c r="H911" t="n">
         <v>201855</v>
@@ -26846,7 +26846,7 @@
         <v>13.25</v>
       </c>
       <c r="G913" t="n">
-        <v>8.34578323364258</v>
+        <v>8.34578418731689</v>
       </c>
       <c r="H913" t="n">
         <v>647996</v>
@@ -26904,7 +26904,7 @@
         <v>13.0249996185303</v>
       </c>
       <c r="G915" t="n">
-        <v>8.20406246185303</v>
+        <v>8.20406150817871</v>
       </c>
       <c r="H915" t="n">
         <v>326623</v>
@@ -27020,7 +27020,7 @@
         <v>12.9650001525879</v>
       </c>
       <c r="G919" t="n">
-        <v>8.16627025604248</v>
+        <v>8.1662712097168</v>
       </c>
       <c r="H919" t="n">
         <v>280860</v>
@@ -27136,7 +27136,7 @@
         <v>14.75</v>
       </c>
       <c r="G923" t="n">
-        <v>9.29058837890625</v>
+        <v>9.29059028625488</v>
       </c>
       <c r="H923" t="n">
         <v>1257029</v>
@@ -27194,7 +27194,7 @@
         <v>14.6750001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>9.24334907531738</v>
+        <v>9.24334812164307</v>
       </c>
       <c r="H925" t="n">
         <v>414297</v>
@@ -27223,7 +27223,7 @@
         <v>14.75</v>
       </c>
       <c r="G926" t="n">
-        <v>9.29058837890625</v>
+        <v>9.29059028625488</v>
       </c>
       <c r="H926" t="n">
         <v>382085</v>
@@ -27310,7 +27310,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G929" t="n">
-        <v>9.24020004272461</v>
+        <v>9.24019908905029</v>
       </c>
       <c r="H929" t="n">
         <v>250054</v>
@@ -27426,7 +27426,7 @@
         <v>14.0349998474121</v>
       </c>
       <c r="G933" t="n">
-        <v>8.84023094177246</v>
+        <v>8.84023189544678</v>
       </c>
       <c r="H933" t="n">
         <v>188556</v>
@@ -27513,7 +27513,7 @@
         <v>14.0299997329712</v>
       </c>
       <c r="G936" t="n">
-        <v>8.83708190917969</v>
+        <v>8.83708095550537</v>
       </c>
       <c r="H936" t="n">
         <v>255846</v>
@@ -27542,7 +27542,7 @@
         <v>13.9049997329712</v>
       </c>
       <c r="G937" t="n">
-        <v>8.75834941864014</v>
+        <v>8.75834846496582</v>
       </c>
       <c r="H937" t="n">
         <v>244364</v>
@@ -27658,7 +27658,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G941" t="n">
-        <v>8.73630332946777</v>
+        <v>8.73630237579346</v>
       </c>
       <c r="H941" t="n">
         <v>276670</v>
@@ -27687,7 +27687,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G942" t="n">
-        <v>8.73630332946777</v>
+        <v>8.73630237579346</v>
       </c>
       <c r="H942" t="n">
         <v>433079</v>
@@ -27803,7 +27803,7 @@
         <v>13.7049999237061</v>
       </c>
       <c r="G946" t="n">
-        <v>8.63237380981445</v>
+        <v>8.63237476348877</v>
       </c>
       <c r="H946" t="n">
         <v>358807</v>
@@ -27832,7 +27832,7 @@
         <v>13.8050003051758</v>
       </c>
       <c r="G947" t="n">
-        <v>8.69536113739014</v>
+        <v>8.69536209106445</v>
       </c>
       <c r="H947" t="n">
         <v>1081374</v>
@@ -27948,7 +27948,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G951" t="n">
-        <v>8.50954914093018</v>
+        <v>8.50955009460449</v>
       </c>
       <c r="H951" t="n">
         <v>280999</v>
@@ -28006,7 +28006,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G953" t="n">
-        <v>8.50954914093018</v>
+        <v>8.50955009460449</v>
       </c>
       <c r="H953" t="n">
         <v>261912</v>
@@ -28035,7 +28035,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G954" t="n">
-        <v>8.54734134674072</v>
+        <v>8.54734230041504</v>
       </c>
       <c r="H954" t="n">
         <v>515523</v>
@@ -28093,7 +28093,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G956" t="n">
-        <v>8.22610855102539</v>
+        <v>8.22610759735107</v>
       </c>
       <c r="H956" t="n">
         <v>729140</v>
@@ -28122,7 +28122,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G957" t="n">
-        <v>8.20721054077148</v>
+        <v>8.2072114944458</v>
       </c>
       <c r="H957" t="n">
         <v>254581</v>
@@ -28180,7 +28180,7 @@
         <v>12.9650001525879</v>
       </c>
       <c r="G959" t="n">
-        <v>8.16627025604248</v>
+        <v>8.1662712097168</v>
       </c>
       <c r="H959" t="n">
         <v>438762</v>
@@ -28238,7 +28238,7 @@
         <v>12.9250001907349</v>
       </c>
       <c r="G961" t="n">
-        <v>8.14107513427734</v>
+        <v>8.14107608795166</v>
       </c>
       <c r="H961" t="n">
         <v>377440</v>
@@ -28325,7 +28325,7 @@
         <v>13.5699996948242</v>
       </c>
       <c r="G964" t="n">
-        <v>8.54734134674072</v>
+        <v>8.54734230041504</v>
       </c>
       <c r="H964" t="n">
         <v>830785</v>
@@ -28383,7 +28383,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G966" t="n">
-        <v>8.35208129882812</v>
+        <v>8.35208225250244</v>
       </c>
       <c r="H966" t="n">
         <v>266277</v>
@@ -28412,7 +28412,7 @@
         <v>13.2749996185303</v>
       </c>
       <c r="G967" t="n">
-        <v>8.36153030395508</v>
+        <v>8.36152935028076</v>
       </c>
       <c r="H967" t="n">
         <v>214395</v>
@@ -28499,7 +28499,7 @@
         <v>13.5249996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>8.51899719238281</v>
+        <v>8.5189962387085</v>
       </c>
       <c r="H970" t="n">
         <v>139146</v>
@@ -28528,7 +28528,7 @@
         <v>13.5349998474121</v>
       </c>
       <c r="G971" t="n">
-        <v>8.52529621124268</v>
+        <v>8.52529716491699</v>
       </c>
       <c r="H971" t="n">
         <v>218241</v>
@@ -28557,7 +28557,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G972" t="n">
-        <v>8.54104423522949</v>
+        <v>8.54104328155518</v>
       </c>
       <c r="H972" t="n">
         <v>227065</v>
@@ -28615,7 +28615,7 @@
         <v>13.6750001907349</v>
       </c>
       <c r="G974" t="n">
-        <v>8.6134786605835</v>
+        <v>8.61347770690918</v>
       </c>
       <c r="H974" t="n">
         <v>236367</v>
@@ -28673,7 +28673,7 @@
         <v>13.4049997329712</v>
       </c>
       <c r="G976" t="n">
-        <v>8.44341373443604</v>
+        <v>8.44341278076172</v>
       </c>
       <c r="H976" t="n">
         <v>310060</v>
@@ -28731,7 +28731,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G978" t="n">
-        <v>8.64182281494141</v>
+        <v>8.64182376861572</v>
       </c>
       <c r="H978" t="n">
         <v>247221</v>
@@ -28760,7 +28760,7 @@
         <v>13.75</v>
       </c>
       <c r="G979" t="n">
-        <v>8.66071891784668</v>
+        <v>8.66071796417236</v>
       </c>
       <c r="H979" t="n">
         <v>377107</v>
@@ -28789,7 +28789,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G980" t="n">
-        <v>8.57883548736572</v>
+        <v>8.57883644104004</v>
       </c>
       <c r="H980" t="n">
         <v>371996</v>
@@ -28876,7 +28876,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G983" t="n">
-        <v>8.54104423522949</v>
+        <v>8.54104328155518</v>
       </c>
       <c r="H983" t="n">
         <v>233924</v>
@@ -28905,7 +28905,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G984" t="n">
-        <v>8.71425819396973</v>
+        <v>8.71425724029541</v>
       </c>
       <c r="H984" t="n">
         <v>1125101</v>
@@ -29021,7 +29021,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G988" t="n">
-        <v>8.42136764526367</v>
+        <v>8.42136669158936</v>
       </c>
       <c r="H988" t="n">
         <v>460101</v>
@@ -29050,7 +29050,7 @@
         <v>13.2950000762939</v>
       </c>
       <c r="G989" t="n">
-        <v>8.37412738800049</v>
+        <v>8.3741283416748</v>
       </c>
       <c r="H989" t="n">
         <v>452197</v>
@@ -29079,7 +29079,7 @@
         <v>13.3549995422363</v>
       </c>
       <c r="G990" t="n">
-        <v>8.41191959381104</v>
+        <v>8.41191864013672</v>
       </c>
       <c r="H990" t="n">
         <v>606089</v>
@@ -29108,7 +29108,7 @@
         <v>13.4049997329712</v>
       </c>
       <c r="G991" t="n">
-        <v>8.44341373443604</v>
+        <v>8.44341278076172</v>
       </c>
       <c r="H991" t="n">
         <v>639147</v>
@@ -29195,7 +29195,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G994" t="n">
-        <v>8.64182281494141</v>
+        <v>8.64182376861572</v>
       </c>
       <c r="H994" t="n">
         <v>576719</v>
@@ -29224,7 +29224,7 @@
         <v>13.8149995803833</v>
       </c>
       <c r="G995" t="n">
-        <v>8.70166110992432</v>
+        <v>8.70166015625</v>
       </c>
       <c r="H995" t="n">
         <v>864167</v>
@@ -29253,7 +29253,7 @@
         <v>13.9449996948242</v>
       </c>
       <c r="G996" t="n">
-        <v>8.78354358673096</v>
+        <v>8.78354263305664</v>
       </c>
       <c r="H996" t="n">
         <v>614847</v>
@@ -29282,7 +29282,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G997" t="n">
-        <v>8.64182281494141</v>
+        <v>8.64182376861572</v>
       </c>
       <c r="H997" t="n">
         <v>1027218</v>
@@ -29340,7 +29340,7 @@
         <v>13.3400001525879</v>
       </c>
       <c r="G999" t="n">
-        <v>8.40247249603271</v>
+        <v>8.4024715423584</v>
       </c>
       <c r="H999" t="n">
         <v>398443</v>
@@ -29369,7 +29369,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G1000" t="n">
-        <v>8.50954914093018</v>
+        <v>8.50955009460449</v>
       </c>
       <c r="H1000" t="n">
         <v>233256</v>
@@ -29398,7 +29398,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1001" t="n">
-        <v>8.46545886993408</v>
+        <v>8.46545791625977</v>
       </c>
       <c r="H1001" t="n">
         <v>293699</v>
@@ -29543,7 +29543,7 @@
         <v>13.6199998855591</v>
       </c>
       <c r="G1006" t="n">
-        <v>8.57883548736572</v>
+        <v>8.57883644104004</v>
       </c>
       <c r="H1006" t="n">
         <v>197832</v>
@@ -29601,7 +29601,7 @@
         <v>13.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>8.50325107574463</v>
+        <v>8.50325012207031</v>
       </c>
       <c r="H1008" t="n">
         <v>195500</v>
@@ -29746,7 +29746,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1013" t="n">
-        <v>8.41506767272949</v>
+        <v>8.41506958007812</v>
       </c>
       <c r="H1013" t="n">
         <v>160962</v>
@@ -29775,7 +29775,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1014" t="n">
-        <v>8.42136764526367</v>
+        <v>8.42136669158936</v>
       </c>
       <c r="H1014" t="n">
         <v>98219</v>
@@ -29833,7 +29833,7 @@
         <v>13.4750003814697</v>
       </c>
       <c r="G1016" t="n">
-        <v>8.48750495910645</v>
+        <v>8.48750400543213</v>
       </c>
       <c r="H1016" t="n">
         <v>258656</v>
@@ -29862,7 +29862,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G1017" t="n">
-        <v>8.50954914093018</v>
+        <v>8.50955009460449</v>
       </c>
       <c r="H1017" t="n">
         <v>377837</v>
@@ -29891,7 +29891,7 @@
         <v>13.5450000762939</v>
       </c>
       <c r="G1018" t="n">
-        <v>8.53159427642822</v>
+        <v>8.53159618377686</v>
       </c>
       <c r="H1018" t="n">
         <v>230051</v>
@@ -30007,7 +30007,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G1022" t="n">
-        <v>8.30799007415771</v>
+        <v>8.30799198150635</v>
       </c>
       <c r="H1022" t="n">
         <v>384912</v>
@@ -30065,7 +30065,7 @@
         <v>13.0649995803833</v>
       </c>
       <c r="G1024" t="n">
-        <v>8.22925567626953</v>
+        <v>8.22925662994385</v>
       </c>
       <c r="H1024" t="n">
         <v>387423</v>
@@ -30123,7 +30123,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1026" t="n">
-        <v>8.20721054077148</v>
+        <v>8.2072114944458</v>
       </c>
       <c r="H1026" t="n">
         <v>319993</v>
@@ -30210,7 +30210,7 @@
         <v>12.8549995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>8.09698390960693</v>
+        <v>8.09698486328125</v>
       </c>
       <c r="H1029" t="n">
         <v>315186</v>
@@ -30239,7 +30239,7 @@
         <v>12.6549997329712</v>
       </c>
       <c r="G1030" t="n">
-        <v>7.9710111618042</v>
+        <v>7.97101020812988</v>
       </c>
       <c r="H1030" t="n">
         <v>424553</v>
@@ -30268,7 +30268,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1031" t="n">
-        <v>7.90487337112427</v>
+        <v>7.90487432479858</v>
       </c>
       <c r="H1031" t="n">
         <v>360322</v>
@@ -30297,7 +30297,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G1032" t="n">
-        <v>7.90487337112427</v>
+        <v>7.90487432479858</v>
       </c>
       <c r="H1032" t="n">
         <v>255316</v>
@@ -30326,7 +30326,7 @@
         <v>12.4549999237061</v>
       </c>
       <c r="G1033" t="n">
-        <v>7.84503602981567</v>
+        <v>7.84503555297852</v>
       </c>
       <c r="H1033" t="n">
         <v>290374</v>
@@ -30384,7 +30384,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1035" t="n">
-        <v>7.74740743637085</v>
+        <v>7.74740600585938</v>
       </c>
       <c r="H1035" t="n">
         <v>394617</v>
@@ -30413,7 +30413,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>7.67182159423828</v>
+        <v>7.67182302474976</v>
       </c>
       <c r="H1036" t="n">
         <v>296897</v>
@@ -30442,7 +30442,7 @@
         <v>11.9350004196167</v>
       </c>
       <c r="G1037" t="n">
-        <v>7.51750469207764</v>
+        <v>7.51750421524048</v>
       </c>
       <c r="H1037" t="n">
         <v>395923</v>
@@ -30529,7 +30529,7 @@
         <v>11.9350004196167</v>
       </c>
       <c r="G1040" t="n">
-        <v>7.51750469207764</v>
+        <v>7.51750421524048</v>
       </c>
       <c r="H1040" t="n">
         <v>379564</v>
@@ -30558,7 +30558,7 @@
         <v>12</v>
       </c>
       <c r="G1041" t="n">
-        <v>7.55844497680664</v>
+        <v>7.55844593048096</v>
       </c>
       <c r="H1041" t="n">
         <v>351465</v>
@@ -30645,7 +30645,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1044" t="n">
-        <v>7.46396541595459</v>
+        <v>7.46396446228027</v>
       </c>
       <c r="H1044" t="n">
         <v>381290</v>
@@ -30674,7 +30674,7 @@
         <v>11.9849996566772</v>
       </c>
       <c r="G1045" t="n">
-        <v>7.54899740219116</v>
+        <v>7.548996925354</v>
       </c>
       <c r="H1045" t="n">
         <v>253560</v>
@@ -30703,7 +30703,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1046" t="n">
-        <v>7.49545860290527</v>
+        <v>7.49545812606812</v>
       </c>
       <c r="H1046" t="n">
         <v>477260</v>
@@ -30732,7 +30732,7 @@
         <v>12</v>
       </c>
       <c r="G1047" t="n">
-        <v>7.55844497680664</v>
+        <v>7.55844593048096</v>
       </c>
       <c r="H1047" t="n">
         <v>509274</v>
@@ -30761,7 +30761,7 @@
         <v>12.0100002288818</v>
       </c>
       <c r="G1048" t="n">
-        <v>7.56474447250366</v>
+        <v>7.5647439956665</v>
       </c>
       <c r="H1048" t="n">
         <v>444424</v>
@@ -30790,7 +30790,7 @@
         <v>11.8649997711182</v>
       </c>
       <c r="G1049" t="n">
-        <v>7.47341203689575</v>
+        <v>7.47341299057007</v>
       </c>
       <c r="H1049" t="n">
         <v>407738</v>
@@ -30819,7 +30819,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1050" t="n">
-        <v>7.32539319992065</v>
+        <v>7.3253927230835</v>
       </c>
       <c r="H1050" t="n">
         <v>844378</v>
@@ -30877,7 +30877,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1052" t="n">
-        <v>7.21831560134888</v>
+        <v>7.21831512451172</v>
       </c>
       <c r="H1052" t="n">
         <v>546426</v>
@@ -30906,7 +30906,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1053" t="n">
-        <v>6.70811939239502</v>
+        <v>6.70812082290649</v>
       </c>
       <c r="H1053" t="n">
         <v>1104852</v>
@@ -31022,7 +31022,7 @@
         <v>10.5649995803833</v>
       </c>
       <c r="G1057" t="n">
-        <v>6.65458106994629</v>
+        <v>6.65458059310913</v>
       </c>
       <c r="H1057" t="n">
         <v>768646</v>
@@ -31051,7 +31051,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G1058" t="n">
-        <v>6.46877002716064</v>
+        <v>6.46876955032349</v>
       </c>
       <c r="H1058" t="n">
         <v>602803</v>
@@ -31109,7 +31109,7 @@
         <v>9.81750011444092</v>
       </c>
       <c r="G1060" t="n">
-        <v>6.18375301361084</v>
+        <v>6.18375396728516</v>
       </c>
       <c r="H1060" t="n">
         <v>558989</v>
@@ -31167,7 +31167,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1062" t="n">
-        <v>5.79480791091919</v>
+        <v>5.79480743408203</v>
       </c>
       <c r="H1062" t="n">
         <v>838763</v>
@@ -31196,7 +31196,7 @@
         <v>8.30249977111816</v>
       </c>
       <c r="G1063" t="n">
-        <v>5.22949981689453</v>
+        <v>5.22949886322021</v>
       </c>
       <c r="H1063" t="n">
         <v>845844</v>
@@ -31225,7 +31225,7 @@
         <v>8.33500003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>5.24997043609619</v>
+        <v>5.24996995925903</v>
       </c>
       <c r="H1064" t="n">
         <v>645705</v>
@@ -31457,7 +31457,7 @@
         <v>8.51000022888184</v>
       </c>
       <c r="G1072" t="n">
-        <v>5.36019802093506</v>
+        <v>5.36019849777222</v>
       </c>
       <c r="H1072" t="n">
         <v>533107</v>
@@ -31486,7 +31486,7 @@
         <v>8.9375</v>
       </c>
       <c r="G1073" t="n">
-        <v>5.62946701049805</v>
+        <v>5.62946653366089</v>
       </c>
       <c r="H1073" t="n">
         <v>363177</v>
@@ -31515,7 +31515,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1074" t="n">
-        <v>5.79480791091919</v>
+        <v>5.79480743408203</v>
       </c>
       <c r="H1074" t="n">
         <v>818396</v>
@@ -31544,7 +31544,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G1075" t="n">
-        <v>5.70032835006714</v>
+        <v>5.70032739639282</v>
       </c>
       <c r="H1075" t="n">
         <v>888894</v>
@@ -31573,7 +31573,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1076" t="n">
-        <v>5.87039232254028</v>
+        <v>5.87039184570312</v>
       </c>
       <c r="H1076" t="n">
         <v>276828</v>
@@ -31602,7 +31602,7 @@
         <v>9.40250015258789</v>
       </c>
       <c r="G1077" t="n">
-        <v>5.92235708236694</v>
+        <v>5.92235660552979</v>
       </c>
       <c r="H1077" t="n">
         <v>407266</v>
@@ -31631,7 +31631,7 @@
         <v>9.67249965667725</v>
       </c>
       <c r="G1078" t="n">
-        <v>6.09242153167725</v>
+        <v>6.0924220085144</v>
       </c>
       <c r="H1078" t="n">
         <v>270658</v>
@@ -31689,7 +31689,7 @@
         <v>9.51000022888184</v>
       </c>
       <c r="G1080" t="n">
-        <v>5.99006843566895</v>
+        <v>5.99006748199463</v>
       </c>
       <c r="H1080" t="n">
         <v>307236</v>
@@ -31718,7 +31718,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G1081" t="n">
-        <v>6.22626924514771</v>
+        <v>6.22626972198486</v>
       </c>
       <c r="H1081" t="n">
         <v>317322</v>
@@ -31747,7 +31747,7 @@
         <v>9.75500011444092</v>
       </c>
       <c r="G1082" t="n">
-        <v>6.14438533782959</v>
+        <v>6.14438581466675</v>
       </c>
       <c r="H1082" t="n">
         <v>311303</v>
@@ -31805,7 +31805,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G1084" t="n">
-        <v>6.22626924514771</v>
+        <v>6.22626972198486</v>
       </c>
       <c r="H1084" t="n">
         <v>502100</v>
@@ -31834,7 +31834,7 @@
         <v>9.8100004196167</v>
       </c>
       <c r="G1085" t="n">
-        <v>6.17902946472168</v>
+        <v>6.17902994155884</v>
       </c>
       <c r="H1085" t="n">
         <v>249434</v>
@@ -31892,7 +31892,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1087" t="n">
-        <v>6.04675579071045</v>
+        <v>6.04675674438477</v>
       </c>
       <c r="H1087" t="n">
         <v>335833</v>
@@ -31921,7 +31921,7 @@
         <v>9.5</v>
       </c>
       <c r="G1088" t="n">
-        <v>5.98376846313477</v>
+        <v>5.98376893997192</v>
       </c>
       <c r="H1088" t="n">
         <v>158398</v>
@@ -31979,7 +31979,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G1090" t="n">
-        <v>5.68143177032471</v>
+        <v>5.68143224716187</v>
       </c>
       <c r="H1090" t="n">
         <v>196442</v>
@@ -32153,7 +32153,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1096" t="n">
-        <v>5.95227527618408</v>
+        <v>5.95227575302124</v>
       </c>
       <c r="H1096" t="n">
         <v>164738</v>
@@ -32182,7 +32182,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1097" t="n">
-        <v>5.97117185592651</v>
+        <v>5.97117233276367</v>
       </c>
       <c r="H1097" t="n">
         <v>189883</v>
@@ -32240,7 +32240,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G1099" t="n">
-        <v>5.84204816818237</v>
+        <v>5.84204769134521</v>
       </c>
       <c r="H1099" t="n">
         <v>152848</v>
@@ -32327,7 +32327,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G1102" t="n">
-        <v>5.65623617172241</v>
+        <v>5.65623569488525</v>
       </c>
       <c r="H1102" t="n">
         <v>73967</v>
@@ -32356,7 +32356,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1103" t="n">
-        <v>5.54915952682495</v>
+        <v>5.54915904998779</v>
       </c>
       <c r="H1103" t="n">
         <v>145163</v>
@@ -32443,7 +32443,7 @@
         <v>9.04500007629395</v>
       </c>
       <c r="G1106" t="n">
-        <v>5.69717788696289</v>
+        <v>5.69717836380005</v>
       </c>
       <c r="H1106" t="n">
         <v>111063</v>
@@ -32530,7 +32530,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G1109" t="n">
-        <v>5.34759950637817</v>
+        <v>5.34759998321533</v>
       </c>
       <c r="H1109" t="n">
         <v>236103</v>
@@ -32559,7 +32559,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>5.32555437088013</v>
+        <v>5.32555484771729</v>
       </c>
       <c r="H1110" t="n">
         <v>248469</v>
@@ -32588,7 +32588,7 @@
         <v>7.59499979019165</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.78386545181274</v>
+        <v>4.7838659286499</v>
       </c>
       <c r="H1111" t="n">
         <v>847930</v>
@@ -32617,7 +32617,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.5823073387146</v>
+        <v>4.58230781555176</v>
       </c>
       <c r="H1112" t="n">
         <v>724929</v>
@@ -32675,7 +32675,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.62324905395508</v>
+        <v>4.62324953079224</v>
       </c>
       <c r="H1114" t="n">
         <v>609413</v>
@@ -32704,7 +32704,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.78701496124268</v>
+        <v>4.78701543807983</v>
       </c>
       <c r="H1115" t="n">
         <v>424500</v>
@@ -32733,7 +32733,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.8657488822937</v>
+        <v>4.86574935913086</v>
       </c>
       <c r="H1116" t="n">
         <v>489503</v>
@@ -32791,7 +32791,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G1118" t="n">
-        <v>5.02636623382568</v>
+        <v>5.02636575698853</v>
       </c>
       <c r="H1118" t="n">
         <v>398179</v>
@@ -32820,7 +32820,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G1119" t="n">
-        <v>4.85315132141113</v>
+        <v>4.85315179824829</v>
       </c>
       <c r="H1119" t="n">
         <v>910716</v>
@@ -32878,7 +32878,7 @@
         <v>8.02499961853027</v>
       </c>
       <c r="G1121" t="n">
-        <v>5.05470991134644</v>
+        <v>5.05471038818359</v>
       </c>
       <c r="H1121" t="n">
         <v>825706</v>
@@ -32907,7 +32907,7 @@
         <v>8.57999992370605</v>
       </c>
       <c r="G1122" t="n">
-        <v>5.40428829193115</v>
+        <v>5.40428781509399</v>
       </c>
       <c r="H1122" t="n">
         <v>833055</v>
@@ -32936,7 +32936,7 @@
         <v>8.57499980926514</v>
       </c>
       <c r="G1123" t="n">
-        <v>5.40113878250122</v>
+        <v>5.40113925933838</v>
       </c>
       <c r="H1123" t="n">
         <v>1041609</v>
@@ -32965,7 +32965,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1124" t="n">
-        <v>5.54286003112793</v>
+        <v>5.54286050796509</v>
       </c>
       <c r="H1124" t="n">
         <v>853454</v>
@@ -32994,7 +32994,7 @@
         <v>8.875</v>
       </c>
       <c r="G1125" t="n">
-        <v>5.59010028839111</v>
+        <v>5.59009981155396</v>
       </c>
       <c r="H1125" t="n">
         <v>675716</v>
@@ -33023,7 +33023,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G1126" t="n">
-        <v>5.47672271728516</v>
+        <v>5.47672319412231</v>
       </c>
       <c r="H1126" t="n">
         <v>512522</v>
@@ -33110,7 +33110,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G1129" t="n">
-        <v>4.90039253234863</v>
+        <v>4.90039205551147</v>
       </c>
       <c r="H1129" t="n">
         <v>558344</v>
@@ -33139,7 +33139,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1130" t="n">
-        <v>4.89094400405884</v>
+        <v>4.89094352722168</v>
       </c>
       <c r="H1130" t="n">
         <v>354452</v>
@@ -33197,7 +33197,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G1132" t="n">
-        <v>4.97282695770264</v>
+        <v>4.97282743453979</v>
       </c>
       <c r="H1132" t="n">
         <v>276756</v>
@@ -33226,7 +33226,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.98857450485229</v>
+        <v>4.98857402801514</v>
       </c>
       <c r="H1133" t="n">
         <v>305333</v>
@@ -33255,7 +33255,7 @@
         <v>7.82499980926514</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.92873573303223</v>
+        <v>4.92873620986938</v>
       </c>
       <c r="H1134" t="n">
         <v>365370</v>
@@ -33342,7 +33342,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G1137" t="n">
-        <v>4.89094400405884</v>
+        <v>4.89094352722168</v>
       </c>
       <c r="H1137" t="n">
         <v>377443</v>
@@ -33429,7 +33429,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.96652889251709</v>
+        <v>4.96652793884277</v>
       </c>
       <c r="H1140" t="n">
         <v>336649</v>
@@ -33516,7 +33516,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G1143" t="n">
-        <v>5.04211330413818</v>
+        <v>5.04211282730103</v>
       </c>
       <c r="H1143" t="n">
         <v>528862</v>
@@ -33545,7 +33545,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1144" t="n">
-        <v>5.00746965408325</v>
+        <v>5.00747013092041</v>
       </c>
       <c r="H1144" t="n">
         <v>333487</v>
@@ -33574,7 +33574,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1145" t="n">
-        <v>5.01061916351318</v>
+        <v>5.01061964035034</v>
       </c>
       <c r="H1145" t="n">
         <v>295912</v>
@@ -33690,7 +33690,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G1149" t="n">
-        <v>4.67678833007812</v>
+        <v>4.67678785324097</v>
       </c>
       <c r="H1149" t="n">
         <v>364624</v>
@@ -33777,7 +33777,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1152" t="n">
-        <v>4.78071737289429</v>
+        <v>4.78071689605713</v>
       </c>
       <c r="H1152" t="n">
         <v>432446</v>
@@ -33835,7 +33835,7 @@
         <v>7.6399998664856</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.81221008300781</v>
+        <v>4.81220960617065</v>
       </c>
       <c r="H1154" t="n">
         <v>169651</v>
@@ -33864,7 +33864,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.82480716705322</v>
+        <v>4.82480764389038</v>
       </c>
       <c r="H1155" t="n">
         <v>287172</v>
@@ -33980,7 +33980,7 @@
         <v>7.54500007629395</v>
       </c>
       <c r="G1159" t="n">
-        <v>4.75237226486206</v>
+        <v>4.75237274169922</v>
       </c>
       <c r="H1159" t="n">
         <v>260185</v>
@@ -34038,7 +34038,7 @@
         <v>7.59000015258789</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.78071737289429</v>
+        <v>4.78071689605713</v>
       </c>
       <c r="H1161" t="n">
         <v>205066</v>
@@ -34067,7 +34067,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.78701496124268</v>
+        <v>4.78701543807983</v>
       </c>
       <c r="H1162" t="n">
         <v>265335</v>
@@ -34212,7 +34212,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1167" t="n">
-        <v>5.07045745849609</v>
+        <v>5.07045698165894</v>
       </c>
       <c r="H1167" t="n">
         <v>903901</v>
@@ -34270,7 +34270,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G1169" t="n">
-        <v>5.05156135559082</v>
+        <v>5.05156087875366</v>
       </c>
       <c r="H1169" t="n">
         <v>391211</v>
@@ -34299,7 +34299,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G1170" t="n">
-        <v>5.01376867294312</v>
+        <v>5.01376819610596</v>
       </c>
       <c r="H1170" t="n">
         <v>266976</v>
@@ -34328,7 +34328,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1171" t="n">
-        <v>5.07045745849609</v>
+        <v>5.07045698165894</v>
       </c>
       <c r="H1171" t="n">
         <v>316589</v>
@@ -34357,7 +34357,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G1172" t="n">
-        <v>5.24682092666626</v>
+        <v>5.2468204498291</v>
       </c>
       <c r="H1172" t="n">
         <v>662594</v>
@@ -34386,7 +34386,7 @@
         <v>8.27499961853027</v>
       </c>
       <c r="G1173" t="n">
-        <v>5.21217775344849</v>
+        <v>5.21217727661133</v>
       </c>
       <c r="H1173" t="n">
         <v>307873</v>
@@ -34415,7 +34415,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G1174" t="n">
-        <v>5.17123651504517</v>
+        <v>5.17123603820801</v>
       </c>
       <c r="H1174" t="n">
         <v>232058</v>
@@ -34560,7 +34560,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G1179" t="n">
-        <v>5.04841232299805</v>
+        <v>5.04841184616089</v>
       </c>
       <c r="H1179" t="n">
         <v>182623</v>
@@ -34879,7 +34879,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G1190" t="n">
-        <v>5.76331472396851</v>
+        <v>5.76331424713135</v>
       </c>
       <c r="H1190" t="n">
         <v>2108666</v>
@@ -34908,7 +34908,7 @@
         <v>9.1899995803833</v>
       </c>
       <c r="G1191" t="n">
-        <v>5.78850984573364</v>
+        <v>5.78850936889648</v>
       </c>
       <c r="H1191" t="n">
         <v>2405489</v>
@@ -34966,7 +34966,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>5.85464572906494</v>
+        <v>5.8546462059021</v>
       </c>
       <c r="H1193" t="n">
         <v>1186866</v>
@@ -34995,7 +34995,7 @@
         <v>9.25500011444092</v>
       </c>
       <c r="G1194" t="n">
-        <v>5.82945108413696</v>
+        <v>5.8294506072998</v>
       </c>
       <c r="H1194" t="n">
         <v>483301</v>
@@ -35053,7 +35053,7 @@
         <v>9.1850004196167</v>
       </c>
       <c r="G1196" t="n">
-        <v>5.78536033630371</v>
+        <v>5.78536081314087</v>
       </c>
       <c r="H1196" t="n">
         <v>295209</v>
@@ -35082,7 +35082,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G1197" t="n">
-        <v>5.84204816818237</v>
+        <v>5.84204769134521</v>
       </c>
       <c r="H1197" t="n">
         <v>356174</v>
@@ -35140,7 +35140,7 @@
         <v>8.8100004196167</v>
       </c>
       <c r="G1199" t="n">
-        <v>5.54915952682495</v>
+        <v>5.54915904998779</v>
       </c>
       <c r="H1199" t="n">
         <v>1690987</v>
@@ -35169,7 +35169,7 @@
         <v>8.52499961853027</v>
       </c>
       <c r="G1200" t="n">
-        <v>5.36964559555054</v>
+        <v>5.36964511871338</v>
       </c>
       <c r="H1200" t="n">
         <v>674270</v>
@@ -35401,7 +35401,7 @@
         <v>8.25</v>
       </c>
       <c r="G1208" t="n">
-        <v>5.19643068313599</v>
+        <v>5.19643115997314</v>
       </c>
       <c r="H1208" t="n">
         <v>240082</v>
@@ -35430,7 +35430,7 @@
         <v>8.25</v>
       </c>
       <c r="G1209" t="n">
-        <v>5.19643068313599</v>
+        <v>5.19643115997314</v>
       </c>
       <c r="H1209" t="n">
         <v>158460</v>
@@ -35459,7 +35459,7 @@
         <v>8.44499969482422</v>
       </c>
       <c r="G1210" t="n">
-        <v>5.31925582885742</v>
+        <v>5.31925535202026</v>
       </c>
       <c r="H1210" t="n">
         <v>187881</v>
@@ -35517,7 +35517,7 @@
         <v>8.51500034332275</v>
       </c>
       <c r="G1212" t="n">
-        <v>5.36334753036499</v>
+        <v>5.36334705352783</v>
       </c>
       <c r="H1212" t="n">
         <v>206253</v>
@@ -35575,7 +35575,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1214" t="n">
-        <v>5.3224048614502</v>
+        <v>5.32240533828735</v>
       </c>
       <c r="H1214" t="n">
         <v>229742</v>
@@ -35604,7 +35604,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1215" t="n">
-        <v>5.22792530059814</v>
+        <v>5.22792482376099</v>
       </c>
       <c r="H1215" t="n">
         <v>222732</v>
@@ -35662,7 +35662,7 @@
         <v>8.25</v>
       </c>
       <c r="G1217" t="n">
-        <v>5.19643068313599</v>
+        <v>5.19643115997314</v>
       </c>
       <c r="H1217" t="n">
         <v>106447</v>
@@ -35691,7 +35691,7 @@
         <v>8.17500019073486</v>
       </c>
       <c r="G1218" t="n">
-        <v>5.14919090270996</v>
+        <v>5.1491904258728</v>
       </c>
       <c r="H1218" t="n">
         <v>315250</v>
@@ -35720,7 +35720,7 @@
         <v>8.22999954223633</v>
       </c>
       <c r="G1219" t="n">
-        <v>5.18383359909058</v>
+        <v>5.18383312225342</v>
       </c>
       <c r="H1219" t="n">
         <v>205036</v>
@@ -35749,7 +35749,7 @@
         <v>8.14500045776367</v>
       </c>
       <c r="G1220" t="n">
-        <v>5.130295753479</v>
+        <v>5.13029527664185</v>
       </c>
       <c r="H1220" t="n">
         <v>146500</v>
@@ -35836,7 +35836,7 @@
         <v>8.00500011444092</v>
       </c>
       <c r="G1223" t="n">
-        <v>5.04211330413818</v>
+        <v>5.04211282730103</v>
       </c>
       <c r="H1223" t="n">
         <v>200334</v>
@@ -35923,7 +35923,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.7996129989624</v>
+        <v>4.79961252212524</v>
       </c>
       <c r="H1226" t="n">
         <v>270879</v>
@@ -35952,7 +35952,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.63269662857056</v>
+        <v>4.63269710540771</v>
       </c>
       <c r="H1227" t="n">
         <v>402067</v>
@@ -36039,7 +36039,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G1230" t="n">
-        <v>4.65159368515015</v>
+        <v>4.65159273147583</v>
       </c>
       <c r="H1230" t="n">
         <v>158600</v>
@@ -36126,7 +36126,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.90984058380127</v>
+        <v>4.90983963012695</v>
       </c>
       <c r="H1233" t="n">
         <v>262650</v>
@@ -36155,7 +36155,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1234" t="n">
-        <v>4.85000228881836</v>
+        <v>4.85000276565552</v>
       </c>
       <c r="H1234" t="n">
         <v>274880</v>
@@ -36184,7 +36184,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>5.01061916351318</v>
+        <v>5.01061964035034</v>
       </c>
       <c r="H1235" t="n">
         <v>813379</v>
@@ -36242,7 +36242,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G1237" t="n">
-        <v>5.51451587677002</v>
+        <v>5.51451635360718</v>
       </c>
       <c r="H1237" t="n">
         <v>1361450</v>
@@ -36271,7 +36271,7 @@
         <v>9.00500011444092</v>
       </c>
       <c r="G1238" t="n">
-        <v>5.67198324203491</v>
+        <v>5.67198371887207</v>
       </c>
       <c r="H1238" t="n">
         <v>1002536</v>
@@ -36300,7 +36300,7 @@
         <v>9.10999965667725</v>
       </c>
       <c r="G1239" t="n">
-        <v>5.73811912536621</v>
+        <v>5.73812007904053</v>
       </c>
       <c r="H1239" t="n">
         <v>522417</v>
@@ -36329,7 +36329,7 @@
         <v>9.625</v>
       </c>
       <c r="G1240" t="n">
-        <v>6.06250238418579</v>
+        <v>6.06250286102295</v>
       </c>
       <c r="H1240" t="n">
         <v>1061732</v>
@@ -36358,7 +36358,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1241" t="n">
-        <v>6.20422315597534</v>
+        <v>6.20422410964966</v>
       </c>
       <c r="H1241" t="n">
         <v>845083</v>
@@ -36387,7 +36387,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G1242" t="n">
-        <v>6.40578269958496</v>
+        <v>6.40578317642212</v>
       </c>
       <c r="H1242" t="n">
         <v>699300</v>
@@ -36416,7 +36416,7 @@
         <v>9.91499996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>6.24516582489014</v>
+        <v>6.24516534805298</v>
       </c>
       <c r="H1243" t="n">
         <v>615063</v>
@@ -36503,7 +36503,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1246" t="n">
-        <v>6.323899269104</v>
+        <v>6.32389879226685</v>
       </c>
       <c r="H1246" t="n">
         <v>543926</v>
@@ -36590,7 +36590,7 @@
         <v>9.92500019073486</v>
       </c>
       <c r="G1249" t="n">
-        <v>6.25146389007568</v>
+        <v>6.25146484375</v>
       </c>
       <c r="H1249" t="n">
         <v>547247</v>
@@ -36619,7 +36619,7 @@
         <v>9.88500022888184</v>
       </c>
       <c r="G1250" t="n">
-        <v>6.22626924514771</v>
+        <v>6.22626972198486</v>
       </c>
       <c r="H1250" t="n">
         <v>403412</v>
@@ -36648,7 +36648,7 @@
         <v>10.1300001144409</v>
       </c>
       <c r="G1251" t="n">
-        <v>6.38058710098267</v>
+        <v>6.38058805465698</v>
       </c>
       <c r="H1251" t="n">
         <v>425417</v>
@@ -36677,7 +36677,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1252" t="n">
-        <v>6.36169242858887</v>
+        <v>6.36169147491455</v>
       </c>
       <c r="H1252" t="n">
         <v>246007</v>
@@ -36706,7 +36706,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G1253" t="n">
-        <v>6.68292474746704</v>
+        <v>6.68292570114136</v>
       </c>
       <c r="H1253" t="n">
         <v>707891</v>
@@ -36735,7 +36735,7 @@
         <v>11</v>
       </c>
       <c r="G1254" t="n">
-        <v>6.92857503890991</v>
+        <v>6.92857456207275</v>
       </c>
       <c r="H1254" t="n">
         <v>990183</v>
@@ -36793,7 +36793,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1256" t="n">
-        <v>6.70182132720947</v>
+        <v>6.70182180404663</v>
       </c>
       <c r="H1256" t="n">
         <v>215386</v>
@@ -36851,7 +36851,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1258" t="n">
-        <v>6.67032861709595</v>
+        <v>6.67032814025879</v>
       </c>
       <c r="H1258" t="n">
         <v>298564</v>
@@ -36880,7 +36880,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>6.56325006484985</v>
+        <v>6.5632495880127</v>
       </c>
       <c r="H1259" t="n">
         <v>232201</v>
@@ -36967,7 +36967,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1262" t="n">
-        <v>6.72701692581177</v>
+        <v>6.72701644897461</v>
       </c>
       <c r="H1262" t="n">
         <v>369792</v>
@@ -36996,7 +36996,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1263" t="n">
-        <v>6.63883495330811</v>
+        <v>6.63883447647095</v>
       </c>
       <c r="H1263" t="n">
         <v>392582</v>
@@ -37054,7 +37054,7 @@
         <v>10.25</v>
       </c>
       <c r="G1265" t="n">
-        <v>6.45617246627808</v>
+        <v>6.45617198944092</v>
       </c>
       <c r="H1265" t="n">
         <v>414219</v>
@@ -37083,7 +37083,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G1266" t="n">
-        <v>6.65143203735352</v>
+        <v>6.65143251419067</v>
       </c>
       <c r="H1266" t="n">
         <v>278489</v>
@@ -37112,7 +37112,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1267" t="n">
-        <v>6.68922424316406</v>
+        <v>6.68922328948975</v>
       </c>
       <c r="H1267" t="n">
         <v>236579</v>
@@ -37141,7 +37141,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G1268" t="n">
-        <v>6.65773010253906</v>
+        <v>6.6577296257019</v>
       </c>
       <c r="H1268" t="n">
         <v>226347</v>
@@ -37170,7 +37170,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1269" t="n">
-        <v>6.63883495330811</v>
+        <v>6.63883447647095</v>
       </c>
       <c r="H1269" t="n">
         <v>142649</v>
@@ -37199,7 +37199,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1270" t="n">
-        <v>6.56954860687256</v>
+        <v>6.5695481300354</v>
       </c>
       <c r="H1270" t="n">
         <v>152422</v>
@@ -37228,7 +37228,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1271" t="n">
-        <v>6.68922424316406</v>
+        <v>6.68922328948975</v>
       </c>
       <c r="H1271" t="n">
         <v>334863</v>
@@ -37257,7 +37257,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1272" t="n">
-        <v>6.67032861709595</v>
+        <v>6.67032814025879</v>
       </c>
       <c r="H1272" t="n">
         <v>214365</v>
@@ -37286,7 +37286,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G1273" t="n">
-        <v>6.7207179069519</v>
+        <v>6.72071743011475</v>
       </c>
       <c r="H1273" t="n">
         <v>219057</v>
@@ -37344,7 +37344,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G1275" t="n">
-        <v>6.67032861709595</v>
+        <v>6.67032814025879</v>
       </c>
       <c r="H1275" t="n">
         <v>179160</v>
@@ -37373,7 +37373,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G1276" t="n">
-        <v>6.5128607749939</v>
+        <v>6.51286125183105</v>
       </c>
       <c r="H1276" t="n">
         <v>269131</v>
@@ -37402,7 +37402,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1277" t="n">
-        <v>6.55695152282715</v>
+        <v>6.55695104598999</v>
       </c>
       <c r="H1277" t="n">
         <v>172172</v>
@@ -37431,7 +37431,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G1278" t="n">
-        <v>6.49396467208862</v>
+        <v>6.49396419525146</v>
       </c>
       <c r="H1278" t="n">
         <v>221552</v>
@@ -37547,7 +37547,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1282" t="n">
-        <v>6.6010422706604</v>
+        <v>6.60104131698608</v>
       </c>
       <c r="H1282" t="n">
         <v>209537</v>
@@ -37605,7 +37605,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1284" t="n">
-        <v>6.764808177948</v>
+        <v>6.76480770111084</v>
       </c>
       <c r="H1284" t="n">
         <v>425309</v>
@@ -37634,7 +37634,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G1285" t="n">
-        <v>6.61993837356567</v>
+        <v>6.61993885040283</v>
       </c>
       <c r="H1285" t="n">
         <v>321970</v>
@@ -37692,7 +37692,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G1287" t="n">
-        <v>6.56954860687256</v>
+        <v>6.5695481300354</v>
       </c>
       <c r="H1287" t="n">
         <v>248010</v>
@@ -37750,7 +37750,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G1289" t="n">
-        <v>6.71441841125488</v>
+        <v>6.71441888809204</v>
       </c>
       <c r="H1289" t="n">
         <v>226742</v>
@@ -37837,7 +37837,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1292" t="n">
-        <v>6.72701692581177</v>
+        <v>6.72701644897461</v>
       </c>
       <c r="H1292" t="n">
         <v>214135</v>
@@ -37895,7 +37895,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1294" t="n">
-        <v>6.84039354324341</v>
+        <v>6.84039258956909</v>
       </c>
       <c r="H1294" t="n">
         <v>263190</v>
@@ -37953,7 +37953,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G1296" t="n">
-        <v>7.10493850708008</v>
+        <v>7.10493898391724</v>
       </c>
       <c r="H1296" t="n">
         <v>604719</v>
@@ -38011,7 +38011,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1298" t="n">
-        <v>6.97266483306885</v>
+        <v>6.97266578674316</v>
       </c>
       <c r="H1298" t="n">
         <v>236611</v>
@@ -38040,7 +38040,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1299" t="n">
-        <v>6.95376968383789</v>
+        <v>6.95377016067505</v>
       </c>
       <c r="H1299" t="n">
         <v>134788</v>
@@ -38069,7 +38069,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G1300" t="n">
-        <v>7.02935457229614</v>
+        <v>7.02935409545898</v>
       </c>
       <c r="H1300" t="n">
         <v>219931</v>
@@ -38098,7 +38098,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1301" t="n">
-        <v>7.11753559112549</v>
+        <v>7.11753606796265</v>
       </c>
       <c r="H1301" t="n">
         <v>368138</v>
@@ -38127,7 +38127,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G1302" t="n">
-        <v>7.06714677810669</v>
+        <v>7.06714630126953</v>
       </c>
       <c r="H1302" t="n">
         <v>210721</v>
@@ -38156,7 +38156,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G1303" t="n">
-        <v>7.09234189987183</v>
+        <v>7.09234142303467</v>
       </c>
       <c r="H1303" t="n">
         <v>140355</v>
@@ -38185,7 +38185,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1304" t="n">
-        <v>7.19312047958374</v>
+        <v>7.19312000274658</v>
       </c>
       <c r="H1304" t="n">
         <v>551082</v>
@@ -38214,7 +38214,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1305" t="n">
-        <v>7.16162633895874</v>
+        <v>7.1616268157959</v>
       </c>
       <c r="H1305" t="n">
         <v>267055</v>
@@ -38243,7 +38243,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1306" t="n">
-        <v>7.16792583465576</v>
+        <v>7.16792488098145</v>
       </c>
       <c r="H1306" t="n">
         <v>137073</v>
@@ -38272,7 +38272,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G1307" t="n">
-        <v>7.16792583465576</v>
+        <v>7.16792488098145</v>
       </c>
       <c r="H1307" t="n">
         <v>263297</v>
@@ -38301,7 +38301,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G1308" t="n">
-        <v>7.30019807815552</v>
+        <v>7.30019760131836</v>
       </c>
       <c r="H1308" t="n">
         <v>360260</v>
@@ -38330,7 +38330,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>7.49545860290527</v>
+        <v>7.49545812606812</v>
       </c>
       <c r="H1309" t="n">
         <v>952860</v>
@@ -38359,7 +38359,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G1310" t="n">
-        <v>7.38838052749634</v>
+        <v>7.38837957382202</v>
       </c>
       <c r="H1310" t="n">
         <v>385043</v>
@@ -38388,7 +38388,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>7.49545860290527</v>
+        <v>7.49545812606812</v>
       </c>
       <c r="H1311" t="n">
         <v>236476</v>
@@ -38417,7 +38417,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1312" t="n">
-        <v>7.5962381362915</v>
+        <v>7.59623718261719</v>
       </c>
       <c r="H1312" t="n">
         <v>460289</v>
@@ -38591,7 +38591,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1318" t="n">
-        <v>8.15052223205566</v>
+        <v>8.1505241394043</v>
       </c>
       <c r="H1318" t="n">
         <v>477435</v>
@@ -38620,7 +38620,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1319" t="n">
-        <v>8.27019882202148</v>
+        <v>8.27019786834717</v>
       </c>
       <c r="H1319" t="n">
         <v>545254</v>
@@ -38649,7 +38649,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G1320" t="n">
-        <v>8.40877056121826</v>
+        <v>8.40877151489258</v>
       </c>
       <c r="H1320" t="n">
         <v>324450</v>
@@ -38736,7 +38736,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1323" t="n">
-        <v>8.3709774017334</v>
+        <v>8.37097835540771</v>
       </c>
       <c r="H1323" t="n">
         <v>211484</v>
@@ -38823,7 +38823,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1326" t="n">
-        <v>8.38987350463867</v>
+        <v>8.38987445831299</v>
       </c>
       <c r="H1326" t="n">
         <v>142589</v>
@@ -38881,7 +38881,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1328" t="n">
-        <v>7.98675680160522</v>
+        <v>7.98675727844238</v>
       </c>
       <c r="H1328" t="n">
         <v>540893</v>
@@ -38939,7 +38939,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G1330" t="n">
-        <v>8.0434455871582</v>
+        <v>8.04344654083252</v>
       </c>
       <c r="H1330" t="n">
         <v>331369</v>
@@ -38968,7 +38968,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1331" t="n">
-        <v>7.98675680160522</v>
+        <v>7.98675727844238</v>
       </c>
       <c r="H1331" t="n">
         <v>203329</v>
@@ -39055,7 +39055,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G1334" t="n">
-        <v>7.75370502471924</v>
+        <v>7.75370454788208</v>
       </c>
       <c r="H1334" t="n">
         <v>192538</v>
@@ -39084,7 +39084,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1335" t="n">
-        <v>7.79779624938965</v>
+        <v>7.79779577255249</v>
       </c>
       <c r="H1335" t="n">
         <v>231422</v>
@@ -39113,7 +39113,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1336" t="n">
-        <v>7.9552640914917</v>
+        <v>7.95526313781738</v>
       </c>
       <c r="H1336" t="n">
         <v>422853</v>
@@ -39142,7 +39142,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1337" t="n">
-        <v>7.80409479141235</v>
+        <v>7.80409526824951</v>
       </c>
       <c r="H1337" t="n">
         <v>172893</v>
@@ -39171,7 +39171,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>7.7600040435791</v>
+        <v>7.76000452041626</v>
       </c>
       <c r="H1338" t="n">
         <v>181914</v>
@@ -39200,7 +39200,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G1339" t="n">
-        <v>7.70331621170044</v>
+        <v>7.70331573486328</v>
       </c>
       <c r="H1339" t="n">
         <v>116812</v>
@@ -39229,7 +39229,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1340" t="n">
-        <v>7.7600040435791</v>
+        <v>7.76000452041626</v>
       </c>
       <c r="H1340" t="n">
         <v>146907</v>
@@ -39258,7 +39258,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1341" t="n">
-        <v>7.7222113609314</v>
+        <v>7.72221088409424</v>
       </c>
       <c r="H1341" t="n">
         <v>243967</v>
@@ -39287,7 +39287,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1342" t="n">
-        <v>7.77889919281006</v>
+        <v>7.77889966964722</v>
       </c>
       <c r="H1342" t="n">
         <v>198378</v>
@@ -39316,7 +39316,7 @@
         <v>12.4399995803833</v>
       </c>
       <c r="G1343" t="n">
-        <v>7.83558750152588</v>
+        <v>7.8355884552002</v>
       </c>
       <c r="H1343" t="n">
         <v>174305</v>
@@ -39345,7 +39345,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G1344" t="n">
-        <v>7.7600040435791</v>
+        <v>7.76000452041626</v>
       </c>
       <c r="H1344" t="n">
         <v>142048</v>
@@ -39374,7 +39374,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>7.35058832168579</v>
+        <v>7.35058736801147</v>
       </c>
       <c r="H1345" t="n">
         <v>776140</v>
@@ -39403,7 +39403,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G1346" t="n">
-        <v>7.31909418106079</v>
+        <v>7.31909513473511</v>
       </c>
       <c r="H1346" t="n">
         <v>258566</v>
@@ -39432,7 +39432,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1347" t="n">
-        <v>7.44506788253784</v>
+        <v>7.445068359375</v>
       </c>
       <c r="H1347" t="n">
         <v>196225</v>
@@ -39461,7 +39461,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G1348" t="n">
-        <v>7.38838052749634</v>
+        <v>7.38837957382202</v>
       </c>
       <c r="H1348" t="n">
         <v>170269</v>
@@ -39519,7 +39519,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1350" t="n">
-        <v>7.52695226669312</v>
+        <v>7.52695178985596</v>
       </c>
       <c r="H1350" t="n">
         <v>476988</v>
@@ -39548,7 +39548,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1351" t="n">
-        <v>8.15682315826416</v>
+        <v>8.15682220458984</v>
       </c>
       <c r="H1351" t="n">
         <v>1624502</v>
@@ -39577,7 +39577,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G1352" t="n">
-        <v>8.64812088012695</v>
+        <v>8.64812183380127</v>
       </c>
       <c r="H1352" t="n">
         <v>1434875</v>
@@ -39606,7 +39606,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1353" t="n">
-        <v>8.3709774017334</v>
+        <v>8.37097835540771</v>
       </c>
       <c r="H1353" t="n">
         <v>551143</v>
@@ -39693,7 +39693,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G1356" t="n">
-        <v>8.61032962799072</v>
+        <v>8.61032867431641</v>
       </c>
       <c r="H1356" t="n">
         <v>429858</v>
@@ -39925,7 +39925,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1364" t="n">
-        <v>8.90636730194092</v>
+        <v>8.90636825561523</v>
       </c>
       <c r="H1364" t="n">
         <v>427072</v>
@@ -40012,7 +40012,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1367" t="n">
-        <v>9.00714683532715</v>
+        <v>9.00714778900146</v>
       </c>
       <c r="H1367" t="n">
         <v>239477</v>
@@ -40041,7 +40041,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1368" t="n">
-        <v>8.95675754547119</v>
+        <v>8.95675849914551</v>
       </c>
       <c r="H1368" t="n">
         <v>221734</v>
@@ -40331,7 +40331,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>9.35357666015625</v>
+        <v>9.35357570648193</v>
       </c>
       <c r="H1378" t="n">
         <v>236636</v>
@@ -40360,7 +40360,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1379" t="n">
-        <v>9.4165620803833</v>
+        <v>9.41656303405762</v>
       </c>
       <c r="H1379" t="n">
         <v>311222</v>
@@ -40389,7 +40389,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G1380" t="n">
-        <v>9.43545913696289</v>
+        <v>9.43545818328857</v>
       </c>
       <c r="H1380" t="n">
         <v>405067</v>
@@ -40447,7 +40447,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G1382" t="n">
-        <v>9.24020004272461</v>
+        <v>9.24019908905029</v>
       </c>
       <c r="H1382" t="n">
         <v>191084</v>
@@ -40505,7 +40505,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1384" t="n">
-        <v>9.1961088180542</v>
+        <v>9.19610786437988</v>
       </c>
       <c r="H1384" t="n">
         <v>259467</v>
@@ -40563,7 +40563,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1386" t="n">
-        <v>9.08273220062256</v>
+        <v>9.08273124694824</v>
       </c>
       <c r="H1386" t="n">
         <v>282737</v>
@@ -40621,7 +40621,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G1388" t="n">
-        <v>8.9126672744751</v>
+        <v>8.91266632080078</v>
       </c>
       <c r="H1388" t="n">
         <v>575391</v>
@@ -40882,7 +40882,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1397" t="n">
-        <v>9.61182308197021</v>
+        <v>9.61182403564453</v>
       </c>
       <c r="H1397" t="n">
         <v>403098</v>
@@ -40969,7 +40969,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1400" t="n">
-        <v>9.97714900970459</v>
+        <v>9.97714805603027</v>
       </c>
       <c r="H1400" t="n">
         <v>1420987</v>
@@ -40998,7 +40998,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G1401" t="n">
-        <v>10.0716276168823</v>
+        <v>10.0716285705566</v>
       </c>
       <c r="H1401" t="n">
         <v>929007</v>
@@ -41027,7 +41027,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G1402" t="n">
-        <v>9.85747146606445</v>
+        <v>9.85747241973877</v>
       </c>
       <c r="H1402" t="n">
         <v>885256</v>
@@ -41085,7 +41085,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G1404" t="n">
-        <v>10.0464334487915</v>
+        <v>10.0464344024658</v>
       </c>
       <c r="H1404" t="n">
         <v>717387</v>
@@ -41114,7 +41114,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G1405" t="n">
-        <v>10.1346158981323</v>
+        <v>10.134614944458</v>
       </c>
       <c r="H1405" t="n">
         <v>571817</v>
@@ -41172,7 +41172,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1407" t="n">
-        <v>10.0149393081665</v>
+        <v>10.0149402618408</v>
       </c>
       <c r="H1407" t="n">
         <v>453810</v>
@@ -41230,7 +41230,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G1409" t="n">
-        <v>9.44517707824707</v>
+        <v>9.44517612457275</v>
       </c>
       <c r="H1409" t="n">
         <v>709665</v>
@@ -41288,7 +41288,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G1411" t="n">
-        <v>9.72379589080811</v>
+        <v>9.72379493713379</v>
       </c>
       <c r="H1411" t="n">
         <v>586268</v>
@@ -41317,7 +41317,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1412" t="n">
-        <v>9.58448696136475</v>
+        <v>9.58448600769043</v>
       </c>
       <c r="H1412" t="n">
         <v>435270</v>
@@ -41346,7 +41346,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G1413" t="n">
-        <v>9.48000431060791</v>
+        <v>9.48000335693359</v>
       </c>
       <c r="H1413" t="n">
         <v>587262</v>
@@ -41433,7 +41433,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G1416" t="n">
-        <v>9.31979846954346</v>
+        <v>9.31979751586914</v>
       </c>
       <c r="H1416" t="n">
         <v>816272</v>
@@ -41462,7 +41462,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G1417" t="n">
-        <v>9.06904220581055</v>
+        <v>9.06904029846191</v>
       </c>
       <c r="H1417" t="n">
         <v>712053</v>
@@ -41491,7 +41491,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G1418" t="n">
-        <v>8.99242115020752</v>
+        <v>8.9924201965332</v>
       </c>
       <c r="H1418" t="n">
         <v>412813</v>
@@ -41578,7 +41578,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1421" t="n">
-        <v>9.0133171081543</v>
+        <v>9.01331806182861</v>
       </c>
       <c r="H1421" t="n">
         <v>282544</v>
@@ -41636,7 +41636,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G1423" t="n">
-        <v>9.1874532699585</v>
+        <v>9.18745517730713</v>
       </c>
       <c r="H1423" t="n">
         <v>379279</v>
@@ -41665,7 +41665,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G1424" t="n">
-        <v>9.21531581878662</v>
+        <v>9.2153148651123</v>
       </c>
       <c r="H1424" t="n">
         <v>264482</v>
@@ -41723,7 +41723,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G1426" t="n">
-        <v>9.25710868835449</v>
+        <v>9.25710964202881</v>
       </c>
       <c r="H1426" t="n">
         <v>494566</v>
@@ -41752,7 +41752,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1427" t="n">
-        <v>9.31283283233643</v>
+        <v>9.31283187866211</v>
       </c>
       <c r="H1427" t="n">
         <v>240869</v>
@@ -41868,7 +41868,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1431" t="n">
-        <v>9.49393463134766</v>
+        <v>9.49393558502197</v>
       </c>
       <c r="H1431" t="n">
         <v>170919</v>
@@ -41897,7 +41897,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1432" t="n">
-        <v>9.30586624145508</v>
+        <v>9.30586719512939</v>
       </c>
       <c r="H1432" t="n">
         <v>229062</v>
@@ -41955,7 +41955,7 @@
         <v>13.25</v>
       </c>
       <c r="G1434" t="n">
-        <v>9.22924613952637</v>
+        <v>9.229248046875</v>
       </c>
       <c r="H1434" t="n">
         <v>207225</v>
@@ -42013,7 +42013,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1436" t="n">
-        <v>9.31283283233643</v>
+        <v>9.31283187866211</v>
       </c>
       <c r="H1436" t="n">
         <v>127170</v>
@@ -42042,7 +42042,7 @@
         <v>13.3699998855591</v>
       </c>
       <c r="G1437" t="n">
-        <v>9.31283283233643</v>
+        <v>9.31283187866211</v>
       </c>
       <c r="H1437" t="n">
         <v>163115</v>
@@ -42100,7 +42100,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G1439" t="n">
-        <v>9.30586624145508</v>
+        <v>9.30586719512939</v>
       </c>
       <c r="H1439" t="n">
         <v>116311</v>
@@ -42129,7 +42129,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G1440" t="n">
-        <v>9.19441890716553</v>
+        <v>9.19441986083984</v>
       </c>
       <c r="H1440" t="n">
         <v>592713</v>
@@ -42187,7 +42187,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G1442" t="n">
-        <v>9.21531581878662</v>
+        <v>9.2153148651123</v>
       </c>
       <c r="H1442" t="n">
         <v>481045</v>
@@ -42245,7 +42245,7 @@
         <v>13.1300001144409</v>
       </c>
       <c r="G1444" t="n">
-        <v>9.14566135406494</v>
+        <v>9.14566040039062</v>
       </c>
       <c r="H1444" t="n">
         <v>183535</v>
@@ -42361,7 +42361,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1448" t="n">
-        <v>8.84614562988281</v>
+        <v>8.84614658355713</v>
       </c>
       <c r="H1448" t="n">
         <v>245143</v>
@@ -42419,7 +42419,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1450" t="n">
-        <v>8.78345680236816</v>
+        <v>8.78345775604248</v>
       </c>
       <c r="H1450" t="n">
         <v>220474</v>
@@ -42448,7 +42448,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1451" t="n">
-        <v>8.71380233764648</v>
+        <v>8.7138032913208</v>
       </c>
       <c r="H1451" t="n">
         <v>766216</v>
@@ -42477,7 +42477,7 @@
         <v>12.6099996566772</v>
       </c>
       <c r="G1452" t="n">
-        <v>8.78345680236816</v>
+        <v>8.78345775604248</v>
       </c>
       <c r="H1452" t="n">
         <v>455423</v>
@@ -42506,7 +42506,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1453" t="n">
-        <v>8.60235404968262</v>
+        <v>8.60235500335693</v>
       </c>
       <c r="H1453" t="n">
         <v>647898</v>
@@ -42622,7 +42622,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1457" t="n">
-        <v>8.79738807678223</v>
+        <v>8.79738712310791</v>
       </c>
       <c r="H1457" t="n">
         <v>474932</v>
@@ -42651,7 +42651,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1458" t="n">
-        <v>8.818284034729</v>
+        <v>8.81828498840332</v>
       </c>
       <c r="H1458" t="n">
         <v>660000</v>
@@ -42680,7 +42680,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1459" t="n">
-        <v>8.86007690429688</v>
+        <v>8.86007785797119</v>
       </c>
       <c r="H1459" t="n">
         <v>339809</v>
@@ -42738,7 +42738,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1461" t="n">
-        <v>8.71380233764648</v>
+        <v>8.7138032913208</v>
       </c>
       <c r="H1461" t="n">
         <v>448523</v>
@@ -42796,7 +42796,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1463" t="n">
-        <v>8.69987106323242</v>
+        <v>8.69987010955811</v>
       </c>
       <c r="H1463" t="n">
         <v>224660</v>
@@ -42825,7 +42825,7 @@
         <v>12.4300003051758</v>
       </c>
       <c r="G1464" t="n">
-        <v>8.65808010101318</v>
+        <v>8.65807914733887</v>
       </c>
       <c r="H1464" t="n">
         <v>393526</v>
@@ -42854,7 +42854,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1465" t="n">
-        <v>8.63718128204346</v>
+        <v>8.63718223571777</v>
       </c>
       <c r="H1465" t="n">
         <v>422558</v>
@@ -42941,7 +42941,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G1468" t="n">
-        <v>8.79738807678223</v>
+        <v>8.79738712310791</v>
       </c>
       <c r="H1468" t="n">
         <v>244196</v>
@@ -42999,7 +42999,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G1470" t="n">
-        <v>8.48394203186035</v>
+        <v>8.48394298553467</v>
       </c>
       <c r="H1470" t="n">
         <v>628440</v>
@@ -43057,7 +43057,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1472" t="n">
-        <v>8.616286277771</v>
+        <v>8.61628532409668</v>
       </c>
       <c r="H1472" t="n">
         <v>357070</v>
@@ -43086,7 +43086,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1473" t="n">
-        <v>8.60235404968262</v>
+        <v>8.60235500335693</v>
       </c>
       <c r="H1473" t="n">
         <v>363646</v>
@@ -43115,7 +43115,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1474" t="n">
-        <v>8.60235404968262</v>
+        <v>8.60235500335693</v>
       </c>
       <c r="H1474" t="n">
         <v>279368</v>
@@ -43173,7 +43173,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1476" t="n">
-        <v>8.76256084442139</v>
+        <v>8.76255989074707</v>
       </c>
       <c r="H1476" t="n">
         <v>261511</v>
@@ -43231,7 +43231,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G1478" t="n">
-        <v>8.80435371398926</v>
+        <v>8.80435276031494</v>
       </c>
       <c r="H1478" t="n">
         <v>351763</v>
@@ -43289,7 +43289,7 @@
         <v>12.3599996566772</v>
       </c>
       <c r="G1480" t="n">
-        <v>8.60932064056396</v>
+        <v>8.60931968688965</v>
       </c>
       <c r="H1480" t="n">
         <v>438085</v>
@@ -43347,7 +43347,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1482" t="n">
-        <v>8.49090766906738</v>
+        <v>8.49090671539307</v>
       </c>
       <c r="H1482" t="n">
         <v>1042190</v>
@@ -43405,7 +43405,7 @@
         <v>12.4899997711182</v>
       </c>
       <c r="G1484" t="n">
-        <v>8.69987106323242</v>
+        <v>8.69987010955811</v>
       </c>
       <c r="H1484" t="n">
         <v>355126</v>
@@ -43434,7 +43434,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1485" t="n">
-        <v>8.60235404968262</v>
+        <v>8.60235500335693</v>
       </c>
       <c r="H1485" t="n">
         <v>155253</v>
@@ -43463,7 +43463,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G1486" t="n">
-        <v>8.56056118011475</v>
+        <v>8.56056213378906</v>
       </c>
       <c r="H1486" t="n">
         <v>250414</v>
@@ -43550,7 +43550,7 @@
         <v>12.1899995803833</v>
       </c>
       <c r="G1489" t="n">
-        <v>8.49090766906738</v>
+        <v>8.49090671539307</v>
       </c>
       <c r="H1489" t="n">
         <v>271903</v>
@@ -43608,7 +43608,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1491" t="n">
-        <v>9.22228145599365</v>
+        <v>9.22228240966797</v>
       </c>
       <c r="H1491" t="n">
         <v>2015401</v>
@@ -43637,7 +43637,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1492" t="n">
-        <v>9.43124675750732</v>
+        <v>9.43124580383301</v>
       </c>
       <c r="H1492" t="n">
         <v>971475</v>
@@ -43695,7 +43695,7 @@
         <v>13.6099996566772</v>
       </c>
       <c r="G1494" t="n">
-        <v>9.48000431060791</v>
+        <v>9.48000335693359</v>
       </c>
       <c r="H1494" t="n">
         <v>384832</v>
@@ -43753,7 +43753,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G1496" t="n">
-        <v>9.09690380096436</v>
+        <v>9.09690284729004</v>
       </c>
       <c r="H1496" t="n">
         <v>690164</v>
@@ -43811,7 +43811,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1498" t="n">
-        <v>8.77649211883545</v>
+        <v>8.77649116516113</v>
       </c>
       <c r="H1498" t="n">
         <v>1208854</v>
@@ -43840,7 +43840,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G1499" t="n">
-        <v>8.90186977386475</v>
+        <v>8.90186882019043</v>
       </c>
       <c r="H1499" t="n">
         <v>407363</v>
@@ -43898,7 +43898,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1501" t="n">
-        <v>8.96455860137939</v>
+        <v>8.96455955505371</v>
       </c>
       <c r="H1501" t="n">
         <v>328455</v>
@@ -44014,7 +44014,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1505" t="n">
-        <v>8.34463310241699</v>
+        <v>8.34463214874268</v>
       </c>
       <c r="H1505" t="n">
         <v>518229</v>
@@ -44072,7 +44072,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G1507" t="n">
-        <v>8.34463310241699</v>
+        <v>8.34463214874268</v>
       </c>
       <c r="H1507" t="n">
         <v>225832</v>
@@ -44101,7 +44101,7 @@
         <v>11.8199996948242</v>
       </c>
       <c r="G1508" t="n">
-        <v>8.23318386077881</v>
+        <v>8.23318481445312</v>
       </c>
       <c r="H1508" t="n">
         <v>220794</v>
@@ -44159,7 +44159,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1510" t="n">
-        <v>8.40732002258301</v>
+        <v>8.40732192993164</v>
       </c>
       <c r="H1510" t="n">
         <v>229847</v>
@@ -44188,7 +44188,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1511" t="n">
-        <v>8.28890895843506</v>
+        <v>8.28890800476074</v>
       </c>
       <c r="H1511" t="n">
         <v>549671</v>
@@ -44217,7 +44217,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1512" t="n">
-        <v>8.25408172607422</v>
+        <v>8.2540807723999</v>
       </c>
       <c r="H1512" t="n">
         <v>500</v>
@@ -44246,7 +44246,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1513" t="n">
-        <v>8.25408172607422</v>
+        <v>8.2540807723999</v>
       </c>
       <c r="H1513" t="n">
         <v>0</v>
@@ -44275,7 +44275,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>8.25408172607422</v>
+        <v>8.2540807723999</v>
       </c>
       <c r="H1514" t="n">
         <v>0</v>
@@ -44304,7 +44304,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1515" t="n">
-        <v>8.25408172607422</v>
+        <v>8.2540807723999</v>
       </c>
       <c r="H1515" t="n">
         <v>0</v>
@@ -44333,7 +44333,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1516" t="n">
-        <v>8.25408172607422</v>
+        <v>8.2540807723999</v>
       </c>
       <c r="H1516" t="n">
         <v>0</v>
@@ -44391,7 +44391,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1518" t="n">
-        <v>4.14445447921753</v>
+        <v>4.14445400238037</v>
       </c>
       <c r="H1518" t="n">
         <v>235</v>
@@ -44420,7 +44420,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1519" t="n">
-        <v>4.14445447921753</v>
+        <v>4.14445400238037</v>
       </c>
       <c r="H1519" t="n">
         <v>0</v>
@@ -44478,7 +44478,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1521" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1521" t="n">
         <v>80</v>
@@ -44507,7 +44507,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1522" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1522" t="n">
         <v>0</v>
@@ -44536,7 +44536,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1523" t="n">
         <v>0</v>
@@ -44565,7 +44565,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1524" t="n">
         <v>0</v>
@@ -44594,7 +44594,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1525" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1525" t="n">
         <v>0</v>
@@ -44623,7 +44623,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1526" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1526" t="n">
         <v>0</v>
@@ -44652,7 +44652,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1527" t="n">
         <v>0</v>
@@ -44681,7 +44681,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1528" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1528" t="n">
         <v>0</v>
@@ -44710,7 +44710,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1529" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1529" t="n">
         <v>0</v>
@@ -44739,7 +44739,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1530" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1530" t="n">
         <v>0</v>
@@ -44768,7 +44768,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1531" t="n">
         <v>0</v>
@@ -44797,7 +44797,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1532" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1532" t="n">
         <v>0</v>
@@ -44826,7 +44826,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1533" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1533" t="n">
         <v>0</v>
@@ -44855,7 +44855,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1534" t="n">
         <v>0</v>
@@ -44884,7 +44884,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1535" t="n">
-        <v>4.31859064102173</v>
+        <v>4.31859111785889</v>
       </c>
       <c r="H1535" t="n">
         <v>0</v>
@@ -44942,7 +44942,7 @@
         <v>6.25</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.35341835021973</v>
+        <v>4.35341882705688</v>
       </c>
       <c r="H1537" t="n">
         <v>328628</v>
@@ -44971,7 +44971,7 @@
         <v>6.34499979019165</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.41959047317505</v>
+        <v>4.41958999633789</v>
       </c>
       <c r="H1538" t="n">
         <v>362338</v>
@@ -45087,7 +45087,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1542" t="n">
-        <v>3.85887026786804</v>
+        <v>3.85887002944946</v>
       </c>
       <c r="H1542" t="n">
         <v>855173</v>
@@ -45116,7 +45116,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>3.88673210144043</v>
+        <v>3.88673186302185</v>
       </c>
       <c r="H1543" t="n">
         <v>703524</v>
@@ -45174,7 +45174,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G1545" t="n">
-        <v>3.94593834877014</v>
+        <v>3.94593858718872</v>
       </c>
       <c r="H1545" t="n">
         <v>1319274</v>
@@ -45232,7 +45232,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G1547" t="n">
-        <v>3.92504239082336</v>
+        <v>3.92504191398621</v>
       </c>
       <c r="H1547" t="n">
         <v>497605</v>
@@ -45319,7 +45319,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1550" t="n">
-        <v>3.95638656616211</v>
+        <v>3.95638680458069</v>
       </c>
       <c r="H1550" t="n">
         <v>735694</v>
@@ -45348,7 +45348,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G1551" t="n">
-        <v>3.88324880599976</v>
+        <v>3.88324904441833</v>
       </c>
       <c r="H1551" t="n">
         <v>505887</v>
@@ -45377,7 +45377,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1552" t="n">
-        <v>3.90066242218018</v>
+        <v>3.90066266059875</v>
       </c>
       <c r="H1552" t="n">
         <v>481600</v>
@@ -45406,7 +45406,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G1553" t="n">
-        <v>3.8484218120575</v>
+        <v>3.84842157363892</v>
       </c>
       <c r="H1553" t="n">
         <v>352453</v>
@@ -45435,7 +45435,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G1554" t="n">
-        <v>3.96335220336914</v>
+        <v>3.96335172653198</v>
       </c>
       <c r="H1554" t="n">
         <v>374164</v>
@@ -45493,7 +45493,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G1556" t="n">
-        <v>4.15838527679443</v>
+        <v>4.15838479995728</v>
       </c>
       <c r="H1556" t="n">
         <v>445975</v>
@@ -45551,7 +45551,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1558" t="n">
-        <v>4.13748931884766</v>
+        <v>4.1374888420105</v>
       </c>
       <c r="H1558" t="n">
         <v>423175</v>
@@ -45580,7 +45580,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.1026611328125</v>
+        <v>4.10266160964966</v>
       </c>
       <c r="H1559" t="n">
         <v>1045884</v>
@@ -45638,7 +45638,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1561" t="n">
-        <v>3.90762853622437</v>
+        <v>3.90762829780579</v>
       </c>
       <c r="H1561" t="n">
         <v>276946</v>
@@ -45667,7 +45667,7 @@
         <v>5.54500007629395</v>
       </c>
       <c r="G1562" t="n">
-        <v>3.8623526096344</v>
+        <v>3.86235284805298</v>
       </c>
       <c r="H1562" t="n">
         <v>284214</v>
@@ -45696,7 +45696,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G1563" t="n">
-        <v>3.85538697242737</v>
+        <v>3.85538744926453</v>
       </c>
       <c r="H1563" t="n">
         <v>786782</v>
@@ -45725,7 +45725,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.93200755119324</v>
+        <v>3.93200731277466</v>
       </c>
       <c r="H1564" t="n">
         <v>441919</v>
@@ -45754,7 +45754,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1565" t="n">
-        <v>3.70562982559204</v>
+        <v>3.70563006401062</v>
       </c>
       <c r="H1565" t="n">
         <v>628721</v>
@@ -45783,7 +45783,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.82056045532227</v>
+        <v>3.82056021690369</v>
       </c>
       <c r="H1566" t="n">
         <v>581531</v>
@@ -45812,7 +45812,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1567" t="n">
-        <v>3.81707668304443</v>
+        <v>3.81707739830017</v>
       </c>
       <c r="H1567" t="n">
         <v>483994</v>
@@ -45841,7 +45841,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G1568" t="n">
-        <v>3.64642333984375</v>
+        <v>3.64642310142517</v>
       </c>
       <c r="H1568" t="n">
         <v>304504</v>
@@ -45870,7 +45870,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1569" t="n">
-        <v>3.8066291809082</v>
+        <v>3.80662941932678</v>
       </c>
       <c r="H1569" t="n">
         <v>1090981</v>
@@ -45899,7 +45899,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1570" t="n">
-        <v>3.62552714347839</v>
+        <v>3.62552666664124</v>
       </c>
       <c r="H1570" t="n">
         <v>932032</v>
@@ -45928,7 +45928,7 @@
         <v>4.84749984741211</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.37651085853577</v>
+        <v>3.37651109695435</v>
       </c>
       <c r="H1571" t="n">
         <v>904825</v>
@@ -45986,7 +45986,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.63249230384827</v>
+        <v>3.63249206542969</v>
       </c>
       <c r="H1573" t="n">
         <v>1489353</v>
@@ -46044,7 +46044,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.80314636230469</v>
+        <v>3.80314612388611</v>
       </c>
       <c r="H1575" t="n">
         <v>332513</v>
@@ -46102,7 +46102,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.08873081207275</v>
+        <v>4.0887303352356</v>
       </c>
       <c r="H1577" t="n">
         <v>593839</v>
@@ -46131,7 +46131,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1578" t="n">
-        <v>4.08873081207275</v>
+        <v>4.0887303352356</v>
       </c>
       <c r="H1578" t="n">
         <v>0</v>
@@ -46160,7 +46160,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.02255821228027</v>
+        <v>4.02255868911743</v>
       </c>
       <c r="H1579" t="n">
         <v>1081936</v>
@@ -46189,7 +46189,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1580" t="n">
-        <v>3.85887026786804</v>
+        <v>3.85887002944946</v>
       </c>
       <c r="H1580" t="n">
         <v>499957</v>
@@ -46276,7 +46276,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1583" t="n">
-        <v>3.73000860214233</v>
+        <v>3.73000907897949</v>
       </c>
       <c r="H1583" t="n">
         <v>339212</v>
@@ -46305,7 +46305,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1584" t="n">
-        <v>3.75090551376343</v>
+        <v>3.75090527534485</v>
       </c>
       <c r="H1584" t="n">
         <v>270434</v>
@@ -46334,7 +46334,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1585" t="n">
-        <v>3.71956086158752</v>
+        <v>3.71956062316895</v>
       </c>
       <c r="H1585" t="n">
         <v>162949</v>
@@ -46363,7 +46363,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G1586" t="n">
-        <v>3.81359434127808</v>
+        <v>3.81359386444092</v>
       </c>
       <c r="H1586" t="n">
         <v>155370</v>
@@ -46421,7 +46421,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1588" t="n">
-        <v>3.78225016593933</v>
+        <v>3.78224968910217</v>
       </c>
       <c r="H1588" t="n">
         <v>185640</v>
@@ -46450,7 +46450,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.75090551376343</v>
+        <v>3.75090527534485</v>
       </c>
       <c r="H1589" t="n">
         <v>190563</v>
@@ -46508,7 +46508,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.63597464561462</v>
+        <v>3.63597536087036</v>
       </c>
       <c r="H1591" t="n">
         <v>468735</v>
@@ -46624,7 +46624,7 @@
         <v>4.77250003814697</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.32427024841309</v>
+        <v>3.32427000999451</v>
       </c>
       <c r="H1595" t="n">
         <v>480755</v>
@@ -46653,7 +46653,7 @@
         <v>4.80499982833862</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.34690809249878</v>
+        <v>3.3469078540802</v>
       </c>
       <c r="H1596" t="n">
         <v>488134</v>
@@ -46682,7 +46682,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.31208086013794</v>
+        <v>3.31208062171936</v>
       </c>
       <c r="H1597" t="n">
         <v>199504</v>
@@ -46711,7 +46711,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.27725338935852</v>
+        <v>3.27725315093994</v>
       </c>
       <c r="H1598" t="n">
         <v>405818</v>
@@ -46740,7 +46740,7 @@
         <v>4.74749994277954</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.30685663223267</v>
+        <v>3.30685615539551</v>
       </c>
       <c r="H1599" t="n">
         <v>200867</v>
@@ -46769,7 +46769,7 @@
         <v>4.8274998664856</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.36257982254028</v>
+        <v>3.36258029937744</v>
       </c>
       <c r="H1600" t="n">
         <v>260504</v>
@@ -46827,7 +46827,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G1602" t="n">
-        <v>3.40263223648071</v>
+        <v>3.40263175964355</v>
       </c>
       <c r="H1602" t="n">
         <v>506926</v>
@@ -46856,7 +46856,7 @@
         <v>5</v>
       </c>
       <c r="G1603" t="n">
-        <v>3.48273491859436</v>
+        <v>3.48273468017578</v>
       </c>
       <c r="H1603" t="n">
         <v>375233</v>
@@ -46885,7 +46885,7 @@
         <v>4.625</v>
       </c>
       <c r="G1604" t="n">
-        <v>3.22152972221375</v>
+        <v>3.22152948379517</v>
       </c>
       <c r="H1604" t="n">
         <v>589007</v>
@@ -46914,7 +46914,7 @@
         <v>4.5</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.13446140289307</v>
+        <v>3.13446116447449</v>
       </c>
       <c r="H1605" t="n">
         <v>487592</v>
@@ -46943,7 +46943,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1606" t="n">
-        <v>3.12401294708252</v>
+        <v>3.1240131855011</v>
       </c>
       <c r="H1606" t="n">
         <v>368904</v>
@@ -47001,7 +47001,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1608" t="n">
-        <v>2.92549705505371</v>
+        <v>2.92549729347229</v>
       </c>
       <c r="H1608" t="n">
         <v>1043977</v>
@@ -47117,7 +47117,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.07177209854126</v>
+        <v>3.07177186012268</v>
       </c>
       <c r="H1612" t="n">
         <v>572832</v>
@@ -47146,7 +47146,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1613" t="n">
-        <v>2.91853165626526</v>
+        <v>2.91853189468384</v>
       </c>
       <c r="H1613" t="n">
         <v>441735</v>
@@ -47262,7 +47262,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1617" t="n">
-        <v>2.86977314949036</v>
+        <v>2.86977338790894</v>
       </c>
       <c r="H1617" t="n">
         <v>484030</v>
@@ -47378,7 +47378,7 @@
         <v>3.96499991416931</v>
       </c>
       <c r="G1621" t="n">
-        <v>2.76180839538574</v>
+        <v>2.76180863380432</v>
       </c>
       <c r="H1621" t="n">
         <v>261272</v>
@@ -47407,7 +47407,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1622" t="n">
-        <v>2.70260190963745</v>
+        <v>2.70260214805603</v>
       </c>
       <c r="H1622" t="n">
         <v>286888</v>
@@ -47494,7 +47494,7 @@
         <v>3.87249994277954</v>
       </c>
       <c r="G1625" t="n">
-        <v>2.69737815856934</v>
+        <v>2.69737768173218</v>
       </c>
       <c r="H1625" t="n">
         <v>330258</v>
@@ -47552,7 +47552,7 @@
         <v>3.92499995231628</v>
       </c>
       <c r="G1627" t="n">
-        <v>2.73394703865051</v>
+        <v>2.73394680023193</v>
       </c>
       <c r="H1627" t="n">
         <v>1679889</v>
@@ -47639,7 +47639,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.75136041641235</v>
+        <v>2.75136065483093</v>
       </c>
       <c r="H1630" t="n">
         <v>429709</v>
@@ -47784,7 +47784,7 @@
         <v>3.81500005722046</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.65732669830322</v>
+        <v>2.6573269367218</v>
       </c>
       <c r="H1635" t="n">
         <v>839348</v>
@@ -47871,7 +47871,7 @@
         <v>3.73250007629395</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.59986138343811</v>
+        <v>2.59986162185669</v>
       </c>
       <c r="H1638" t="n">
         <v>581048</v>
@@ -47929,7 +47929,7 @@
         <v>3.41750001907349</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.38044929504395</v>
+        <v>2.38044905662537</v>
       </c>
       <c r="H1640" t="n">
         <v>252450</v>
@@ -48074,7 +48074,7 @@
         <v>3.53250002861023</v>
       </c>
       <c r="G1645" t="n">
-        <v>2.46055221557617</v>
+        <v>2.46055197715759</v>
       </c>
       <c r="H1645" t="n">
         <v>101477</v>
@@ -48103,7 +48103,7 @@
         <v>3.48250007629395</v>
       </c>
       <c r="G1646" t="n">
-        <v>2.42572474479675</v>
+        <v>2.42572498321533</v>
       </c>
       <c r="H1646" t="n">
         <v>213215</v>
@@ -48132,7 +48132,7 @@
         <v>3.40249991416931</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.37000107765198</v>
+        <v>2.3700008392334</v>
       </c>
       <c r="H1647" t="n">
         <v>290840</v>
@@ -48161,7 +48161,7 @@
         <v>3.30749988555908</v>
       </c>
       <c r="G1648" t="n">
-        <v>2.30382895469666</v>
+        <v>2.30382871627808</v>
       </c>
       <c r="H1648" t="n">
         <v>386522</v>
@@ -48190,7 +48190,7 @@
         <v>3.34249997138977</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.32820820808411</v>
+        <v>2.32820796966553</v>
       </c>
       <c r="H1649" t="n">
         <v>264918</v>
@@ -48451,7 +48451,7 @@
         <v>3.17249989509583</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.20979523658752</v>
+        <v>2.20979499816895</v>
       </c>
       <c r="H1658" t="n">
         <v>320151</v>
@@ -48509,7 +48509,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.27074313163757</v>
+        <v>2.27074337005615</v>
       </c>
       <c r="H1660" t="n">
         <v>397705</v>
@@ -48654,7 +48654,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.0582959651947</v>
+        <v>2.05829620361328</v>
       </c>
       <c r="H1665" t="n">
         <v>1027798</v>
@@ -48712,7 +48712,7 @@
         <v>3.08750009536743</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.15058851242065</v>
+        <v>2.15058875083923</v>
       </c>
       <c r="H1667" t="n">
         <v>653387</v>
@@ -48770,7 +48770,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1669" t="n">
-        <v>2.21501922607422</v>
+        <v>2.2150194644928</v>
       </c>
       <c r="H1669" t="n">
         <v>685440</v>
@@ -48828,7 +48828,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.12098550796509</v>
+        <v>2.12098574638367</v>
       </c>
       <c r="H1671" t="n">
         <v>680217</v>
@@ -48857,7 +48857,7 @@
         <v>3.0625</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.13317489624023</v>
+        <v>2.13317513465881</v>
       </c>
       <c r="H1672" t="n">
         <v>1425109</v>
@@ -48886,7 +48886,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.15233016014099</v>
+        <v>2.15232992172241</v>
       </c>
       <c r="H1673" t="n">
         <v>529596</v>
@@ -48944,7 +48944,7 @@
         <v>3.07249999046326</v>
       </c>
       <c r="G1675" t="n">
-        <v>2.14014029502869</v>
+        <v>2.14014053344727</v>
       </c>
       <c r="H1675" t="n">
         <v>465226</v>
@@ -48973,7 +48973,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.09312343597412</v>
+        <v>2.0931236743927</v>
       </c>
       <c r="H1676" t="n">
         <v>690292</v>
@@ -49002,7 +49002,7 @@
         <v>3.04749989509583</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.12272691726685</v>
+        <v>2.12272667884827</v>
       </c>
       <c r="H1677" t="n">
         <v>481214</v>
@@ -49060,7 +49060,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.11053729057312</v>
+        <v>2.11053705215454</v>
       </c>
       <c r="H1679" t="n">
         <v>227617</v>
@@ -49118,7 +49118,7 @@
         <v>2.94749999046326</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.05307197570801</v>
+        <v>2.05307221412659</v>
       </c>
       <c r="H1681" t="n">
         <v>1208792</v>
@@ -49205,7 +49205,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.21501922607422</v>
+        <v>2.2150194644928</v>
       </c>
       <c r="H1684" t="n">
         <v>248536</v>
@@ -49263,7 +49263,7 @@
         <v>3.0625</v>
       </c>
       <c r="G1686" t="n">
-        <v>2.13317489624023</v>
+        <v>2.13317513465881</v>
       </c>
       <c r="H1686" t="n">
         <v>696672</v>
@@ -49321,7 +49321,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1688" t="n">
-        <v>2.08267521858215</v>
+        <v>2.08267545700073</v>
       </c>
       <c r="H1688" t="n">
         <v>236332</v>
@@ -49350,7 +49350,7 @@
         <v>2.87750005722046</v>
       </c>
       <c r="G1689" t="n">
-        <v>2.00431418418884</v>
+        <v>2.00431394577026</v>
       </c>
       <c r="H1689" t="n">
         <v>496914</v>
@@ -49408,7 +49408,7 @@
         <v>2.90249991416931</v>
       </c>
       <c r="G1691" t="n">
-        <v>2.0217273235321</v>
+        <v>2.02172756195068</v>
       </c>
       <c r="H1691" t="n">
         <v>284478</v>
@@ -49466,7 +49466,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.96426236629486</v>
+        <v>1.96426248550415</v>
       </c>
       <c r="H1693" t="n">
         <v>462256</v>
@@ -49495,7 +49495,7 @@
         <v>2.87750005722046</v>
       </c>
       <c r="G1694" t="n">
-        <v>2.00431418418884</v>
+        <v>2.00431394577026</v>
       </c>
       <c r="H1694" t="n">
         <v>402693</v>
@@ -49524,7 +49524,7 @@
         <v>2.88750004768372</v>
       </c>
       <c r="G1695" t="n">
-        <v>2.01127910614014</v>
+        <v>2.01127934455872</v>
       </c>
       <c r="H1695" t="n">
         <v>394080</v>
@@ -49553,7 +49553,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1696" t="n">
-        <v>2.0199863910675</v>
+        <v>2.01998615264893</v>
       </c>
       <c r="H1696" t="n">
         <v>563230</v>
@@ -49611,7 +49611,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.97819328308105</v>
+        <v>1.97819340229034</v>
       </c>
       <c r="H1698" t="n">
         <v>505024</v>
@@ -49669,7 +49669,7 @@
         <v>2.80250000953674</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.95207285881042</v>
+        <v>1.95207297801971</v>
       </c>
       <c r="H1700" t="n">
         <v>241952</v>
@@ -49756,7 +49756,7 @@
         <v>2.86249995231628</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.9938657283783</v>
+        <v>1.99386560916901</v>
       </c>
       <c r="H1703" t="n">
         <v>243949</v>
@@ -49785,7 +49785,7 @@
         <v>2.87249994277954</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.00083112716675</v>
+        <v>2.00083088874817</v>
       </c>
       <c r="H1704" t="n">
         <v>167563</v>
@@ -49814,7 +49814,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.95033121109009</v>
+        <v>1.95033133029938</v>
       </c>
       <c r="H1705" t="n">
         <v>333894</v>
@@ -49843,7 +49843,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1706" t="n">
-        <v>1.89460790157318</v>
+        <v>1.89460778236389</v>
       </c>
       <c r="H1706" t="n">
         <v>796896</v>
@@ -49901,7 +49901,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.75181555747986</v>
+        <v>1.75181579589844</v>
       </c>
       <c r="H1708" t="n">
         <v>1286014</v>
@@ -49930,7 +49930,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1709" t="n">
-        <v>1.89489984512329</v>
+        <v>1.894899725914</v>
       </c>
       <c r="H1709" t="n">
         <v>1035736</v>
@@ -49959,7 +49959,7 @@
         <v>2.31299996376038</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.78894019126892</v>
+        <v>1.78894007205963</v>
       </c>
       <c r="H1710" t="n">
         <v>908113</v>
@@ -49988,7 +49988,7 @@
         <v>2.23399996757507</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.72783899307251</v>
+        <v>1.7278391122818</v>
       </c>
       <c r="H1711" t="n">
         <v>823679</v>
@@ -50046,7 +50046,7 @@
         <v>2.32399988174438</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.79744780063629</v>
+        <v>1.79744756221771</v>
       </c>
       <c r="H1713" t="n">
         <v>686537</v>
@@ -50075,7 +50075,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.76960444450378</v>
+        <v>1.76960456371307</v>
       </c>
       <c r="H1714" t="n">
         <v>1138540</v>
@@ -50104,7 +50104,7 @@
         <v>2.25</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.74021399021149</v>
+        <v>1.74021422863007</v>
       </c>
       <c r="H1715" t="n">
         <v>595479</v>
@@ -50162,7 +50162,7 @@
         <v>2.07800006866455</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.60718441009521</v>
+        <v>1.6071845293045</v>
       </c>
       <c r="H1717" t="n">
         <v>1051607</v>
@@ -50220,7 +50220,7 @@
         <v>2.35199999809265</v>
       </c>
       <c r="G1719" t="n">
-        <v>1.81910371780396</v>
+        <v>1.81910383701324</v>
       </c>
       <c r="H1719" t="n">
         <v>1165853</v>
@@ -50249,7 +50249,7 @@
         <v>2.30599999427795</v>
       </c>
       <c r="G1720" t="n">
-        <v>1.78352606296539</v>
+        <v>1.78352618217468</v>
       </c>
       <c r="H1720" t="n">
         <v>1083622</v>
@@ -50307,7 +50307,7 @@
         <v>2.28800010681152</v>
       </c>
       <c r="G1722" t="n">
-        <v>1.76960444450378</v>
+        <v>1.76960456371307</v>
       </c>
       <c r="H1722" t="n">
         <v>552690</v>
@@ -50394,7 +50394,7 @@
         <v>2.14299988746643</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.65745723247528</v>
+        <v>1.65745711326599</v>
       </c>
       <c r="H1725" t="n">
         <v>434125</v>
@@ -50481,7 +50481,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.68607413768768</v>
+        <v>1.68607425689697</v>
       </c>
       <c r="H1728" t="n">
         <v>752918</v>
@@ -50510,7 +50510,7 @@
         <v>2.26099991798401</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.74872171878815</v>
+        <v>1.74872183799744</v>
       </c>
       <c r="H1729" t="n">
         <v>562498</v>
@@ -50539,7 +50539,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.79358065128326</v>
+        <v>1.79358053207397</v>
       </c>
       <c r="H1730" t="n">
         <v>317481</v>
@@ -50568,7 +50568,7 @@
         <v>2.31900000572205</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.79358065128326</v>
+        <v>1.79358053207397</v>
       </c>
       <c r="H1731" t="n">
         <v>394947</v>
@@ -50655,7 +50655,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.88252484798431</v>
+        <v>1.8825249671936</v>
       </c>
       <c r="H1734" t="n">
         <v>431258</v>
@@ -50684,7 +50684,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.91655600070953</v>
+        <v>1.91655576229095</v>
       </c>
       <c r="H1735" t="n">
         <v>192050</v>
@@ -50742,7 +50742,7 @@
         <v>2.48099994659424</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.91887617111206</v>
+        <v>1.91887605190277</v>
       </c>
       <c r="H1737" t="n">
         <v>354898</v>
@@ -50858,7 +50858,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.95677411556244</v>
+        <v>1.95677423477173</v>
       </c>
       <c r="H1741" t="n">
         <v>262789</v>
@@ -50945,7 +50945,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.98771119117737</v>
+        <v>1.98771107196808</v>
       </c>
       <c r="H1744" t="n">
         <v>841864</v>
@@ -50974,7 +50974,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.98771119117737</v>
+        <v>1.98771107196808</v>
       </c>
       <c r="H1745" t="n">
         <v>516489</v>
@@ -51003,7 +51003,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.96837544441223</v>
+        <v>1.96837556362152</v>
       </c>
       <c r="H1746" t="n">
         <v>291255</v>
@@ -51032,7 +51032,7 @@
         <v>2.6175000667572</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.02444911003113</v>
+        <v>2.02444887161255</v>
       </c>
       <c r="H1747" t="n">
         <v>946083</v>
@@ -51061,7 +51061,7 @@
         <v>2.74499988555908</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.12306094169617</v>
+        <v>2.12306118011475</v>
       </c>
       <c r="H1748" t="n">
         <v>635042</v>
@@ -51148,7 +51148,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.01478123664856</v>
+        <v>2.01478099822998</v>
       </c>
       <c r="H1751" t="n">
         <v>418210</v>
@@ -51177,7 +51177,7 @@
         <v>2.6175000667572</v>
       </c>
       <c r="G1752" t="n">
-        <v>2.02444911003113</v>
+        <v>2.02444887161255</v>
       </c>
       <c r="H1752" t="n">
         <v>295346</v>
@@ -51206,7 +51206,7 @@
         <v>2.6175000667572</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.02444911003113</v>
+        <v>2.02444887161255</v>
       </c>
       <c r="H1753" t="n">
         <v>175061</v>
@@ -51293,7 +51293,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.06892108917236</v>
+        <v>2.06892132759094</v>
       </c>
       <c r="H1756" t="n">
         <v>246478</v>
@@ -51322,7 +51322,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.15013122558594</v>
+        <v>2.15013146400452</v>
       </c>
       <c r="H1757" t="n">
         <v>444028</v>
@@ -51409,7 +51409,7 @@
         <v>2.77250003814697</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.14433026313782</v>
+        <v>2.1443305015564</v>
       </c>
       <c r="H1760" t="n">
         <v>295725</v>
@@ -51467,7 +51467,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.20813846588135</v>
+        <v>2.20813822746277</v>
       </c>
       <c r="H1762" t="n">
         <v>249132</v>
@@ -51496,7 +51496,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.21200513839722</v>
+        <v>2.2120053768158</v>
       </c>
       <c r="H1763" t="n">
         <v>371800</v>
@@ -51525,7 +51525,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.20427107810974</v>
+        <v>2.20427131652832</v>
       </c>
       <c r="H1764" t="n">
         <v>348195</v>
@@ -51554,7 +51554,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.16559982299805</v>
+        <v>2.16559958457947</v>
       </c>
       <c r="H1765" t="n">
         <v>392897</v>
@@ -51583,7 +51583,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.11726069450378</v>
+        <v>2.11726021766663</v>
       </c>
       <c r="H1766" t="n">
         <v>484370</v>
@@ -51670,7 +51670,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.06118679046631</v>
+        <v>2.06118702888489</v>
       </c>
       <c r="H1769" t="n">
         <v>1011223</v>
@@ -51786,7 +51786,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.01864814758301</v>
+        <v>2.01864838600159</v>
       </c>
       <c r="H1773" t="n">
         <v>1155865</v>
@@ -51815,7 +51815,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1774" t="n">
-        <v>2.0882568359375</v>
+        <v>2.08825707435608</v>
       </c>
       <c r="H1774" t="n">
         <v>275588</v>
@@ -51844,7 +51844,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.06892108917236</v>
+        <v>2.06892132759094</v>
       </c>
       <c r="H1775" t="n">
         <v>313734</v>
@@ -51873,7 +51873,7 @@
         <v>2.73749995231628</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.11726069450378</v>
+        <v>2.11726021766663</v>
       </c>
       <c r="H1776" t="n">
         <v>347402</v>
@@ -51960,7 +51960,7 @@
         <v>2.7425000667572</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.12112760543823</v>
+        <v>2.12112784385681</v>
       </c>
       <c r="H1779" t="n">
         <v>186101</v>
@@ -51989,7 +51989,7 @@
         <v>2.77250003814697</v>
       </c>
       <c r="G1780" t="n">
-        <v>2.14433026313782</v>
+        <v>2.1443305015564</v>
       </c>
       <c r="H1780" t="n">
         <v>289941</v>
@@ -52018,7 +52018,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.1733341217041</v>
+        <v>2.17333388328552</v>
       </c>
       <c r="H1781" t="n">
         <v>162163</v>
@@ -52163,7 +52163,7 @@
         <v>3.09750008583069</v>
       </c>
       <c r="G1786" t="n">
-        <v>2.39569473266602</v>
+        <v>2.39569497108459</v>
       </c>
       <c r="H1786" t="n">
         <v>329286</v>
@@ -52308,7 +52308,7 @@
         <v>2.9925000667572</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.31448459625244</v>
+        <v>2.31448483467102</v>
       </c>
       <c r="H1791" t="n">
         <v>568207</v>
@@ -52366,7 +52366,7 @@
         <v>3.06750011444092</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.37249183654785</v>
+        <v>2.37249207496643</v>
       </c>
       <c r="H1793" t="n">
         <v>333695</v>
@@ -52424,7 +52424,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.36282420158386</v>
+        <v>2.36282396316528</v>
       </c>
       <c r="H1795" t="n">
         <v>237989</v>
@@ -52482,7 +52482,7 @@
         <v>2.9925000667572</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.31448459625244</v>
+        <v>2.31448483467102</v>
       </c>
       <c r="H1797" t="n">
         <v>206747</v>
@@ -52511,7 +52511,7 @@
         <v>3.02250003814697</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.33768773078918</v>
+        <v>2.33768749237061</v>
       </c>
       <c r="H1798" t="n">
         <v>247058</v>
@@ -52569,7 +52569,7 @@
         <v>2.97749996185303</v>
       </c>
       <c r="G1800" t="n">
-        <v>2.30288338661194</v>
+        <v>2.30288314819336</v>
       </c>
       <c r="H1800" t="n">
         <v>192131</v>
@@ -52656,7 +52656,7 @@
         <v>3.11249995231628</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.40729594230652</v>
+        <v>2.4072961807251</v>
       </c>
       <c r="H1803" t="n">
         <v>251554</v>
@@ -52743,7 +52743,7 @@
         <v>3.23250007629395</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.5001072883606</v>
+        <v>2.50010776519775</v>
       </c>
       <c r="H1806" t="n">
         <v>462951</v>
@@ -52801,7 +52801,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.59485244750977</v>
+        <v>2.59485268592834</v>
       </c>
       <c r="H1808" t="n">
         <v>365411</v>
@@ -52917,7 +52917,7 @@
         <v>3.20749998092651</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.48077201843262</v>
+        <v>2.48077178001404</v>
       </c>
       <c r="H1812" t="n">
         <v>382488</v>
@@ -52975,7 +52975,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.50977516174316</v>
+        <v>2.50977540016174</v>
       </c>
       <c r="H1814" t="n">
         <v>230305</v>
@@ -53062,7 +53062,7 @@
         <v>3.26250004768372</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.52331066131592</v>
+        <v>2.52331042289734</v>
       </c>
       <c r="H1817" t="n">
         <v>186182</v>
@@ -53120,7 +53120,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.54457974433899</v>
+        <v>2.54457950592041</v>
       </c>
       <c r="H1819" t="n">
         <v>266780</v>
@@ -53207,7 +53207,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.54844689369202</v>
+        <v>2.54844665527344</v>
       </c>
       <c r="H1822" t="n">
         <v>219279</v>
@@ -53236,7 +53236,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1823" t="n">
-        <v>2.61418867111206</v>
+        <v>2.61418843269348</v>
       </c>
       <c r="H1823" t="n">
         <v>462330</v>
@@ -53323,7 +53323,7 @@
         <v>3.30749988555908</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.55811476707458</v>
+        <v>2.55811452865601</v>
       </c>
       <c r="H1826" t="n">
         <v>311873</v>
@@ -53439,7 +53439,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.60645413398743</v>
+        <v>2.60645389556885</v>
       </c>
       <c r="H1830" t="n">
         <v>120084</v>
@@ -53497,7 +53497,7 @@
         <v>3.26250004768372</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.52331066131592</v>
+        <v>2.52331042289734</v>
       </c>
       <c r="H1832" t="n">
         <v>274724</v>
@@ -53526,7 +53526,7 @@
         <v>3.23250007629395</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.5001072883606</v>
+        <v>2.50010776519775</v>
       </c>
       <c r="H1833" t="n">
         <v>305684</v>
@@ -53555,7 +53555,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.54457974433899</v>
+        <v>2.54457950592041</v>
       </c>
       <c r="H1834" t="n">
         <v>218273</v>
@@ -53584,7 +53584,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1835" t="n">
-        <v>2.50204110145569</v>
+        <v>2.50204133987427</v>
       </c>
       <c r="H1835" t="n">
         <v>241580</v>
@@ -53700,7 +53700,7 @@
         <v>3.29250001907349</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.5465133190155</v>
+        <v>2.54651308059692</v>
       </c>
       <c r="H1839" t="n">
         <v>206681</v>
@@ -53903,7 +53903,7 @@
         <v>3.1875</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.46530318260193</v>
+        <v>2.46530342102051</v>
       </c>
       <c r="H1846" t="n">
         <v>96845</v>
@@ -53932,7 +53932,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.43243265151978</v>
+        <v>2.4324324131012</v>
       </c>
       <c r="H1847" t="n">
         <v>103067</v>
@@ -54019,7 +54019,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.53684544563293</v>
+        <v>2.53684520721436</v>
       </c>
       <c r="H1850" t="n">
         <v>669540</v>
@@ -54106,7 +54106,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1853" t="n">
-        <v>2.75727248191833</v>
+        <v>2.75727272033691</v>
       </c>
       <c r="H1853" t="n">
         <v>583125</v>
@@ -54164,7 +54164,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.7418041229248</v>
+        <v>2.74180388450623</v>
       </c>
       <c r="H1855" t="n">
         <v>308568</v>
@@ -54193,7 +54193,7 @@
         <v>3.58249998092651</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.77080726623535</v>
+        <v>2.77080750465393</v>
       </c>
       <c r="H1856" t="n">
         <v>254276</v>
@@ -54222,7 +54222,7 @@
         <v>3.6324999332428</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.80947923660278</v>
+        <v>2.8094789981842</v>
       </c>
       <c r="H1857" t="n">
         <v>228212</v>
@@ -54251,7 +54251,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.78434252738953</v>
+        <v>2.78434228897095</v>
       </c>
       <c r="H1858" t="n">
         <v>176859</v>
@@ -54309,7 +54309,7 @@
         <v>3.64249992370605</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.81721305847168</v>
+        <v>2.81721329689026</v>
       </c>
       <c r="H1860" t="n">
         <v>396114</v>
@@ -54338,7 +54338,7 @@
         <v>3.64750003814697</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.82108020782471</v>
+        <v>2.82108044624329</v>
       </c>
       <c r="H1861" t="n">
         <v>172677</v>
@@ -54367,7 +54367,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.72633576393127</v>
+        <v>2.7263355255127</v>
       </c>
       <c r="H1862" t="n">
         <v>245568</v>
@@ -54425,7 +54425,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.66059398651123</v>
+        <v>2.66059422492981</v>
       </c>
       <c r="H1864" t="n">
         <v>114621</v>
@@ -54454,7 +54454,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.58325099945068</v>
+        <v>2.58325123786926</v>
       </c>
       <c r="H1865" t="n">
         <v>432318</v>
@@ -54541,7 +54541,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.50204110145569</v>
+        <v>2.50204133987427</v>
       </c>
       <c r="H1868" t="n">
         <v>476442</v>
@@ -54570,7 +54570,7 @@
         <v>3.28250002861023</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.53877902030945</v>
+        <v>2.53877878189087</v>
       </c>
       <c r="H1869" t="n">
         <v>224368</v>
@@ -54628,7 +54628,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.53684544563293</v>
+        <v>2.53684520721436</v>
       </c>
       <c r="H1871" t="n">
         <v>96033</v>
@@ -54715,7 +54715,7 @@
         <v>3.29250001907349</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.5465133190155</v>
+        <v>2.54651308059692</v>
       </c>
       <c r="H1874" t="n">
         <v>257173</v>
@@ -54860,7 +54860,7 @@
         <v>3.63750004768372</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.81334590911865</v>
+        <v>2.81334614753723</v>
       </c>
       <c r="H1879" t="n">
         <v>504631</v>
@@ -54889,7 +54889,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.75727248191833</v>
+        <v>2.75727272033691</v>
       </c>
       <c r="H1880" t="n">
         <v>146090</v>
@@ -54947,7 +54947,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.66059398651123</v>
+        <v>2.66059422492981</v>
       </c>
       <c r="H1882" t="n">
         <v>287505</v>
@@ -54976,7 +54976,7 @@
         <v>3.45749998092651</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.67412900924683</v>
+        <v>2.67412924766541</v>
       </c>
       <c r="H1883" t="n">
         <v>306979</v>
@@ -55005,7 +55005,7 @@
         <v>3.37249994277954</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.60838770866394</v>
+        <v>2.60838747024536</v>
       </c>
       <c r="H1884" t="n">
         <v>816004</v>
@@ -55034,7 +55034,7 @@
         <v>3.38750004768372</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.61998915672302</v>
+        <v>2.61998891830444</v>
       </c>
       <c r="H1885" t="n">
         <v>396596</v>
@@ -55063,7 +55063,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.58325099945068</v>
+        <v>2.58325123786926</v>
       </c>
       <c r="H1886" t="n">
         <v>217966</v>
@@ -55092,7 +55092,7 @@
         <v>3.22749996185303</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.49624061584473</v>
+        <v>2.49624037742615</v>
       </c>
       <c r="H1887" t="n">
         <v>459351</v>
@@ -55295,7 +55295,7 @@
         <v>3.44250011444092</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.66252779960632</v>
+        <v>2.66252756118774</v>
       </c>
       <c r="H1894" t="n">
         <v>664502</v>
@@ -55411,7 +55411,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.78434252738953</v>
+        <v>2.78434228897095</v>
       </c>
       <c r="H1898" t="n">
         <v>559137</v>
@@ -55498,7 +55498,7 @@
         <v>3.57249999046326</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.76307320594788</v>
+        <v>2.76307344436646</v>
       </c>
       <c r="H1901" t="n">
         <v>187621</v>
@@ -55846,7 +55846,7 @@
         <v>3.54250001907349</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.73987054824829</v>
+        <v>2.73987030982971</v>
       </c>
       <c r="H1913" t="n">
         <v>369216</v>
@@ -55933,7 +55933,7 @@
         <v>3.63750004768372</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.81334590911865</v>
+        <v>2.81334614753723</v>
       </c>
       <c r="H1916" t="n">
         <v>322345</v>
@@ -55962,7 +55962,7 @@
         <v>3.67750000953674</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.84428334236145</v>
+        <v>2.84428310394287</v>
       </c>
       <c r="H1917" t="n">
         <v>359282</v>
@@ -55991,7 +55991,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.88488841056824</v>
+        <v>2.88488817214966</v>
       </c>
       <c r="H1918" t="n">
         <v>449584</v>
@@ -56049,7 +56049,7 @@
         <v>3.62750005722046</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.80561184883118</v>
+        <v>2.8056116104126</v>
       </c>
       <c r="H1920" t="n">
         <v>348133</v>
@@ -56107,7 +56107,7 @@
         <v>3.64249992370605</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.81721305847168</v>
+        <v>2.81721329689026</v>
       </c>
       <c r="H1922" t="n">
         <v>248418</v>
@@ -56165,7 +56165,7 @@
         <v>3.55749988555908</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.75147199630737</v>
+        <v>2.75147175788879</v>
       </c>
       <c r="H1924" t="n">
         <v>464210</v>
@@ -56252,7 +56252,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.74939227104187</v>
+        <v>2.74939203262329</v>
       </c>
       <c r="H1927" t="n">
         <v>218617</v>
@@ -56368,7 +56368,7 @@
         <v>3.46250009536743</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.88041472434998</v>
+        <v>2.8804144859314</v>
       </c>
       <c r="H1931" t="n">
         <v>158009</v>
@@ -56484,7 +56484,7 @@
         <v>3.51749992370605</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.92616844177246</v>
+        <v>2.92616820335388</v>
       </c>
       <c r="H1935" t="n">
         <v>182053</v>
@@ -56513,7 +56513,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.89081311225891</v>
+        <v>2.89081287384033</v>
       </c>
       <c r="H1936" t="n">
         <v>218456</v>
@@ -56542,7 +56542,7 @@
         <v>3.5</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.91161012649536</v>
+        <v>2.91161036491394</v>
       </c>
       <c r="H1937" t="n">
         <v>128266</v>
@@ -56658,7 +56658,7 @@
         <v>3.48499989509583</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.89913177490234</v>
+        <v>2.89913201332092</v>
       </c>
       <c r="H1941" t="n">
         <v>601086</v>
@@ -56774,7 +56774,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.79514598846436</v>
+        <v>2.79514575004578</v>
       </c>
       <c r="H1945" t="n">
         <v>267592</v>
@@ -56832,7 +56832,7 @@
         <v>3.30749988555908</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.75147199630737</v>
+        <v>2.75147175788879</v>
       </c>
       <c r="H1947" t="n">
         <v>163651</v>
@@ -56948,7 +56948,7 @@
         <v>3.30749988555908</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.75147199630737</v>
+        <v>2.75147175788879</v>
       </c>
       <c r="H1951" t="n">
         <v>385922</v>
@@ -56977,7 +56977,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.74939227104187</v>
+        <v>2.74939203262329</v>
       </c>
       <c r="H1952" t="n">
         <v>122275</v>
@@ -57064,7 +57064,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.70779776573181</v>
+        <v>2.70779752731323</v>
       </c>
       <c r="H1955" t="n">
         <v>572258</v>
@@ -57209,7 +57209,7 @@
         <v>3.20250010490417</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.66412377357483</v>
+        <v>2.66412353515625</v>
       </c>
       <c r="H1960" t="n">
         <v>238751</v>
@@ -57354,7 +57354,7 @@
         <v>3.01749992370605</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.51022386550903</v>
+        <v>2.51022410392761</v>
       </c>
       <c r="H1965" t="n">
         <v>377997</v>
@@ -57383,7 +57383,7 @@
         <v>3.07249999046326</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.5559778213501</v>
+        <v>2.55597805976868</v>
       </c>
       <c r="H1966" t="n">
         <v>299454</v>
@@ -57615,7 +57615,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.40415859222412</v>
+        <v>2.40415835380554</v>
       </c>
       <c r="H1974" t="n">
         <v>183747</v>
@@ -57673,7 +57673,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.3043315410614</v>
+        <v>2.30433177947998</v>
       </c>
       <c r="H1976" t="n">
         <v>290330</v>
@@ -57731,7 +57731,7 @@
         <v>2.80250000953674</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.33136820793152</v>
+        <v>2.33136796951294</v>
       </c>
       <c r="H1978" t="n">
         <v>259195</v>
@@ -57818,7 +57818,7 @@
         <v>2.89499998092651</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.40831780433655</v>
+        <v>2.40831756591797</v>
       </c>
       <c r="H1981" t="n">
         <v>154673</v>
@@ -57876,7 +57876,7 @@
         <v>2.80250000953674</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.33136820793152</v>
+        <v>2.33136796951294</v>
       </c>
       <c r="H1983" t="n">
         <v>126265</v>
@@ -57934,7 +57934,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.40415859222412</v>
+        <v>2.40415835380554</v>
       </c>
       <c r="H1985" t="n">
         <v>310477</v>
@@ -58021,7 +58021,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.34176683425903</v>
+        <v>2.34176659584045</v>
       </c>
       <c r="H1988" t="n">
         <v>215811</v>
@@ -58050,7 +58050,7 @@
         <v>0.563000023365021</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.46835333108902</v>
+        <v>0.468353360891342</v>
       </c>
       <c r="H1989" t="n">
         <v>162966</v>
@@ -58079,7 +58079,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.1878674030304</v>
+        <v>2.18786716461182</v>
       </c>
       <c r="H1990" t="n">
         <v>1104499</v>
@@ -58224,7 +58224,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1995" t="n">
-        <v>2.08388113975525</v>
+        <v>2.08388137817383</v>
       </c>
       <c r="H1995" t="n">
         <v>308268</v>
@@ -58804,7 +58804,7 @@
         <v>3.16300010681152</v>
       </c>
       <c r="G2015" t="n">
-        <v>2.63126397132874</v>
+        <v>2.63126420974731</v>
       </c>
       <c r="H2015" t="n">
         <v>311889</v>
@@ -58920,7 +58920,7 @@
         <v>3.13700008392334</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.60963487625122</v>
+        <v>2.60963463783264</v>
       </c>
       <c r="H2019" t="n">
         <v>324374</v>
@@ -59007,7 +59007,7 @@
         <v>3.21050000190735</v>
       </c>
       <c r="G2022" t="n">
-        <v>2.67077851295471</v>
+        <v>2.67077827453613</v>
       </c>
       <c r="H2022" t="n">
         <v>307025</v>
@@ -59065,7 +59065,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.79514598846436</v>
+        <v>2.79514575004578</v>
       </c>
       <c r="H2024" t="n">
         <v>673513</v>
@@ -59123,7 +59123,7 @@
         <v>3.21499991416931</v>
       </c>
       <c r="G2026" t="n">
-        <v>2.67452216148376</v>
+        <v>2.67452192306519</v>
       </c>
       <c r="H2026" t="n">
         <v>261198</v>
@@ -59181,7 +59181,7 @@
         <v>3.32649993896484</v>
       </c>
       <c r="G2028" t="n">
-        <v>2.76727747917175</v>
+        <v>2.76727771759033</v>
       </c>
       <c r="H2028" t="n">
         <v>712108</v>
@@ -59297,7 +59297,7 @@
         <v>3.31150007247925</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.75479936599731</v>
+        <v>2.75479960441589</v>
       </c>
       <c r="H2032" t="n">
         <v>136306</v>
@@ -59355,7 +59355,7 @@
         <v>3.30800008773804</v>
       </c>
       <c r="G2034" t="n">
-        <v>2.75188779830933</v>
+        <v>2.75188803672791</v>
       </c>
       <c r="H2034" t="n">
         <v>292624</v>
@@ -59413,7 +59413,7 @@
         <v>3.26699995994568</v>
       </c>
       <c r="G2036" t="n">
-        <v>2.71778011322021</v>
+        <v>2.71778035163879</v>
       </c>
       <c r="H2036" t="n">
         <v>114452</v>
@@ -59500,7 +59500,7 @@
         <v>3.31100010871887</v>
       </c>
       <c r="G2039" t="n">
-        <v>2.75438332557678</v>
+        <v>2.75438356399536</v>
       </c>
       <c r="H2039" t="n">
         <v>199914</v>
@@ -59616,7 +59616,7 @@
         <v>3.42799997329712</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.85171437263489</v>
+        <v>2.85171461105347</v>
       </c>
       <c r="H2043" t="n">
         <v>160508</v>
@@ -59645,7 +59645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2044" t="n">
-        <v>2.78682684898376</v>
+        <v>2.78682708740234</v>
       </c>
       <c r="H2044" t="n">
         <v>264745</v>
@@ -59674,7 +59674,7 @@
         <v>3.31949996948242</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.76145434379578</v>
+        <v>2.76145458221436</v>
       </c>
       <c r="H2045" t="n">
         <v>186727</v>
@@ -59703,7 +59703,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2046" t="n">
-        <v>2.72693109512329</v>
+        <v>2.72693133354187</v>
       </c>
       <c r="H2046" t="n">
         <v>225182</v>
@@ -59732,7 +59732,7 @@
         <v>3.29949998855591</v>
       </c>
       <c r="G2047" t="n">
-        <v>2.74481678009033</v>
+        <v>2.74481654167175</v>
       </c>
       <c r="H2047" t="n">
         <v>192205</v>
@@ -59964,7 +59964,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G2055" t="n">
-        <v>2.82426190376282</v>
+        <v>2.8242621421814</v>
       </c>
       <c r="H2055" t="n">
         <v>109564</v>
@@ -60051,7 +60051,7 @@
         <v>3.34299993515015</v>
       </c>
       <c r="G2058" t="n">
-        <v>2.78100371360779</v>
+        <v>2.78100347518921</v>
       </c>
       <c r="H2058" t="n">
         <v>142985</v>
@@ -60080,7 +60080,7 @@
         <v>3.27449989318848</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.7240195274353</v>
+        <v>2.72401928901672</v>
       </c>
       <c r="H2059" t="n">
         <v>260960</v>
@@ -60109,7 +60109,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G2060" t="n">
-        <v>2.74939227104187</v>
+        <v>2.74939203262329</v>
       </c>
       <c r="H2060" t="n">
         <v>209580</v>
@@ -60341,7 +60341,7 @@
         <v>3.07699990272522</v>
       </c>
       <c r="G2068" t="n">
-        <v>2.55972123146057</v>
+        <v>2.55972146987915</v>
       </c>
       <c r="H2068" t="n">
         <v>434577</v>
@@ -60370,7 +60370,7 @@
         <v>3.06450009346008</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.54932308197021</v>
+        <v>2.54932284355164</v>
       </c>
       <c r="H2069" t="n">
         <v>190789</v>
@@ -60428,7 +60428,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G2071" t="n">
-        <v>2.51063990592957</v>
+        <v>2.51064014434814</v>
       </c>
       <c r="H2071" t="n">
         <v>176906</v>
@@ -60515,7 +60515,7 @@
         <v>2.96600008010864</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.46738195419312</v>
+        <v>2.46738171577454</v>
       </c>
       <c r="H2074" t="n">
         <v>178402</v>
@@ -60544,7 +60544,7 @@
         <v>2.96700000762939</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.4682137966156</v>
+        <v>2.46821355819702</v>
       </c>
       <c r="H2075" t="n">
         <v>201536</v>
@@ -60631,7 +60631,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2078" t="n">
-        <v>2.42495536804199</v>
+        <v>2.42495560646057</v>
       </c>
       <c r="H2078" t="n">
         <v>290118</v>
@@ -60689,7 +60689,7 @@
         <v>2.95099997520447</v>
       </c>
       <c r="G2080" t="n">
-        <v>2.4549036026001</v>
+        <v>2.45490336418152</v>
       </c>
       <c r="H2080" t="n">
         <v>189020</v>
@@ -60805,7 +60805,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G2084" t="n">
-        <v>2.49608182907104</v>
+        <v>2.49608206748962</v>
       </c>
       <c r="H2084" t="n">
         <v>424179</v>
@@ -60892,7 +60892,7 @@
         <v>3.07699990272522</v>
       </c>
       <c r="G2087" t="n">
-        <v>2.55972123146057</v>
+        <v>2.55972146987915</v>
       </c>
       <c r="H2087" t="n">
         <v>251454</v>
@@ -61240,7 +61240,7 @@
         <v>3.21600008010864</v>
       </c>
       <c r="G2099" t="n">
-        <v>2.67535424232483</v>
+        <v>2.67535400390625</v>
       </c>
       <c r="H2099" t="n">
         <v>120798</v>
@@ -61269,7 +61269,7 @@
         <v>3.27800011634827</v>
       </c>
       <c r="G2100" t="n">
-        <v>2.72693109512329</v>
+        <v>2.72693133354187</v>
       </c>
       <c r="H2100" t="n">
         <v>408594</v>
@@ -61472,7 +61472,7 @@
         <v>3.38599991798401</v>
       </c>
       <c r="G2107" t="n">
-        <v>2.81677508354187</v>
+        <v>2.81677484512329</v>
       </c>
       <c r="H2107" t="n">
         <v>219094</v>
@@ -61704,7 +61704,7 @@
         <v>3.87400007247925</v>
       </c>
       <c r="G2115" t="n">
-        <v>3.22273707389832</v>
+        <v>3.22273683547974</v>
       </c>
       <c r="H2115" t="n">
         <v>907508</v>
@@ -61733,7 +61733,7 @@
         <v>3.86800003051758</v>
       </c>
       <c r="G2116" t="n">
-        <v>3.21774554252625</v>
+        <v>3.21774530410767</v>
       </c>
       <c r="H2116" t="n">
         <v>299565</v>
@@ -61878,7 +61878,7 @@
         <v>3.80599999427795</v>
       </c>
       <c r="G2121" t="n">
-        <v>3.16616821289062</v>
+        <v>3.1661684513092</v>
       </c>
       <c r="H2121" t="n">
         <v>158809</v>
@@ -61907,7 +61907,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G2122" t="n">
-        <v>3.10627222061157</v>
+        <v>3.10627245903015</v>
       </c>
       <c r="H2122" t="n">
         <v>322970</v>
@@ -62052,7 +62052,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G2127" t="n">
-        <v>3.20942664146423</v>
+        <v>3.20942640304565</v>
       </c>
       <c r="H2127" t="n">
         <v>142725</v>
@@ -62313,7 +62313,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G2136" t="n">
-        <v>3.29927039146423</v>
+        <v>3.29927062988281</v>
       </c>
       <c r="H2136" t="n">
         <v>774950</v>
@@ -62371,7 +62371,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2138" t="n">
-        <v>3.40242481231689</v>
+        <v>3.40242457389832</v>
       </c>
       <c r="H2138" t="n">
         <v>367846</v>
@@ -62429,7 +62429,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G2140" t="n">
-        <v>3.38578701019287</v>
+        <v>3.38578724861145</v>
       </c>
       <c r="H2140" t="n">
         <v>395788</v>
@@ -62458,7 +62458,7 @@
         <v>4.10599994659424</v>
       </c>
       <c r="G2141" t="n">
-        <v>3.4157350063324</v>
+        <v>3.41573476791382</v>
       </c>
       <c r="H2141" t="n">
         <v>281002</v>
@@ -62487,7 +62487,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2142" t="n">
-        <v>3.48561382293701</v>
+        <v>3.48561358451843</v>
       </c>
       <c r="H2142" t="n">
         <v>535695</v>
@@ -62545,7 +62545,7 @@
         <v>4.32200002670288</v>
       </c>
       <c r="G2144" t="n">
-        <v>3.59542274475098</v>
+        <v>3.5954225063324</v>
       </c>
       <c r="H2144" t="n">
         <v>956033</v>
@@ -62922,7 +62922,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G2157" t="n">
-        <v>3.22772836685181</v>
+        <v>3.22772812843323</v>
       </c>
       <c r="H2157" t="n">
         <v>1061275</v>
@@ -63009,7 +63009,7 @@
         <v>3.99200010299683</v>
       </c>
       <c r="G2160" t="n">
-        <v>3.32089948654175</v>
+        <v>3.32089972496033</v>
       </c>
       <c r="H2160" t="n">
         <v>338278</v>
@@ -63183,7 +63183,7 @@
         <v>4.13600015640259</v>
       </c>
       <c r="G2166" t="n">
-        <v>3.44069147109985</v>
+        <v>3.44069170951843</v>
       </c>
       <c r="H2166" t="n">
         <v>396325</v>
@@ -63299,7 +63299,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G2170" t="n">
-        <v>3.58211302757263</v>
+        <v>3.58211278915405</v>
       </c>
       <c r="H2170" t="n">
         <v>282823</v>
@@ -63328,7 +63328,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G2171" t="n">
-        <v>3.95646238327026</v>
+        <v>3.95646262168884</v>
       </c>
       <c r="H2171" t="n">
         <v>2664405</v>
@@ -63415,7 +63415,7 @@
         <v>4.62799978256226</v>
       </c>
       <c r="G2174" t="n">
-        <v>3.84998059272766</v>
+        <v>3.84998083114624</v>
       </c>
       <c r="H2174" t="n">
         <v>294219</v>
@@ -63444,7 +63444,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G2175" t="n">
-        <v>3.87660121917725</v>
+        <v>3.87660098075867</v>
       </c>
       <c r="H2175" t="n">
         <v>306977</v>
@@ -80038,6 +80038,35 @@
         <v>341336</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>2.88599991798401</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>2.93199992179871</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>2.88599991798401</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>2.89599990844727</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>2.89599990844727</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>166801</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>
